--- a/TFG1/02_datasets/metadata/METADATA.xlsx
+++ b/TFG1/02_datasets/metadata/METADATA.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Scripts-CIC18" sheetId="1" state="visible" r:id="rId3"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="294">
   <si>
     <t xml:space="preserve">TÉCNICA</t>
   </si>
@@ -355,31 +355,11 @@
 Pd_CIC18__NearMiss_SMOTE__v1__val__5.csv</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">pd_CIC18__NearMiss_SMOTE__v1__training_v1__1_5.ipynb
+    <t xml:space="preserve">pd_CIC18__NearMiss_SMOTE__v1__training_v1__1_5.ipynb
 pd_CIC18__NearMiss_SMOTE__v1__training_v1__2_5.ipynb
 pd_CIC18__NearMiss_SMOTE__v1__training_v1__3_5.ipynb
-</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">pd_CIC18__NearMiss_SMOTE__v1__training_v1__4_5.ipynb
+pd_CIC18__NearMiss_SMOTE__v1__training_v1__4_5.ipynb
 pd_CIC18__NearMiss_SMOTE__v1__training_v1__5_5.ipynb</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">Entrenamiento con Simple T5. 2 horas por epoch
@@ -563,6 +543,36 @@
   </si>
   <si>
     <t xml:space="preserve">COLUMNAS:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NÚMERO EXPERIMENTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DESCRIPCIÓN EXPERIMENTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACCURACY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRECISION WEIGHTED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECALL WEIGHTED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F1 WEIGHTED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRECISION MACRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECALL MACRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F1 MACRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCC</t>
   </si>
   <si>
     <t xml:space="preserve">CIC18__clean_dataset_v1.ipynb</t>
@@ -860,7 +870,17 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">pd_CIC17__NearMiss_SMOTE__v1__training_v1__4_5.ipynb
-pd_CIC17__NearMiss_SMOTE__v1__training_v1__5_5.ipynb</t>
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pd_CIC17__NearMiss_SMOTE__v1__training_v1__5_5.ipynb</t>
     </r>
   </si>
   <si>
@@ -1319,31 +1339,11 @@
 Pd_BCCC17__NearMiss_SMOTE__v1__val__5.csv</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">pd_BCCC17__NearMiss_SMOTE__v1__training_v1__1_5.ipynb
+    <t xml:space="preserve">pd_BCCC17__NearMiss_SMOTE__v1__training_v1__1_5.ipynb
 pd_BCCC17__NearMiss_SMOTE__v1__training_v1__2_5.ipynb
 pd_BCCC17__NearMiss_SMOTE__v1__training_v1__3_5.ipynb
-</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">pd_BCCC17__NearMiss_SMOTE__v1__training_v1__4_5.ipynb
+pd_BCCC17__NearMiss_SMOTE__v1__training_v1__4_5.ipynb
 pd_BCCC17__NearMiss_SMOTE__v1__training_v1__5_5.ipynb</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">pd_BCCC17__NearMiss_SMOTE__v1__train__1.csv
@@ -1813,7 +1813,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="128">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1962,6 +1962,14 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1974,11 +1982,187 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1987,170 +2171,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2879,22 +2899,22 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="37" t="s">
+      <c r="A20" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="B20" s="38" t="s">
+      <c r="B20" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="38" t="s">
+      <c r="C20" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="D20" s="38" t="s">
+      <c r="D20" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="E20" s="38"/>
-      <c r="F20" s="39"/>
-    </row>
-    <row r="21" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E20" s="25"/>
+      <c r="F20" s="23"/>
+    </row>
+    <row r="21" customFormat="false" ht="127.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="26"/>
       <c r="B21" s="27"/>
       <c r="C21" s="27"/>
@@ -2902,12 +2922,12 @@
       <c r="E21" s="27"/>
       <c r="F21" s="28"/>
     </row>
-    <row r="22" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="40"/>
-      <c r="B22" s="41"/>
-      <c r="C22" s="41"/>
-      <c r="D22" s="41"/>
-      <c r="E22" s="41"/>
+    <row r="22" customFormat="false" ht="98.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="37"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
       <c r="F22" s="31"/>
     </row>
     <row r="23" s="2" customFormat="true" ht="119.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2947,38 +2967,38 @@
       <c r="F24" s="22"/>
     </row>
     <row r="25" customFormat="false" ht="299.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="42" t="s">
+      <c r="A25" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="B25" s="43" t="s">
+      <c r="B25" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="43" t="s">
+      <c r="C25" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="D25" s="43" t="s">
+      <c r="D25" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="E25" s="43"/>
-      <c r="F25" s="39" t="s">
+      <c r="E25" s="15"/>
+      <c r="F25" s="23" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="213.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="26" t="s">
+      <c r="A26" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="B26" s="27" t="s">
+      <c r="B26" s="40" t="s">
         <v>66</v>
       </c>
-      <c r="C26" s="27" t="s">
+      <c r="C26" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="D26" s="27" t="s">
+      <c r="D26" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="E26" s="27"/>
-      <c r="F26" s="28"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="41"/>
     </row>
     <row r="27" customFormat="false" ht="213.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="26"/>
@@ -3039,38 +3059,38 @@
       <c r="H30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="191.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="42" t="s">
+      <c r="A31" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="B31" s="43" t="s">
+      <c r="B31" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="C31" s="43" t="s">
+      <c r="C31" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D31" s="43" t="s">
+      <c r="D31" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="E31" s="43"/>
-      <c r="F31" s="39" t="s">
+      <c r="E31" s="15"/>
+      <c r="F31" s="23" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="165.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="26" t="s">
+      <c r="A32" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="B32" s="27" t="s">
+      <c r="B32" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="C32" s="27" t="s">
+      <c r="C32" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="D32" s="27" t="s">
+      <c r="D32" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="E32" s="27"/>
-      <c r="F32" s="28"/>
+      <c r="E32" s="40"/>
+      <c r="F32" s="41"/>
     </row>
     <row r="33" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="26"/>
@@ -3115,137 +3135,137 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="62" t="s">
+      <c r="B1" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="62" t="s">
+      <c r="C1" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="62" t="s">
+      <c r="D1" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="62" t="s">
+      <c r="E1" s="65" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="179.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="63"/>
-      <c r="B2" s="64" t="s">
-        <v>274</v>
-      </c>
-      <c r="C2" s="65" t="s">
-        <v>102</v>
-      </c>
-      <c r="D2" s="65" t="s">
-        <v>208</v>
-      </c>
-      <c r="E2" s="65" t="s">
-        <v>275</v>
+      <c r="A2" s="66"/>
+      <c r="B2" s="67" t="s">
+        <v>284</v>
+      </c>
+      <c r="C2" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="D2" s="68" t="s">
+        <v>218</v>
+      </c>
+      <c r="E2" s="68" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="101.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="64"/>
-      <c r="B3" s="64" t="s">
-        <v>276</v>
-      </c>
-      <c r="C3" s="64" t="s">
-        <v>105</v>
-      </c>
-      <c r="D3" s="65" t="s">
-        <v>275</v>
-      </c>
-      <c r="E3" s="65" t="s">
-        <v>277</v>
+      <c r="A3" s="67"/>
+      <c r="B3" s="67" t="s">
+        <v>286</v>
+      </c>
+      <c r="C3" s="67" t="s">
+        <v>115</v>
+      </c>
+      <c r="D3" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="E3" s="68" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="86.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="64"/>
-      <c r="B4" s="64" t="s">
-        <v>278</v>
-      </c>
-      <c r="C4" s="64" t="s">
-        <v>108</v>
-      </c>
-      <c r="D4" s="65" t="s">
-        <v>277</v>
-      </c>
-      <c r="E4" s="65" t="s">
-        <v>279</v>
+      <c r="A4" s="67"/>
+      <c r="B4" s="67" t="s">
+        <v>288</v>
+      </c>
+      <c r="C4" s="67" t="s">
+        <v>118</v>
+      </c>
+      <c r="D4" s="68" t="s">
+        <v>287</v>
+      </c>
+      <c r="E4" s="68" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="89.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="64"/>
-      <c r="B5" s="64" t="s">
-        <v>280</v>
-      </c>
-      <c r="C5" s="65" t="s">
-        <v>111</v>
-      </c>
-      <c r="D5" s="65" t="s">
-        <v>279</v>
-      </c>
-      <c r="E5" s="64"/>
+      <c r="A5" s="67"/>
+      <c r="B5" s="67" t="s">
+        <v>290</v>
+      </c>
+      <c r="C5" s="68" t="s">
+        <v>121</v>
+      </c>
+      <c r="D5" s="68" t="s">
+        <v>289</v>
+      </c>
+      <c r="E5" s="67"/>
     </row>
     <row r="6" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="63"/>
-      <c r="B6" s="64" t="s">
-        <v>281</v>
-      </c>
-      <c r="C6" s="65" t="s">
-        <v>282</v>
-      </c>
-      <c r="D6" s="65" t="s">
-        <v>208</v>
-      </c>
-      <c r="E6" s="65" t="s">
-        <v>283</v>
+      <c r="A6" s="66"/>
+      <c r="B6" s="67" t="s">
+        <v>291</v>
+      </c>
+      <c r="C6" s="68" t="s">
+        <v>292</v>
+      </c>
+      <c r="D6" s="68" t="s">
+        <v>218</v>
+      </c>
+      <c r="E6" s="68" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="86.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="64"/>
-      <c r="B7" s="64" t="s">
-        <v>276</v>
-      </c>
-      <c r="C7" s="64" t="s">
-        <v>105</v>
-      </c>
-      <c r="D7" s="65" t="s">
-        <v>275</v>
-      </c>
-      <c r="E7" s="65" t="s">
-        <v>277</v>
+      <c r="A7" s="67"/>
+      <c r="B7" s="67" t="s">
+        <v>286</v>
+      </c>
+      <c r="C7" s="67" t="s">
+        <v>115</v>
+      </c>
+      <c r="D7" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="E7" s="68" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="107.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="66"/>
-      <c r="B8" s="66" t="s">
-        <v>278</v>
-      </c>
-      <c r="C8" s="66" t="s">
-        <v>108</v>
-      </c>
-      <c r="D8" s="67" t="s">
-        <v>277</v>
-      </c>
-      <c r="E8" s="67" t="s">
-        <v>279</v>
+      <c r="A8" s="69"/>
+      <c r="B8" s="69" t="s">
+        <v>288</v>
+      </c>
+      <c r="C8" s="69" t="s">
+        <v>118</v>
+      </c>
+      <c r="D8" s="70" t="s">
+        <v>287</v>
+      </c>
+      <c r="E8" s="70" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="123.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="68"/>
-      <c r="B9" s="68" t="s">
-        <v>280</v>
-      </c>
-      <c r="C9" s="69" t="s">
-        <v>111</v>
-      </c>
-      <c r="D9" s="69" t="s">
-        <v>279</v>
-      </c>
-      <c r="E9" s="68"/>
+      <c r="A9" s="71"/>
+      <c r="B9" s="71" t="s">
+        <v>290</v>
+      </c>
+      <c r="C9" s="72" t="s">
+        <v>121</v>
+      </c>
+      <c r="D9" s="72" t="s">
+        <v>289</v>
+      </c>
+      <c r="E9" s="71"/>
     </row>
     <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -3268,11 +3288,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD28"/>
+  <dimension ref="A1:XFD46"/>
   <sheetFormatPr defaultColWidth="10.18359375" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="35.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="19.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="34.64"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="25.12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="21.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="21.2"/>
@@ -3284,576 +3304,576 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="31.21"/>
   </cols>
   <sheetData>
-    <row r="1" s="47" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="44" t="s">
+    <row r="1" s="45" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="42" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="42" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="45" t="s">
+      <c r="C1" s="43" t="s">
         <v>81</v>
       </c>
-      <c r="D1" s="45" t="s">
+      <c r="D1" s="43" t="s">
         <v>82</v>
       </c>
-      <c r="E1" s="45" t="s">
+      <c r="E1" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="F1" s="45" t="s">
+      <c r="F1" s="43" t="s">
         <v>84</v>
       </c>
-      <c r="G1" s="45" t="s">
+      <c r="G1" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="45" t="s">
+      <c r="H1" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="I1" s="46" t="s">
+      <c r="I1" s="44" t="s">
         <v>57</v>
       </c>
-      <c r="J1" s="45" t="s">
+      <c r="J1" s="43" t="s">
         <v>46</v>
       </c>
-      <c r="K1" s="46" t="s">
+      <c r="K1" s="44" t="s">
         <v>68</v>
       </c>
       <c r="XFD1" s="2"/>
     </row>
     <row r="2" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="46" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="49" t="n">
+      <c r="B2" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="50" t="n">
+      <c r="C2" s="48" t="n">
         <v>13484658</v>
       </c>
-      <c r="D2" s="50" t="n">
+      <c r="D2" s="48" t="n">
         <v>13445443</v>
       </c>
-      <c r="E2" s="50" t="n">
+      <c r="E2" s="48" t="n">
         <v>450000</v>
       </c>
-      <c r="F2" s="50" t="n">
+      <c r="F2" s="48" t="n">
         <v>360000</v>
       </c>
-      <c r="G2" s="50" t="n">
+      <c r="G2" s="48" t="n">
         <v>339865</v>
       </c>
-      <c r="H2" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I2" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J2" s="50" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K2" s="52" t="n">
+      <c r="H2" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I2" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J2" s="48" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K2" s="50" t="n">
         <v>10000</v>
       </c>
       <c r="XFD2" s="2"/>
     </row>
     <row r="3" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="53" t="s">
+      <c r="A3" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="B3" s="49" t="n">
+      <c r="B3" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="50" t="n">
+      <c r="C3" s="48" t="n">
         <v>686012</v>
       </c>
-      <c r="D3" s="50" t="n">
+      <c r="D3" s="48" t="n">
         <v>668461</v>
       </c>
-      <c r="E3" s="50" t="n">
+      <c r="E3" s="48" t="n">
         <v>450000</v>
       </c>
-      <c r="F3" s="50" t="n">
+      <c r="F3" s="48" t="n">
         <v>360000</v>
       </c>
-      <c r="G3" s="50" t="n">
+      <c r="G3" s="48" t="n">
         <v>359280</v>
       </c>
-      <c r="H3" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I3" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J3" s="50" t="n">
+      <c r="H3" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I3" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J3" s="48" t="n">
         <v>9840</v>
       </c>
-      <c r="K3" s="52" t="n">
+      <c r="K3" s="50" t="n">
         <v>9993</v>
       </c>
       <c r="XFD3" s="2"/>
     </row>
     <row r="4" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="51" t="s">
         <v>87</v>
       </c>
-      <c r="B4" s="49" t="n">
+      <c r="B4" s="47" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="50" t="n">
+      <c r="C4" s="48" t="n">
         <v>576191</v>
       </c>
-      <c r="D4" s="50" t="n">
+      <c r="D4" s="48" t="n">
         <v>576175</v>
       </c>
-      <c r="E4" s="50" t="n">
+      <c r="E4" s="48" t="n">
         <v>450000</v>
       </c>
-      <c r="F4" s="50" t="n">
+      <c r="F4" s="48" t="n">
         <v>360000</v>
       </c>
-      <c r="G4" s="50" t="n">
+      <c r="G4" s="48" t="n">
         <v>359369</v>
       </c>
-      <c r="H4" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I4" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J4" s="50" t="n">
+      <c r="H4" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I4" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J4" s="48" t="n">
         <v>9974</v>
       </c>
-      <c r="K4" s="52" t="n">
+      <c r="K4" s="50" t="n">
         <v>9968</v>
       </c>
       <c r="XFD4" s="2"/>
     </row>
     <row r="5" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="53" t="s">
+      <c r="A5" s="51" t="s">
         <v>88</v>
       </c>
-      <c r="B5" s="49" t="n">
+      <c r="B5" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="50" t="n">
+      <c r="C5" s="48" t="n">
         <v>461912</v>
       </c>
-      <c r="D5" s="50" t="n">
+      <c r="D5" s="48" t="n">
         <v>434873</v>
       </c>
-      <c r="E5" s="54" t="n">
+      <c r="E5" s="52" t="n">
         <v>434873</v>
       </c>
-      <c r="F5" s="50" t="n">
+      <c r="F5" s="48" t="n">
         <v>347898</v>
       </c>
-      <c r="G5" s="50" t="n">
+      <c r="G5" s="48" t="n">
         <v>346118</v>
       </c>
-      <c r="H5" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I5" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J5" s="50" t="n">
+      <c r="H5" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I5" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J5" s="48" t="n">
         <v>9855</v>
       </c>
-      <c r="K5" s="52" t="n">
+      <c r="K5" s="50" t="n">
         <v>9914</v>
       </c>
       <c r="XFD5" s="2"/>
     </row>
     <row r="6" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="53" t="s">
+      <c r="A6" s="51" t="s">
         <v>89</v>
       </c>
-      <c r="B6" s="49" t="n">
+      <c r="B6" s="47" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="50" t="n">
+      <c r="C6" s="48" t="n">
         <v>286191</v>
       </c>
-      <c r="D6" s="50" t="n">
+      <c r="D6" s="48" t="n">
         <v>282310</v>
       </c>
-      <c r="E6" s="54" t="n">
+      <c r="E6" s="52" t="n">
         <v>282310</v>
       </c>
-      <c r="F6" s="50" t="n">
+      <c r="F6" s="48" t="n">
         <v>225848</v>
       </c>
-      <c r="G6" s="50" t="n">
+      <c r="G6" s="48" t="n">
         <v>225602</v>
       </c>
-      <c r="H6" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I6" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J6" s="50" t="n">
+      <c r="H6" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I6" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J6" s="48" t="n">
         <v>9971</v>
       </c>
-      <c r="K6" s="52" t="n">
+      <c r="K6" s="50" t="n">
         <v>10000</v>
       </c>
       <c r="XFD6" s="2"/>
     </row>
     <row r="7" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="53" t="s">
+      <c r="A7" s="51" t="s">
         <v>90</v>
       </c>
-      <c r="B7" s="49" t="n">
+      <c r="B7" s="47" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="50" t="n">
+      <c r="C7" s="48" t="n">
         <v>161934</v>
       </c>
-      <c r="D7" s="50" t="n">
+      <c r="D7" s="48" t="n">
         <v>161897</v>
       </c>
-      <c r="E7" s="54" t="n">
+      <c r="E7" s="52" t="n">
         <v>161897</v>
       </c>
-      <c r="F7" s="50" t="n">
+      <c r="F7" s="48" t="n">
         <v>129517</v>
       </c>
-      <c r="G7" s="50" t="n">
+      <c r="G7" s="48" t="n">
         <v>108526</v>
       </c>
-      <c r="H7" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I7" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J7" s="50" t="n">
+      <c r="H7" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I7" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J7" s="48" t="n">
         <v>8820</v>
       </c>
-      <c r="K7" s="52" t="n">
+      <c r="K7" s="50" t="n">
         <v>9998</v>
       </c>
       <c r="XFD7" s="2"/>
     </row>
     <row r="8" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="53" t="s">
+      <c r="A8" s="51" t="s">
         <v>91</v>
       </c>
-      <c r="B8" s="49" t="n">
+      <c r="B8" s="47" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="50" t="n">
+      <c r="C8" s="48" t="n">
         <v>187589</v>
       </c>
-      <c r="D8" s="50" t="n">
+      <c r="D8" s="48" t="n">
         <v>117322</v>
       </c>
-      <c r="E8" s="54" t="n">
+      <c r="E8" s="52" t="n">
         <v>117322</v>
       </c>
-      <c r="F8" s="50" t="n">
+      <c r="F8" s="48" t="n">
         <v>93857</v>
       </c>
-      <c r="G8" s="50" t="n">
+      <c r="G8" s="48" t="n">
         <v>93112</v>
       </c>
-      <c r="H8" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I8" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J8" s="50" t="n">
+      <c r="H8" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I8" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J8" s="48" t="n">
         <v>9896</v>
       </c>
-      <c r="K8" s="52" t="n">
+      <c r="K8" s="50" t="n">
         <v>9967</v>
       </c>
       <c r="XFD8" s="2"/>
     </row>
     <row r="9" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="53" t="s">
+      <c r="A9" s="51" t="s">
         <v>92</v>
       </c>
-      <c r="B9" s="49" t="n">
+      <c r="B9" s="47" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="50" t="n">
+      <c r="C9" s="48" t="n">
         <v>41508</v>
       </c>
-      <c r="D9" s="50" t="n">
+      <c r="D9" s="48" t="n">
         <v>41455</v>
       </c>
-      <c r="E9" s="54" t="n">
+      <c r="E9" s="52" t="n">
         <v>41455</v>
       </c>
-      <c r="F9" s="50" t="n">
+      <c r="F9" s="48" t="n">
         <v>33164</v>
       </c>
-      <c r="G9" s="50" t="n">
+      <c r="G9" s="48" t="n">
         <v>31187</v>
       </c>
-      <c r="H9" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I9" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J9" s="50" t="n">
+      <c r="H9" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I9" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J9" s="48" t="n">
         <v>9533</v>
       </c>
-      <c r="K9" s="52" t="n">
+      <c r="K9" s="50" t="n">
         <v>9974</v>
       </c>
       <c r="XFD9" s="2"/>
     </row>
     <row r="10" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="53" t="s">
+      <c r="A10" s="51" t="s">
         <v>93</v>
       </c>
-      <c r="B10" s="49" t="n">
+      <c r="B10" s="47" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="50" t="n">
+      <c r="C10" s="48" t="n">
         <v>193360</v>
       </c>
-      <c r="D10" s="50" t="n">
+      <c r="D10" s="48" t="n">
         <v>39352</v>
       </c>
-      <c r="E10" s="54" t="n">
+      <c r="E10" s="52" t="n">
         <v>39352</v>
       </c>
-      <c r="F10" s="50" t="n">
+      <c r="F10" s="48" t="n">
         <v>31482</v>
       </c>
-      <c r="G10" s="50" t="n">
+      <c r="G10" s="48" t="n">
         <v>31432</v>
       </c>
-      <c r="H10" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I10" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J10" s="50" t="n">
+      <c r="H10" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I10" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J10" s="48" t="n">
         <v>9986</v>
       </c>
-      <c r="K10" s="52" t="n">
+      <c r="K10" s="50" t="n">
         <v>10000</v>
       </c>
       <c r="XFD10" s="2"/>
     </row>
     <row r="11" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="53" t="s">
+      <c r="A11" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="B11" s="49" t="n">
+      <c r="B11" s="47" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="50" t="n">
+      <c r="C11" s="48" t="n">
         <v>139890</v>
       </c>
-      <c r="D11" s="50" t="n">
+      <c r="D11" s="48" t="n">
         <v>19462</v>
       </c>
-      <c r="E11" s="54" t="n">
+      <c r="E11" s="52" t="n">
         <v>19462</v>
       </c>
-      <c r="F11" s="50" t="n">
+      <c r="F11" s="48" t="n">
         <v>15570</v>
       </c>
-      <c r="G11" s="50" t="n">
+      <c r="G11" s="48" t="n">
         <v>15570</v>
       </c>
-      <c r="H11" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I11" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J11" s="50" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K11" s="52" t="n">
+      <c r="H11" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I11" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J11" s="48" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K11" s="50" t="n">
         <v>10000</v>
       </c>
       <c r="XFD11" s="2"/>
     </row>
     <row r="12" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="B12" s="49" t="n">
+      <c r="B12" s="47" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="50" t="n">
+      <c r="C12" s="48" t="n">
         <v>10990</v>
       </c>
-      <c r="D12" s="50" t="n">
+      <c r="D12" s="48" t="n">
         <v>10285</v>
       </c>
-      <c r="E12" s="54" t="n">
+      <c r="E12" s="52" t="n">
         <v>10285</v>
       </c>
-      <c r="F12" s="50" t="n">
+      <c r="F12" s="48" t="n">
         <v>8228</v>
       </c>
-      <c r="G12" s="50" t="n">
+      <c r="G12" s="48" t="n">
         <v>7975</v>
       </c>
-      <c r="H12" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I12" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J12" s="50" t="n">
+      <c r="H12" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I12" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J12" s="48" t="n">
         <v>9838</v>
       </c>
-      <c r="K12" s="52" t="n">
+      <c r="K12" s="50" t="n">
         <v>9939</v>
       </c>
       <c r="XFD12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="51" t="s">
         <v>96</v>
       </c>
-      <c r="B13" s="49" t="n">
+      <c r="B13" s="47" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="50" t="n">
+      <c r="C13" s="48" t="n">
         <v>1730</v>
       </c>
-      <c r="D13" s="50" t="n">
+      <c r="D13" s="48" t="n">
         <v>1730</v>
       </c>
-      <c r="E13" s="54" t="n">
+      <c r="E13" s="52" t="n">
         <v>1730</v>
       </c>
-      <c r="F13" s="50" t="n">
+      <c r="F13" s="48" t="n">
         <v>1384</v>
       </c>
-      <c r="G13" s="50" t="n">
+      <c r="G13" s="48" t="n">
         <v>1378</v>
       </c>
-      <c r="H13" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I13" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J13" s="50" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K13" s="52" t="n">
+      <c r="H13" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I13" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J13" s="48" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K13" s="50" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="53" t="s">
+      <c r="A14" s="51" t="s">
         <v>97</v>
       </c>
-      <c r="B14" s="49" t="n">
+      <c r="B14" s="47" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="50" t="n">
+      <c r="C14" s="48" t="n">
         <v>611</v>
       </c>
-      <c r="D14" s="50" t="n">
+      <c r="D14" s="48" t="n">
         <v>611</v>
       </c>
-      <c r="E14" s="54" t="n">
+      <c r="E14" s="52" t="n">
         <v>611</v>
       </c>
-      <c r="F14" s="50" t="n">
+      <c r="F14" s="48" t="n">
         <v>489</v>
       </c>
-      <c r="G14" s="50" t="n">
+      <c r="G14" s="48" t="n">
         <v>211</v>
       </c>
-      <c r="H14" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I14" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J14" s="50" t="n">
+      <c r="H14" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I14" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J14" s="48" t="n">
         <v>9624</v>
       </c>
-      <c r="K14" s="52" t="n">
+      <c r="K14" s="50" t="n">
         <v>9593</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="53" t="s">
+      <c r="A15" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="B15" s="49" t="n">
+      <c r="B15" s="47" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="50" t="n">
+      <c r="C15" s="48" t="n">
         <v>230</v>
       </c>
-      <c r="D15" s="50" t="n">
+      <c r="D15" s="48" t="n">
         <v>230</v>
       </c>
-      <c r="E15" s="54" t="n">
+      <c r="E15" s="52" t="n">
         <v>230</v>
       </c>
-      <c r="F15" s="50" t="n">
+      <c r="F15" s="48" t="n">
         <v>184</v>
       </c>
-      <c r="G15" s="50" t="n">
+      <c r="G15" s="48" t="n">
         <v>66</v>
       </c>
-      <c r="H15" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I15" s="51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J15" s="50" t="n">
+      <c r="H15" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I15" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J15" s="48" t="n">
         <v>9673</v>
       </c>
-      <c r="K15" s="52" t="n">
+      <c r="K15" s="50" t="n">
         <v>9655</v>
       </c>
       <c r="XFD15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="55" t="s">
+      <c r="A16" s="53" t="s">
         <v>99</v>
       </c>
-      <c r="B16" s="56" t="n">
+      <c r="B16" s="54" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="57" t="n">
+      <c r="C16" s="55" t="n">
         <v>87</v>
       </c>
-      <c r="D16" s="57" t="n">
+      <c r="D16" s="55" t="n">
         <v>87</v>
       </c>
-      <c r="E16" s="57" t="n">
+      <c r="E16" s="55" t="n">
         <v>87</v>
       </c>
-      <c r="F16" s="57" t="n">
+      <c r="F16" s="55" t="n">
         <v>70</v>
       </c>
-      <c r="G16" s="58" t="n">
+      <c r="G16" s="56" t="n">
         <v>70</v>
       </c>
-      <c r="H16" s="59" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I16" s="59" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J16" s="57" t="n">
+      <c r="H16" s="57" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I16" s="57" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J16" s="55" t="n">
         <v>9987</v>
       </c>
-      <c r="K16" s="60" t="n">
+      <c r="K16" s="58" t="n">
         <v>9986</v>
       </c>
     </row>
@@ -3896,18 +3916,18 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E18" s="61"/>
-      <c r="F18" s="49"/>
+      <c r="E18" s="59"/>
+      <c r="F18" s="47"/>
       <c r="G18" s="3"/>
-      <c r="H18" s="61"/>
-      <c r="I18" s="50"/>
+      <c r="H18" s="59"/>
+      <c r="I18" s="48"/>
     </row>
     <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E19" s="61"/>
-      <c r="F19" s="49"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="47"/>
       <c r="G19" s="3"/>
-      <c r="H19" s="50"/>
-      <c r="I19" s="50"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="48"/>
     </row>
     <row r="20" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
@@ -3928,23 +3948,23 @@
       <c r="G20" s="3" t="n">
         <v>56</v>
       </c>
-      <c r="H20" s="50" t="n">
+      <c r="H20" s="48" t="n">
         <v>56</v>
       </c>
-      <c r="I20" s="50" t="n">
+      <c r="I20" s="48" t="n">
         <v>56</v>
       </c>
       <c r="XFD20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G21" s="3"/>
-      <c r="H21" s="50"/>
-      <c r="I21" s="50"/>
+      <c r="H21" s="48"/>
+      <c r="I21" s="48"/>
     </row>
     <row r="22" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G22" s="3"/>
-      <c r="H22" s="50"/>
-      <c r="I22" s="50"/>
+      <c r="H22" s="48"/>
+      <c r="I22" s="48"/>
     </row>
     <row r="23" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G23" s="3"/>
@@ -3955,14 +3975,293 @@
     <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G25" s="3"/>
     </row>
-    <row r="26" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G26" s="3"/>
+    <row r="26" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="60" t="s">
+        <v>101</v>
+      </c>
+      <c r="B26" s="60" t="s">
+        <v>102</v>
+      </c>
+      <c r="C26" s="60" t="s">
+        <v>103</v>
+      </c>
+      <c r="D26" s="60" t="s">
+        <v>104</v>
+      </c>
+      <c r="E26" s="60" t="s">
+        <v>105</v>
+      </c>
+      <c r="F26" s="60" t="s">
+        <v>106</v>
+      </c>
+      <c r="G26" s="60" t="s">
+        <v>107</v>
+      </c>
+      <c r="H26" s="60" t="s">
+        <v>108</v>
+      </c>
+      <c r="I26" s="60" t="s">
+        <v>109</v>
+      </c>
+      <c r="J26" s="61" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G27" s="3"/>
-    </row>
-    <row r="28" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G28" s="3"/>
+      <c r="A27" s="62" t="n">
+        <v>1</v>
+      </c>
+      <c r="B27" s="62" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="48"/>
+      <c r="D27" s="48"/>
+      <c r="E27" s="48"/>
+      <c r="F27" s="48"/>
+      <c r="G27" s="48"/>
+      <c r="H27" s="48"/>
+      <c r="I27" s="48"/>
+      <c r="J27" s="48"/>
+    </row>
+    <row r="28" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="62" t="n">
+        <v>2</v>
+      </c>
+      <c r="B28" s="62" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" s="48"/>
+      <c r="D28" s="48"/>
+      <c r="E28" s="48"/>
+      <c r="F28" s="48"/>
+      <c r="G28" s="48"/>
+      <c r="H28" s="48"/>
+      <c r="I28" s="48"/>
+      <c r="J28" s="48"/>
+    </row>
+    <row r="29" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="62" t="n">
+        <v>3</v>
+      </c>
+      <c r="B29" s="62" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" s="63"/>
+      <c r="D29" s="63"/>
+      <c r="E29" s="63"/>
+      <c r="F29" s="63"/>
+      <c r="G29" s="63"/>
+      <c r="H29" s="63"/>
+      <c r="I29" s="63"/>
+      <c r="J29" s="64"/>
+    </row>
+    <row r="30" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="62" t="n">
+        <v>4</v>
+      </c>
+      <c r="B30" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30" s="48"/>
+      <c r="D30" s="48"/>
+      <c r="E30" s="48"/>
+      <c r="F30" s="48"/>
+      <c r="G30" s="48"/>
+      <c r="H30" s="48"/>
+      <c r="I30" s="48"/>
+      <c r="J30" s="48"/>
+    </row>
+    <row r="31" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="48"/>
+      <c r="B31" s="48"/>
+      <c r="C31" s="48"/>
+      <c r="D31" s="48"/>
+      <c r="E31" s="48"/>
+      <c r="F31" s="48"/>
+      <c r="G31" s="48"/>
+      <c r="H31" s="48"/>
+      <c r="J31" s="0"/>
+      <c r="K31" s="0"/>
+    </row>
+    <row r="32" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="48"/>
+      <c r="B32" s="48"/>
+      <c r="C32" s="48"/>
+      <c r="D32" s="48"/>
+      <c r="E32" s="48"/>
+      <c r="F32" s="48"/>
+      <c r="G32" s="48"/>
+      <c r="H32" s="48"/>
+      <c r="J32" s="0"/>
+      <c r="K32" s="0"/>
+    </row>
+    <row r="33" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="48"/>
+      <c r="B33" s="48"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="48"/>
+      <c r="E33" s="48"/>
+      <c r="F33" s="48"/>
+      <c r="G33" s="48"/>
+      <c r="H33" s="48"/>
+      <c r="J33" s="0"/>
+      <c r="K33" s="0"/>
+    </row>
+    <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="48"/>
+      <c r="B34" s="48"/>
+      <c r="C34" s="48"/>
+      <c r="D34" s="48"/>
+      <c r="E34" s="48"/>
+      <c r="F34" s="48"/>
+      <c r="G34" s="48"/>
+      <c r="H34" s="48"/>
+      <c r="J34" s="0"/>
+      <c r="K34" s="0"/>
+    </row>
+    <row r="35" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="48"/>
+      <c r="B35" s="48"/>
+      <c r="C35" s="48"/>
+      <c r="D35" s="48"/>
+      <c r="E35" s="48"/>
+      <c r="F35" s="48"/>
+      <c r="G35" s="48"/>
+      <c r="H35" s="48"/>
+      <c r="J35" s="0"/>
+      <c r="K35" s="0"/>
+    </row>
+    <row r="36" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="48"/>
+      <c r="B36" s="48"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="48"/>
+      <c r="H36" s="48"/>
+      <c r="J36" s="0"/>
+      <c r="K36" s="0"/>
+    </row>
+    <row r="37" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="48"/>
+      <c r="B37" s="48"/>
+      <c r="C37" s="48"/>
+      <c r="D37" s="48"/>
+      <c r="E37" s="48"/>
+      <c r="F37" s="48"/>
+      <c r="G37" s="48"/>
+      <c r="H37" s="48"/>
+      <c r="J37" s="0"/>
+      <c r="K37" s="0"/>
+    </row>
+    <row r="38" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="48"/>
+      <c r="B38" s="48"/>
+      <c r="C38" s="48"/>
+      <c r="D38" s="48"/>
+      <c r="E38" s="48"/>
+      <c r="F38" s="48"/>
+      <c r="G38" s="48"/>
+      <c r="H38" s="48"/>
+      <c r="J38" s="0"/>
+      <c r="K38" s="0"/>
+    </row>
+    <row r="39" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="48"/>
+      <c r="B39" s="48"/>
+      <c r="C39" s="48"/>
+      <c r="D39" s="48"/>
+      <c r="E39" s="48"/>
+      <c r="F39" s="48"/>
+      <c r="G39" s="48"/>
+      <c r="H39" s="48"/>
+      <c r="J39" s="0"/>
+      <c r="K39" s="0"/>
+    </row>
+    <row r="40" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="48"/>
+      <c r="B40" s="48"/>
+      <c r="C40" s="48"/>
+      <c r="D40" s="48"/>
+      <c r="E40" s="48"/>
+      <c r="F40" s="48"/>
+      <c r="G40" s="48"/>
+      <c r="H40" s="48"/>
+      <c r="J40" s="0"/>
+      <c r="K40" s="0"/>
+    </row>
+    <row r="41" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="48"/>
+      <c r="B41" s="48"/>
+      <c r="C41" s="48"/>
+      <c r="D41" s="48"/>
+      <c r="E41" s="48"/>
+      <c r="F41" s="48"/>
+      <c r="G41" s="48"/>
+      <c r="H41" s="48"/>
+      <c r="J41" s="0"/>
+      <c r="K41" s="0"/>
+    </row>
+    <row r="42" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="48"/>
+      <c r="B42" s="48"/>
+      <c r="C42" s="48"/>
+      <c r="D42" s="48"/>
+      <c r="E42" s="48"/>
+      <c r="F42" s="48"/>
+      <c r="G42" s="48"/>
+      <c r="H42" s="48"/>
+      <c r="J42" s="0"/>
+      <c r="K42" s="0"/>
+    </row>
+    <row r="43" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="48"/>
+      <c r="B43" s="48"/>
+      <c r="C43" s="48"/>
+      <c r="D43" s="48"/>
+      <c r="E43" s="48"/>
+      <c r="F43" s="48"/>
+      <c r="G43" s="48"/>
+      <c r="H43" s="48"/>
+      <c r="J43" s="0"/>
+      <c r="K43" s="0"/>
+    </row>
+    <row r="44" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="48"/>
+      <c r="B44" s="48"/>
+      <c r="C44" s="48"/>
+      <c r="D44" s="48"/>
+      <c r="E44" s="48"/>
+      <c r="F44" s="48"/>
+      <c r="G44" s="48"/>
+      <c r="H44" s="48"/>
+      <c r="J44" s="0"/>
+      <c r="K44" s="0"/>
+    </row>
+    <row r="45" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="48"/>
+      <c r="B45" s="48"/>
+      <c r="C45" s="48"/>
+      <c r="D45" s="48"/>
+      <c r="E45" s="48"/>
+      <c r="F45" s="48"/>
+      <c r="G45" s="48"/>
+      <c r="H45" s="48"/>
+      <c r="J45" s="0"/>
+      <c r="K45" s="0"/>
+    </row>
+    <row r="46" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="48"/>
+      <c r="B46" s="48"/>
+      <c r="C46" s="48"/>
+      <c r="D46" s="48"/>
+      <c r="E46" s="48"/>
+      <c r="F46" s="48"/>
+      <c r="G46" s="48"/>
+      <c r="H46" s="48"/>
+      <c r="J46" s="0"/>
+      <c r="K46" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3991,79 +4290,79 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="62" t="s">
+      <c r="B1" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="62" t="s">
+      <c r="C1" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="62" t="s">
+      <c r="D1" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="62" t="s">
+      <c r="E1" s="65" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="179.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="63"/>
-      <c r="B2" s="64" t="s">
-        <v>101</v>
-      </c>
-      <c r="C2" s="65" t="s">
-        <v>102</v>
-      </c>
-      <c r="D2" s="65" t="s">
+      <c r="A2" s="66"/>
+      <c r="B2" s="67" t="s">
+        <v>111</v>
+      </c>
+      <c r="C2" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="D2" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="65" t="s">
-        <v>103</v>
+      <c r="E2" s="68" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="101.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="66"/>
-      <c r="B3" s="66" t="s">
-        <v>104</v>
-      </c>
-      <c r="C3" s="66" t="s">
-        <v>105</v>
-      </c>
-      <c r="D3" s="67" t="s">
-        <v>103</v>
-      </c>
-      <c r="E3" s="67" t="s">
-        <v>106</v>
+      <c r="A3" s="69"/>
+      <c r="B3" s="69" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" s="69" t="s">
+        <v>115</v>
+      </c>
+      <c r="D3" s="70" t="s">
+        <v>113</v>
+      </c>
+      <c r="E3" s="70" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="86.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="68"/>
-      <c r="B4" s="68" t="s">
-        <v>107</v>
-      </c>
-      <c r="C4" s="68" t="s">
-        <v>108</v>
-      </c>
-      <c r="D4" s="69" t="s">
-        <v>106</v>
-      </c>
-      <c r="E4" s="69" t="s">
-        <v>109</v>
+      <c r="A4" s="71"/>
+      <c r="B4" s="71" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" s="71" t="s">
+        <v>118</v>
+      </c>
+      <c r="D4" s="72" t="s">
+        <v>116</v>
+      </c>
+      <c r="E4" s="72" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="89.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="68"/>
-      <c r="B5" s="68" t="s">
-        <v>110</v>
-      </c>
-      <c r="C5" s="69" t="s">
-        <v>111</v>
-      </c>
-      <c r="D5" s="69" t="s">
-        <v>109</v>
-      </c>
-      <c r="E5" s="68"/>
+      <c r="A5" s="71"/>
+      <c r="B5" s="71" t="s">
+        <v>120</v>
+      </c>
+      <c r="C5" s="72" t="s">
+        <v>121</v>
+      </c>
+      <c r="D5" s="72" t="s">
+        <v>119</v>
+      </c>
+      <c r="E5" s="71"/>
     </row>
     <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -4090,21 +4389,21 @@
   <sheetFormatPr defaultColWidth="10.18359375" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="70" width="92.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="71" width="56.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="70" width="61.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="70" width="68.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="73" width="92.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="74" width="56.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="73" width="61.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="73" width="68.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="59.58"/>
   </cols>
   <sheetData>
-    <row r="1" s="75" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="78" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="72" t="s">
+      <c r="C1" s="75" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
@@ -4113,119 +4412,119 @@
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="73" t="s">
-        <v>112</v>
-      </c>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
+      <c r="F1" s="76" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6"/>
       <c r="B2" s="10" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="76"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
     </row>
     <row r="3" customFormat="false" ht="201.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6"/>
       <c r="B3" s="10" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="F3" s="78"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
+        <v>127</v>
+      </c>
+      <c r="F3" s="81"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
     </row>
     <row r="4" customFormat="false" ht="76.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6"/>
       <c r="B4" s="10" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="78"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="80"/>
     </row>
     <row r="5" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6"/>
       <c r="B5" s="10" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="78"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
+      <c r="F5" s="81"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="80"/>
     </row>
     <row r="6" s="2" customFormat="true" ht="73.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="7" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>20</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="F6" s="78"/>
-      <c r="G6" s="77"/>
-      <c r="H6" s="77"/>
+        <v>131</v>
+      </c>
+      <c r="F6" s="81"/>
+      <c r="G6" s="80"/>
+      <c r="H6" s="80"/>
     </row>
     <row r="7" s="2" customFormat="true" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
         <v>22</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="F7" s="76"/>
+        <v>133</v>
+      </c>
+      <c r="F7" s="79"/>
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
     </row>
@@ -4234,128 +4533,128 @@
         <v>27</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>29</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="F8" s="76"/>
-      <c r="G8" s="77"/>
-      <c r="H8" s="77"/>
+        <v>135</v>
+      </c>
+      <c r="F8" s="79"/>
+      <c r="G8" s="80"/>
+      <c r="H8" s="80"/>
     </row>
     <row r="9" s="2" customFormat="true" ht="241.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
         <v>27</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="F9" s="76"/>
-      <c r="G9" s="77"/>
-      <c r="H9" s="77"/>
+        <v>137</v>
+      </c>
+      <c r="F9" s="79"/>
+      <c r="G9" s="80"/>
+      <c r="H9" s="80"/>
     </row>
     <row r="10" s="2" customFormat="true" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="79" t="s">
-        <v>128</v>
+      <c r="B10" s="82" t="s">
+        <v>138</v>
       </c>
       <c r="C10" s="33" t="s">
         <v>35</v>
       </c>
       <c r="D10" s="33" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>129</v>
-      </c>
-      <c r="F10" s="80"/>
-      <c r="G10" s="77"/>
-      <c r="H10" s="77"/>
-    </row>
-    <row r="11" s="82" customFormat="true" ht="225.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>139</v>
+      </c>
+      <c r="F10" s="83"/>
+      <c r="G10" s="80"/>
+      <c r="H10" s="80"/>
+    </row>
+    <row r="11" s="85" customFormat="true" ht="225.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
         <v>33</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="F11" s="81"/>
-      <c r="G11" s="77"/>
-      <c r="H11" s="77"/>
+        <v>141</v>
+      </c>
+      <c r="F11" s="84"/>
+      <c r="G11" s="80"/>
+      <c r="H11" s="80"/>
     </row>
     <row r="12" customFormat="false" ht="176.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
         <v>33</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>40</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="E12" s="15"/>
       <c r="F12" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="G12" s="77"/>
-      <c r="H12" s="77"/>
+        <v>144</v>
+      </c>
+      <c r="G12" s="80"/>
+      <c r="H12" s="80"/>
     </row>
     <row r="13" customFormat="false" ht="211.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
         <v>33</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>44</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="E13" s="15"/>
       <c r="F13" s="23"/>
-      <c r="G13" s="77"/>
-      <c r="H13" s="77"/>
+      <c r="G13" s="80"/>
+      <c r="H13" s="80"/>
     </row>
     <row r="14" customFormat="false" ht="211.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="83"/>
-      <c r="B14" s="84"/>
-      <c r="C14" s="84"/>
-      <c r="D14" s="84"/>
-      <c r="E14" s="84"/>
+      <c r="A14" s="86"/>
+      <c r="B14" s="87"/>
+      <c r="C14" s="87"/>
+      <c r="D14" s="87"/>
+      <c r="E14" s="87"/>
       <c r="F14" s="28"/>
-      <c r="G14" s="77"/>
-      <c r="H14" s="77"/>
+      <c r="G14" s="80"/>
+      <c r="H14" s="80"/>
     </row>
     <row r="15" customFormat="false" ht="211.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="29"/>
@@ -4364,87 +4663,87 @@
       <c r="D15" s="30"/>
       <c r="E15" s="30"/>
       <c r="F15" s="31"/>
-      <c r="G15" s="77"/>
-      <c r="H15" s="77"/>
+      <c r="G15" s="80"/>
+      <c r="H15" s="80"/>
     </row>
     <row r="16" customFormat="false" ht="159.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="32" t="s">
         <v>46</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="C16" s="33" t="s">
         <v>29</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="F16" s="34"/>
-      <c r="G16" s="82"/>
-      <c r="H16" s="82"/>
+      <c r="G16" s="85"/>
+      <c r="H16" s="85"/>
     </row>
     <row r="17" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="35" t="s">
         <v>46</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="C17" s="11" t="s">
         <v>24</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="F17" s="36"/>
     </row>
     <row r="18" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="42" t="s">
+      <c r="A18" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="B18" s="43" t="s">
-        <v>142</v>
-      </c>
-      <c r="C18" s="43" t="s">
+      <c r="B18" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="C18" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="43" t="s">
-        <v>143</v>
-      </c>
-      <c r="E18" s="43"/>
-      <c r="F18" s="39" t="s">
-        <v>144</v>
+      <c r="D18" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="E18" s="15"/>
+      <c r="F18" s="23" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="83" t="s">
+      <c r="A19" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="84" t="s">
-        <v>145</v>
-      </c>
-      <c r="C19" s="84" t="s">
+      <c r="B19" s="89" t="s">
+        <v>155</v>
+      </c>
+      <c r="C19" s="89" t="s">
         <v>44</v>
       </c>
-      <c r="D19" s="84" t="s">
-        <v>146</v>
-      </c>
-      <c r="E19" s="84"/>
-      <c r="F19" s="28"/>
+      <c r="D19" s="89" t="s">
+        <v>156</v>
+      </c>
+      <c r="E19" s="89"/>
+      <c r="F19" s="41"/>
     </row>
     <row r="20" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="83"/>
-      <c r="B20" s="84"/>
-      <c r="C20" s="84"/>
-      <c r="D20" s="84"/>
-      <c r="E20" s="84"/>
+      <c r="A20" s="86"/>
+      <c r="B20" s="87"/>
+      <c r="C20" s="87"/>
+      <c r="D20" s="87"/>
+      <c r="E20" s="87"/>
       <c r="F20" s="28"/>
     </row>
     <row r="21" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4459,89 +4758,89 @@
       <c r="A22" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="79" t="s">
-        <v>147</v>
+      <c r="B22" s="82" t="s">
+        <v>157</v>
       </c>
       <c r="C22" s="33" t="s">
         <v>35</v>
       </c>
       <c r="D22" s="33" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>148</v>
-      </c>
-      <c r="F22" s="80"/>
-      <c r="G22" s="77"/>
-      <c r="H22" s="77"/>
+        <v>158</v>
+      </c>
+      <c r="F22" s="83"/>
+      <c r="G22" s="80"/>
+      <c r="H22" s="80"/>
     </row>
     <row r="23" customFormat="false" ht="210.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="21" t="s">
         <v>57</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="C23" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="F23" s="81"/>
-      <c r="G23" s="77"/>
-      <c r="H23" s="77"/>
+        <v>160</v>
+      </c>
+      <c r="F23" s="84"/>
+      <c r="G23" s="80"/>
+      <c r="H23" s="80"/>
     </row>
     <row r="24" customFormat="false" ht="177.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="42" t="s">
+      <c r="A24" s="88" t="s">
         <v>57</v>
       </c>
-      <c r="B24" s="43" t="s">
-        <v>151</v>
-      </c>
-      <c r="C24" s="43" t="s">
+      <c r="B24" s="89" t="s">
+        <v>161</v>
+      </c>
+      <c r="C24" s="89" t="s">
         <v>40</v>
       </c>
-      <c r="D24" s="43" t="s">
-        <v>152</v>
-      </c>
-      <c r="E24" s="43"/>
-      <c r="F24" s="39" t="s">
-        <v>153</v>
-      </c>
-      <c r="G24" s="77"/>
-      <c r="H24" s="77"/>
+      <c r="D24" s="89" t="s">
+        <v>162</v>
+      </c>
+      <c r="E24" s="89"/>
+      <c r="F24" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="G24" s="80"/>
+      <c r="H24" s="80"/>
     </row>
     <row r="25" customFormat="false" ht="202.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="83" t="s">
+      <c r="A25" s="86" t="s">
         <v>57</v>
       </c>
-      <c r="B25" s="84" t="s">
-        <v>154</v>
-      </c>
-      <c r="C25" s="84" t="s">
+      <c r="B25" s="87" t="s">
+        <v>164</v>
+      </c>
+      <c r="C25" s="87" t="s">
         <v>44</v>
       </c>
-      <c r="D25" s="84" t="s">
-        <v>155</v>
-      </c>
-      <c r="E25" s="84"/>
+      <c r="D25" s="87" t="s">
+        <v>165</v>
+      </c>
+      <c r="E25" s="87"/>
       <c r="F25" s="28"/>
-      <c r="G25" s="77"/>
-      <c r="H25" s="77"/>
+      <c r="G25" s="80"/>
+      <c r="H25" s="80"/>
     </row>
     <row r="26" customFormat="false" ht="202.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="83"/>
-      <c r="B26" s="84"/>
-      <c r="C26" s="84"/>
-      <c r="D26" s="84"/>
-      <c r="E26" s="84"/>
+      <c r="A26" s="86"/>
+      <c r="B26" s="87"/>
+      <c r="C26" s="87"/>
+      <c r="D26" s="87"/>
+      <c r="E26" s="87"/>
       <c r="F26" s="28"/>
-      <c r="G26" s="77"/>
-      <c r="H26" s="77"/>
+      <c r="G26" s="80"/>
+      <c r="H26" s="80"/>
     </row>
     <row r="27" customFormat="false" ht="202.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="29"/>
@@ -4550,174 +4849,174 @@
       <c r="D27" s="30"/>
       <c r="E27" s="30"/>
       <c r="F27" s="31"/>
-      <c r="G27" s="77"/>
-      <c r="H27" s="77"/>
+      <c r="G27" s="80"/>
+      <c r="H27" s="80"/>
     </row>
     <row r="28" customFormat="false" ht="156.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="32" t="s">
         <v>68</v>
       </c>
       <c r="B28" s="33" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="C28" s="33" t="s">
         <v>29</v>
       </c>
       <c r="D28" s="33" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="E28" s="33" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="F28" s="34"/>
-      <c r="G28" s="77"/>
-      <c r="H28" s="77"/>
+      <c r="G28" s="80"/>
+      <c r="H28" s="80"/>
     </row>
     <row r="29" customFormat="false" ht="248.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="35" t="s">
         <v>68</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="C29" s="11" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="F29" s="36"/>
-      <c r="G29" s="77"/>
-      <c r="H29" s="77"/>
+      <c r="G29" s="80"/>
+      <c r="H29" s="80"/>
     </row>
     <row r="30" customFormat="false" ht="100.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="42" t="s">
+      <c r="A30" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="B30" s="43" t="s">
-        <v>161</v>
-      </c>
-      <c r="C30" s="43" t="s">
+      <c r="B30" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="C30" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D30" s="43" t="s">
-        <v>162</v>
-      </c>
-      <c r="E30" s="43"/>
-      <c r="F30" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="G30" s="77"/>
-      <c r="H30" s="77"/>
+      <c r="D30" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="E30" s="15"/>
+      <c r="F30" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="G30" s="80"/>
+      <c r="H30" s="80"/>
     </row>
     <row r="31" customFormat="false" ht="108.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="83" t="s">
+      <c r="A31" s="88" t="s">
         <v>68</v>
       </c>
-      <c r="B31" s="84" t="s">
-        <v>164</v>
-      </c>
-      <c r="C31" s="84" t="s">
+      <c r="B31" s="89" t="s">
+        <v>174</v>
+      </c>
+      <c r="C31" s="89" t="s">
         <v>44</v>
       </c>
-      <c r="D31" s="84" t="s">
-        <v>165</v>
-      </c>
-      <c r="E31" s="84"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="77"/>
-      <c r="H31" s="77"/>
+      <c r="D31" s="89" t="s">
+        <v>175</v>
+      </c>
+      <c r="E31" s="89"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="80"/>
+      <c r="H31" s="80"/>
     </row>
     <row r="32" customFormat="false" ht="108.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="83"/>
-      <c r="B32" s="84"/>
-      <c r="C32" s="84"/>
-      <c r="D32" s="84"/>
-      <c r="E32" s="84"/>
+      <c r="A32" s="86"/>
+      <c r="B32" s="87"/>
+      <c r="C32" s="87"/>
+      <c r="D32" s="87"/>
+      <c r="E32" s="87"/>
       <c r="F32" s="28"/>
-      <c r="G32" s="77"/>
-      <c r="H32" s="77"/>
+      <c r="G32" s="80"/>
+      <c r="H32" s="80"/>
     </row>
     <row r="33" customFormat="false" ht="130.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="29"/>
-      <c r="B33" s="85"/>
+      <c r="B33" s="90"/>
       <c r="C33" s="30"/>
-      <c r="D33" s="85"/>
-      <c r="E33" s="85"/>
-      <c r="F33" s="86"/>
-      <c r="G33" s="77"/>
-      <c r="H33" s="77"/>
+      <c r="D33" s="90"/>
+      <c r="E33" s="90"/>
+      <c r="F33" s="91"/>
+      <c r="G33" s="80"/>
+      <c r="H33" s="80"/>
     </row>
     <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G34" s="77"/>
-      <c r="H34" s="77"/>
+      <c r="G34" s="80"/>
+      <c r="H34" s="80"/>
     </row>
     <row r="35" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G35" s="77"/>
-      <c r="H35" s="77"/>
+      <c r="G35" s="80"/>
+      <c r="H35" s="80"/>
     </row>
     <row r="36" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G36" s="77"/>
-      <c r="H36" s="77"/>
+      <c r="G36" s="80"/>
+      <c r="H36" s="80"/>
     </row>
     <row r="37" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G37" s="77"/>
-      <c r="H37" s="77"/>
+      <c r="G37" s="80"/>
+      <c r="H37" s="80"/>
     </row>
     <row r="38" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G38" s="77"/>
-      <c r="H38" s="77"/>
+      <c r="G38" s="80"/>
+      <c r="H38" s="80"/>
     </row>
     <row r="39" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G39" s="77"/>
-      <c r="H39" s="77"/>
+      <c r="G39" s="80"/>
+      <c r="H39" s="80"/>
     </row>
     <row r="40" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G40" s="77"/>
-      <c r="H40" s="77"/>
+      <c r="G40" s="80"/>
+      <c r="H40" s="80"/>
     </row>
     <row r="41" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G41" s="77"/>
-      <c r="H41" s="77"/>
+      <c r="G41" s="80"/>
+      <c r="H41" s="80"/>
     </row>
     <row r="42" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G42" s="77"/>
-      <c r="H42" s="77"/>
+      <c r="G42" s="80"/>
+      <c r="H42" s="80"/>
     </row>
     <row r="43" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G43" s="77"/>
-      <c r="H43" s="77"/>
+      <c r="G43" s="80"/>
+      <c r="H43" s="80"/>
     </row>
     <row r="44" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G44" s="77"/>
-      <c r="H44" s="77"/>
+      <c r="G44" s="80"/>
+      <c r="H44" s="80"/>
     </row>
     <row r="45" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G45" s="77"/>
-      <c r="H45" s="77"/>
+      <c r="G45" s="80"/>
+      <c r="H45" s="80"/>
     </row>
     <row r="46" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G46" s="77"/>
-      <c r="H46" s="77"/>
+      <c r="G46" s="80"/>
+      <c r="H46" s="80"/>
     </row>
     <row r="47" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G47" s="77"/>
-      <c r="H47" s="77"/>
+      <c r="G47" s="80"/>
+      <c r="H47" s="80"/>
     </row>
     <row r="48" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G48" s="77"/>
-      <c r="H48" s="77"/>
+      <c r="G48" s="80"/>
+      <c r="H48" s="80"/>
     </row>
     <row r="49" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G49" s="77"/>
-      <c r="H49" s="77"/>
+      <c r="G49" s="80"/>
+      <c r="H49" s="80"/>
     </row>
     <row r="50" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G50" s="77"/>
-      <c r="H50" s="77"/>
+      <c r="G50" s="80"/>
+      <c r="H50" s="80"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4749,531 +5048,531 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="11" style="3" width="10.16"/>
   </cols>
   <sheetData>
-    <row r="1" s="90" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="44" t="s">
+    <row r="1" s="95" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="42" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="45" t="s">
+      <c r="B1" s="43" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="45" t="s">
-        <v>166</v>
-      </c>
-      <c r="D1" s="45" t="s">
+      <c r="C1" s="43" t="s">
+        <v>176</v>
+      </c>
+      <c r="D1" s="43" t="s">
         <v>82</v>
       </c>
-      <c r="E1" s="87" t="s">
-        <v>167</v>
-      </c>
-      <c r="F1" s="87" t="s">
+      <c r="E1" s="92" t="s">
+        <v>177</v>
+      </c>
+      <c r="F1" s="92" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="88" t="s">
+      <c r="G1" s="93" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="88" t="s">
+      <c r="H1" s="93" t="s">
         <v>57</v>
       </c>
-      <c r="I1" s="88" t="s">
+      <c r="I1" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="J1" s="88" t="s">
+      <c r="J1" s="93" t="s">
         <v>68</v>
       </c>
-      <c r="K1" s="89"/>
+      <c r="K1" s="94"/>
       <c r="XFD1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="91" t="s">
+      <c r="A2" s="96" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="92" t="n">
+      <c r="B2" s="97" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="92" t="n">
+      <c r="C2" s="97" t="n">
         <v>2273097</v>
       </c>
-      <c r="D2" s="93" t="n">
+      <c r="D2" s="98" t="n">
         <v>2095051</v>
       </c>
-      <c r="E2" s="50" t="n">
+      <c r="E2" s="48" t="n">
         <v>1676040</v>
       </c>
-      <c r="F2" s="54" t="n">
+      <c r="F2" s="52" t="n">
         <v>1661804</v>
       </c>
-      <c r="G2" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H2" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I2" s="50" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J2" s="52" t="n">
+      <c r="G2" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H2" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I2" s="48" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J2" s="50" t="n">
         <v>10000</v>
       </c>
       <c r="L2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="91" t="s">
-        <v>168</v>
-      </c>
-      <c r="B3" s="92" t="n">
+      <c r="A3" s="96" t="s">
+        <v>178</v>
+      </c>
+      <c r="B3" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="92" t="n">
+      <c r="C3" s="97" t="n">
         <v>231073</v>
       </c>
-      <c r="D3" s="93" t="n">
+      <c r="D3" s="98" t="n">
         <v>172846</v>
       </c>
-      <c r="E3" s="50" t="n">
+      <c r="E3" s="48" t="n">
         <v>138277</v>
       </c>
-      <c r="F3" s="54" t="n">
+      <c r="F3" s="52" t="n">
         <v>135226</v>
       </c>
-      <c r="G3" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H3" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I3" s="50" t="n">
+      <c r="G3" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H3" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I3" s="48" t="n">
         <v>9656</v>
       </c>
-      <c r="J3" s="52" t="n">
+      <c r="J3" s="50" t="n">
         <v>9968</v>
       </c>
       <c r="L3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="91" t="s">
-        <v>169</v>
-      </c>
-      <c r="B4" s="92" t="n">
+      <c r="A4" s="96" t="s">
+        <v>179</v>
+      </c>
+      <c r="B4" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="92" t="n">
+      <c r="C4" s="97" t="n">
         <v>128027</v>
       </c>
-      <c r="D4" s="93" t="n">
+      <c r="D4" s="98" t="n">
         <v>128014</v>
       </c>
-      <c r="E4" s="50" t="n">
+      <c r="E4" s="48" t="n">
         <v>102411</v>
       </c>
-      <c r="F4" s="54" t="n">
+      <c r="F4" s="52" t="n">
         <v>101341</v>
       </c>
-      <c r="G4" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H4" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I4" s="50" t="n">
+      <c r="G4" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H4" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I4" s="48" t="n">
         <v>9765</v>
       </c>
-      <c r="J4" s="52" t="n">
+      <c r="J4" s="50" t="n">
         <v>9995</v>
       </c>
       <c r="L4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="91" t="s">
-        <v>170</v>
-      </c>
-      <c r="B5" s="92" t="n">
+      <c r="A5" s="96" t="s">
+        <v>180</v>
+      </c>
+      <c r="B5" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="92" t="n">
+      <c r="C5" s="97" t="n">
         <v>158930</v>
       </c>
-      <c r="D5" s="93" t="n">
+      <c r="D5" s="98" t="n">
         <v>90694</v>
       </c>
-      <c r="E5" s="50" t="n">
+      <c r="E5" s="48" t="n">
         <v>72555</v>
       </c>
-      <c r="F5" s="54" t="n">
+      <c r="F5" s="52" t="n">
         <v>66678</v>
       </c>
-      <c r="G5" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H5" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I5" s="50" t="n">
+      <c r="G5" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H5" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I5" s="48" t="n">
         <v>9712</v>
       </c>
-      <c r="J5" s="52" t="n">
+      <c r="J5" s="50" t="n">
         <v>9960</v>
       </c>
       <c r="L5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="91" t="s">
-        <v>171</v>
-      </c>
-      <c r="B6" s="92" t="n">
+      <c r="A6" s="96" t="s">
+        <v>181</v>
+      </c>
+      <c r="B6" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="92" t="n">
+      <c r="C6" s="97" t="n">
         <v>10293</v>
       </c>
-      <c r="D6" s="93" t="n">
+      <c r="D6" s="98" t="n">
         <v>10286</v>
       </c>
-      <c r="E6" s="50" t="n">
+      <c r="E6" s="48" t="n">
         <v>8229</v>
       </c>
-      <c r="F6" s="54" t="n">
+      <c r="F6" s="52" t="n">
         <v>7672</v>
       </c>
-      <c r="G6" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H6" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I6" s="50" t="n">
+      <c r="G6" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H6" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I6" s="48" t="n">
         <v>9913</v>
       </c>
-      <c r="J6" s="52" t="n">
+      <c r="J6" s="50" t="n">
         <v>9958</v>
       </c>
       <c r="L6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="91" t="s">
-        <v>172</v>
-      </c>
-      <c r="B7" s="92" t="n">
+      <c r="A7" s="96" t="s">
+        <v>182</v>
+      </c>
+      <c r="B7" s="97" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="92" t="n">
+      <c r="C7" s="97" t="n">
         <v>7938</v>
       </c>
-      <c r="D7" s="93" t="n">
+      <c r="D7" s="98" t="n">
         <v>5931</v>
       </c>
-      <c r="E7" s="50" t="n">
+      <c r="E7" s="48" t="n">
         <v>4745</v>
       </c>
-      <c r="F7" s="54" t="n">
+      <c r="F7" s="52" t="n">
         <v>4648</v>
       </c>
-      <c r="G7" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H7" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I7" s="50" t="n">
+      <c r="G7" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H7" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I7" s="48" t="n">
         <v>9908</v>
       </c>
-      <c r="J7" s="52" t="n">
+      <c r="J7" s="50" t="n">
         <v>9923</v>
       </c>
       <c r="L7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="91" t="s">
-        <v>173</v>
-      </c>
-      <c r="B8" s="92" t="n">
+      <c r="A8" s="96" t="s">
+        <v>183</v>
+      </c>
+      <c r="B8" s="97" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="92" t="n">
+      <c r="C8" s="97" t="n">
         <v>5796</v>
       </c>
-      <c r="D8" s="93" t="n">
+      <c r="D8" s="98" t="n">
         <v>5385</v>
       </c>
-      <c r="E8" s="50" t="n">
+      <c r="E8" s="48" t="n">
         <v>4308</v>
       </c>
-      <c r="F8" s="54" t="n">
+      <c r="F8" s="52" t="n">
         <v>4034</v>
       </c>
-      <c r="G8" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H8" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I8" s="50" t="n">
+      <c r="G8" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H8" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I8" s="48" t="n">
         <v>9637</v>
       </c>
-      <c r="J8" s="52" t="n">
+      <c r="J8" s="50" t="n">
         <v>9785</v>
       </c>
       <c r="L8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="91" t="s">
-        <v>174</v>
-      </c>
-      <c r="B9" s="92" t="n">
+      <c r="A9" s="96" t="s">
+        <v>184</v>
+      </c>
+      <c r="B9" s="97" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="92" t="n">
+      <c r="C9" s="97" t="n">
         <v>5499</v>
       </c>
-      <c r="D9" s="93" t="n">
+      <c r="D9" s="98" t="n">
         <v>5228</v>
       </c>
-      <c r="E9" s="50" t="n">
+      <c r="E9" s="48" t="n">
         <v>4182</v>
       </c>
-      <c r="F9" s="54" t="n">
+      <c r="F9" s="52" t="n">
         <v>3921</v>
       </c>
-      <c r="G9" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H9" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I9" s="50" t="n">
+      <c r="G9" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H9" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I9" s="48" t="n">
         <v>9814</v>
       </c>
-      <c r="J9" s="52" t="n">
+      <c r="J9" s="50" t="n">
         <v>9872</v>
       </c>
       <c r="L9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="91" t="s">
-        <v>175</v>
-      </c>
-      <c r="B10" s="92" t="n">
+      <c r="A10" s="96" t="s">
+        <v>185</v>
+      </c>
+      <c r="B10" s="97" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="92" t="n">
+      <c r="C10" s="97" t="n">
         <v>5897</v>
       </c>
-      <c r="D10" s="93" t="n">
+      <c r="D10" s="98" t="n">
         <v>3219</v>
       </c>
-      <c r="E10" s="50" t="n">
+      <c r="E10" s="48" t="n">
         <v>2575</v>
       </c>
-      <c r="F10" s="54" t="n">
+      <c r="F10" s="52" t="n">
         <v>2369</v>
       </c>
-      <c r="G10" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H10" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I10" s="50" t="n">
+      <c r="G10" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H10" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I10" s="48" t="n">
         <v>9622</v>
       </c>
-      <c r="J10" s="52" t="n">
+      <c r="J10" s="50" t="n">
         <v>9637</v>
       </c>
       <c r="L10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="91" t="s">
+      <c r="A11" s="96" t="s">
         <v>89</v>
       </c>
-      <c r="B11" s="92" t="n">
+      <c r="B11" s="97" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="92" t="n">
+      <c r="C11" s="97" t="n">
         <v>1966</v>
       </c>
-      <c r="D11" s="93" t="n">
+      <c r="D11" s="98" t="n">
         <v>1948</v>
       </c>
-      <c r="E11" s="50" t="n">
+      <c r="E11" s="48" t="n">
         <v>1558</v>
       </c>
-      <c r="F11" s="54" t="n">
+      <c r="F11" s="52" t="n">
         <v>717</v>
       </c>
-      <c r="G11" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H11" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I11" s="50" t="n">
+      <c r="G11" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H11" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I11" s="48" t="n">
         <v>9832</v>
       </c>
-      <c r="J11" s="52" t="n">
+      <c r="J11" s="50" t="n">
         <v>9979</v>
       </c>
       <c r="L11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="91" t="s">
-        <v>176</v>
-      </c>
-      <c r="B12" s="92" t="n">
+      <c r="A12" s="96" t="s">
+        <v>186</v>
+      </c>
+      <c r="B12" s="97" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="92" t="n">
+      <c r="C12" s="97" t="n">
         <v>1507</v>
       </c>
-      <c r="D12" s="93" t="n">
+      <c r="D12" s="98" t="n">
         <v>1470</v>
       </c>
-      <c r="E12" s="50" t="n">
+      <c r="E12" s="48" t="n">
         <v>1176</v>
       </c>
-      <c r="F12" s="54" t="n">
+      <c r="F12" s="52" t="n">
         <v>469</v>
       </c>
-      <c r="G12" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H12" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I12" s="50" t="n">
+      <c r="G12" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H12" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I12" s="48" t="n">
         <v>5782</v>
       </c>
-      <c r="J12" s="52" t="n">
+      <c r="J12" s="50" t="n">
         <v>5793</v>
       </c>
       <c r="L12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="91" t="s">
-        <v>177</v>
-      </c>
-      <c r="B13" s="92" t="n">
+      <c r="A13" s="96" t="s">
+        <v>187</v>
+      </c>
+      <c r="B13" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="92" t="n">
+      <c r="C13" s="97" t="n">
         <v>652</v>
       </c>
-      <c r="D13" s="93" t="n">
+      <c r="D13" s="98" t="n">
         <v>652</v>
       </c>
-      <c r="E13" s="50" t="n">
+      <c r="E13" s="48" t="n">
         <v>522</v>
       </c>
-      <c r="F13" s="54" t="n">
+      <c r="F13" s="52" t="n">
         <v>47</v>
       </c>
-      <c r="G13" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H13" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I13" s="50" t="n">
+      <c r="G13" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H13" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I13" s="48" t="n">
         <v>5862</v>
       </c>
-      <c r="J13" s="52" t="n">
+      <c r="J13" s="50" t="n">
         <v>5871</v>
       </c>
       <c r="L13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="91" t="s">
-        <v>178</v>
-      </c>
-      <c r="B14" s="92" t="n">
+      <c r="A14" s="96" t="s">
+        <v>188</v>
+      </c>
+      <c r="B14" s="97" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="92" t="n">
+      <c r="C14" s="97" t="n">
         <v>36</v>
       </c>
-      <c r="D14" s="93" t="n">
+      <c r="D14" s="98" t="n">
         <v>36</v>
       </c>
-      <c r="E14" s="50" t="n">
+      <c r="E14" s="48" t="n">
         <v>29</v>
       </c>
-      <c r="F14" s="51" t="n">
+      <c r="F14" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H14" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I14" s="50" t="n">
+      <c r="G14" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H14" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I14" s="48" t="n">
         <v>9904</v>
       </c>
-      <c r="J14" s="52" t="n">
+      <c r="J14" s="50" t="n">
         <v>9934</v>
       </c>
       <c r="L14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="91" t="s">
-        <v>179</v>
-      </c>
-      <c r="B15" s="92" t="n">
+      <c r="A15" s="96" t="s">
+        <v>189</v>
+      </c>
+      <c r="B15" s="97" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="92" t="n">
+      <c r="C15" s="97" t="n">
         <v>21</v>
       </c>
-      <c r="D15" s="93" t="n">
+      <c r="D15" s="98" t="n">
         <v>21</v>
       </c>
-      <c r="E15" s="50" t="n">
+      <c r="E15" s="48" t="n">
         <v>17</v>
       </c>
-      <c r="F15" s="51" t="n">
+      <c r="F15" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H15" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I15" s="50" t="n">
+      <c r="G15" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H15" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I15" s="48" t="n">
         <v>9725</v>
       </c>
-      <c r="J15" s="52" t="n">
+      <c r="J15" s="50" t="n">
         <v>9727</v>
       </c>
       <c r="L15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="94" t="s">
-        <v>180</v>
-      </c>
-      <c r="B16" s="95" t="n">
+      <c r="A16" s="99" t="s">
+        <v>190</v>
+      </c>
+      <c r="B16" s="100" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="95" t="n">
+      <c r="C16" s="100" t="n">
         <v>11</v>
       </c>
-      <c r="D16" s="95" t="n">
+      <c r="D16" s="100" t="n">
         <v>11</v>
       </c>
-      <c r="E16" s="57" t="n">
+      <c r="E16" s="55" t="n">
         <v>9</v>
       </c>
-      <c r="F16" s="57" t="n">
+      <c r="F16" s="55" t="n">
         <v>9</v>
       </c>
-      <c r="G16" s="57" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H16" s="57" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I16" s="57" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J16" s="60" t="n">
+      <c r="G16" s="55" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H16" s="55" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I16" s="55" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J16" s="58" t="n">
         <v>10000</v>
       </c>
       <c r="L16" s="2"/>
@@ -5314,23 +5613,23 @@
       <c r="L17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E18" s="61"/>
-      <c r="F18" s="49"/>
+      <c r="E18" s="59"/>
+      <c r="F18" s="47"/>
       <c r="L18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E19" s="61"/>
-      <c r="F19" s="49"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="47"/>
       <c r="L19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="89" t="s">
+      <c r="A20" s="94" t="s">
         <v>100</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>79</v>
       </c>
-      <c r="D20" s="50" t="n">
+      <c r="D20" s="48" t="n">
         <v>48</v>
       </c>
       <c r="E20" s="3" t="n">
@@ -5348,54 +5647,54 @@
       <c r="L20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="50"/>
+      <c r="B21" s="48"/>
       <c r="L21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="50"/>
+      <c r="B22" s="48"/>
       <c r="L22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="50"/>
+      <c r="B23" s="48"/>
       <c r="L23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="50"/>
+      <c r="B24" s="48"/>
       <c r="L24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="50"/>
+      <c r="B25" s="48"/>
       <c r="L25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="50"/>
+      <c r="B26" s="48"/>
     </row>
     <row r="27" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="50"/>
+      <c r="B27" s="48"/>
     </row>
     <row r="28" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="50"/>
+      <c r="B28" s="48"/>
     </row>
     <row r="29" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="50"/>
+      <c r="B29" s="48"/>
     </row>
     <row r="30" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="50"/>
+      <c r="B30" s="48"/>
     </row>
     <row r="31" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="50"/>
+      <c r="B31" s="48"/>
     </row>
     <row r="32" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="50"/>
+      <c r="B32" s="48"/>
     </row>
     <row r="33" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="50"/>
+      <c r="B33" s="48"/>
     </row>
     <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="50"/>
+      <c r="B34" s="48"/>
     </row>
     <row r="35" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="50"/>
+      <c r="B35" s="48"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -5416,87 +5715,87 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultColWidth="10.16796875" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="96" width="45.65"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="96" width="74.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="96" width="74.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="96" width="55.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="96" width="52.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="101" width="45.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="101" width="74.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="101" width="74.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="101" width="55.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="101" width="52.63"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="62" t="s">
+      <c r="B1" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="62" t="s">
+      <c r="C1" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="62" t="s">
+      <c r="D1" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="62" t="s">
+      <c r="E1" s="65" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="179.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="63"/>
-      <c r="B2" s="64" t="s">
-        <v>181</v>
-      </c>
-      <c r="C2" s="65" t="s">
-        <v>102</v>
-      </c>
-      <c r="D2" s="65" t="s">
-        <v>114</v>
-      </c>
-      <c r="E2" s="65" t="s">
-        <v>182</v>
+      <c r="A2" s="66"/>
+      <c r="B2" s="67" t="s">
+        <v>191</v>
+      </c>
+      <c r="C2" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="D2" s="68" t="s">
+        <v>124</v>
+      </c>
+      <c r="E2" s="68" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="131.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="64"/>
-      <c r="B3" s="64" t="s">
-        <v>183</v>
-      </c>
-      <c r="C3" s="64" t="s">
-        <v>105</v>
-      </c>
-      <c r="D3" s="65" t="s">
-        <v>182</v>
-      </c>
-      <c r="E3" s="65" t="s">
-        <v>184</v>
+      <c r="A3" s="67"/>
+      <c r="B3" s="67" t="s">
+        <v>193</v>
+      </c>
+      <c r="C3" s="67" t="s">
+        <v>115</v>
+      </c>
+      <c r="D3" s="68" t="s">
+        <v>192</v>
+      </c>
+      <c r="E3" s="68" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="141.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="64"/>
-      <c r="B4" s="64" t="s">
-        <v>185</v>
-      </c>
-      <c r="C4" s="64" t="s">
-        <v>108</v>
-      </c>
-      <c r="D4" s="65" t="s">
-        <v>184</v>
-      </c>
-      <c r="E4" s="65" t="s">
-        <v>186</v>
+      <c r="A4" s="67"/>
+      <c r="B4" s="67" t="s">
+        <v>195</v>
+      </c>
+      <c r="C4" s="67" t="s">
+        <v>118</v>
+      </c>
+      <c r="D4" s="68" t="s">
+        <v>194</v>
+      </c>
+      <c r="E4" s="68" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="176.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="64"/>
-      <c r="B5" s="64" t="s">
-        <v>187</v>
-      </c>
-      <c r="C5" s="65" t="s">
-        <v>111</v>
-      </c>
-      <c r="D5" s="65" t="s">
-        <v>186</v>
-      </c>
-      <c r="E5" s="64"/>
+      <c r="A5" s="67"/>
+      <c r="B5" s="67" t="s">
+        <v>197</v>
+      </c>
+      <c r="C5" s="68" t="s">
+        <v>121</v>
+      </c>
+      <c r="D5" s="68" t="s">
+        <v>196</v>
+      </c>
+      <c r="E5" s="67"/>
     </row>
     <row r="6" customFormat="false" ht="168.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
@@ -5518,139 +5817,139 @@
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultColWidth="10.16796875" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="96" width="45.65"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="96" width="74.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="96" width="74.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="96" width="55.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="96" width="52.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="101" width="45.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="101" width="74.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="101" width="74.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="101" width="55.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="101" width="52.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="71.46"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="62" t="s">
+      <c r="B1" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="62" t="s">
+      <c r="C1" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="62" t="s">
+      <c r="D1" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="62" t="s">
+      <c r="E1" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="97" t="s">
-        <v>188</v>
+      <c r="F1" s="102" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="179.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="63" t="s">
-        <v>189</v>
-      </c>
-      <c r="B2" s="64" t="s">
-        <v>181</v>
-      </c>
-      <c r="C2" s="65" t="s">
-        <v>102</v>
-      </c>
-      <c r="D2" s="65" t="s">
-        <v>114</v>
-      </c>
-      <c r="E2" s="65" t="s">
-        <v>182</v>
+      <c r="A2" s="66" t="s">
+        <v>199</v>
+      </c>
+      <c r="B2" s="67" t="s">
+        <v>191</v>
+      </c>
+      <c r="C2" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="D2" s="68" t="s">
+        <v>124</v>
+      </c>
+      <c r="E2" s="68" t="s">
+        <v>192</v>
       </c>
       <c r="F2" s="16"/>
     </row>
     <row r="3" customFormat="false" ht="179.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="63" t="s">
-        <v>190</v>
-      </c>
-      <c r="B3" s="64" t="s">
-        <v>183</v>
-      </c>
-      <c r="C3" s="65" t="s">
-        <v>191</v>
-      </c>
-      <c r="D3" s="65" t="s">
-        <v>182</v>
-      </c>
-      <c r="E3" s="65" t="s">
+      <c r="A3" s="66" t="s">
+        <v>200</v>
+      </c>
+      <c r="B3" s="67" t="s">
+        <v>193</v>
+      </c>
+      <c r="C3" s="68" t="s">
+        <v>201</v>
+      </c>
+      <c r="D3" s="68" t="s">
         <v>192</v>
       </c>
+      <c r="E3" s="68" t="s">
+        <v>202</v>
+      </c>
       <c r="F3" s="16"/>
     </row>
     <row r="4" customFormat="false" ht="131.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="98" t="s">
-        <v>193</v>
-      </c>
-      <c r="B4" s="99" t="s">
-        <v>194</v>
-      </c>
-      <c r="C4" s="100" t="s">
-        <v>195</v>
-      </c>
-      <c r="D4" s="100" t="s">
-        <v>196</v>
-      </c>
-      <c r="E4" s="100"/>
-      <c r="F4" s="101"/>
+      <c r="A4" s="103" t="s">
+        <v>203</v>
+      </c>
+      <c r="B4" s="104" t="s">
+        <v>204</v>
+      </c>
+      <c r="C4" s="105" t="s">
+        <v>205</v>
+      </c>
+      <c r="D4" s="105" t="s">
+        <v>206</v>
+      </c>
+      <c r="E4" s="105"/>
+      <c r="F4" s="106"/>
     </row>
     <row r="5" customFormat="false" ht="131.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="102" t="s">
-        <v>197</v>
-      </c>
-      <c r="B5" s="103" t="s">
-        <v>198</v>
-      </c>
-      <c r="C5" s="104" t="s">
-        <v>199</v>
-      </c>
-      <c r="D5" s="104" t="s">
-        <v>196</v>
-      </c>
-      <c r="E5" s="104"/>
-      <c r="F5" s="105"/>
+      <c r="A5" s="107" t="s">
+        <v>207</v>
+      </c>
+      <c r="B5" s="108" t="s">
+        <v>208</v>
+      </c>
+      <c r="C5" s="109" t="s">
+        <v>209</v>
+      </c>
+      <c r="D5" s="109" t="s">
+        <v>206</v>
+      </c>
+      <c r="E5" s="109"/>
+      <c r="F5" s="110"/>
     </row>
     <row r="6" customFormat="false" ht="141.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="106" t="s">
-        <v>200</v>
-      </c>
-      <c r="B6" s="107" t="s">
-        <v>201</v>
-      </c>
-      <c r="C6" s="107" t="s">
+      <c r="A6" s="111" t="s">
+        <v>210</v>
+      </c>
+      <c r="B6" s="112" t="s">
+        <v>211</v>
+      </c>
+      <c r="C6" s="112" t="s">
+        <v>212</v>
+      </c>
+      <c r="D6" s="113" t="s">
         <v>202</v>
       </c>
-      <c r="D6" s="108" t="s">
-        <v>192</v>
-      </c>
-      <c r="E6" s="108" t="s">
-        <v>203</v>
-      </c>
-      <c r="F6" s="109"/>
+      <c r="E6" s="113" t="s">
+        <v>213</v>
+      </c>
+      <c r="F6" s="114"/>
     </row>
     <row r="7" customFormat="false" ht="176.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="110" t="s">
-        <v>200</v>
-      </c>
-      <c r="B7" s="111" t="s">
-        <v>204</v>
-      </c>
-      <c r="C7" s="112" t="s">
-        <v>195</v>
-      </c>
-      <c r="D7" s="112" t="s">
+      <c r="A7" s="115" t="s">
+        <v>210</v>
+      </c>
+      <c r="B7" s="116" t="s">
+        <v>214</v>
+      </c>
+      <c r="C7" s="117" t="s">
         <v>205</v>
       </c>
-      <c r="E7" s="111"/>
-      <c r="F7" s="113"/>
+      <c r="D7" s="117" t="s">
+        <v>215</v>
+      </c>
+      <c r="E7" s="116"/>
+      <c r="F7" s="118"/>
     </row>
     <row r="8" customFormat="false" ht="168.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="114" t="s">
-        <v>206</v>
+      <c r="A8" s="119" t="s">
+        <v>216</v>
       </c>
     </row>
   </sheetData>
@@ -5697,13 +5996,13 @@
         <v>4</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
+        <v>217</v>
+      </c>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="80"/>
     </row>
     <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6"/>
@@ -5712,117 +6011,117 @@
         <v>7</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>9</v>
       </c>
       <c r="F2" s="8"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
+      <c r="J2" s="80"/>
+      <c r="K2" s="80"/>
     </row>
     <row r="3" customFormat="false" ht="74.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6"/>
       <c r="B3" s="7" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>9</v>
       </c>
       <c r="F3" s="8"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
-      <c r="K3" s="77"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
+      <c r="I3" s="80"/>
+      <c r="J3" s="80"/>
+      <c r="K3" s="80"/>
     </row>
     <row r="4" customFormat="false" ht="173.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6"/>
       <c r="B4" s="7" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="F4" s="8"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
-      <c r="K4" s="77"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="80"/>
+      <c r="I4" s="80"/>
+      <c r="J4" s="80"/>
+      <c r="K4" s="80"/>
     </row>
     <row r="5" customFormat="false" ht="85.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6"/>
       <c r="B5" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>9</v>
       </c>
       <c r="F5" s="8"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
-      <c r="K5" s="77"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="80"/>
+      <c r="J5" s="80"/>
+      <c r="K5" s="80"/>
     </row>
     <row r="6" s="2" customFormat="true" ht="75.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="7" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>20</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="F6" s="8"/>
-      <c r="G6" s="77"/>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
-      <c r="J6" s="77"/>
-      <c r="K6" s="77"/>
+      <c r="G6" s="80"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
+      <c r="J6" s="80"/>
+      <c r="K6" s="80"/>
     </row>
     <row r="7" s="2" customFormat="true" ht="224.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>24</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="12"/>
@@ -5833,149 +6132,149 @@
         <v>27</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>29</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="F8" s="8"/>
-      <c r="G8" s="77"/>
-      <c r="H8" s="77"/>
-      <c r="I8" s="77"/>
-      <c r="J8" s="77"/>
-      <c r="K8" s="77"/>
+      <c r="G8" s="80"/>
+      <c r="H8" s="80"/>
+      <c r="I8" s="80"/>
+      <c r="J8" s="80"/>
+      <c r="K8" s="80"/>
     </row>
     <row r="9" s="2" customFormat="true" ht="238.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
         <v>27</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>24</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="F9" s="8"/>
-      <c r="G9" s="77"/>
-      <c r="H9" s="77"/>
-      <c r="I9" s="77"/>
-      <c r="J9" s="77"/>
-      <c r="K9" s="77"/>
+      <c r="G9" s="80"/>
+      <c r="H9" s="80"/>
+      <c r="I9" s="80"/>
+      <c r="J9" s="80"/>
+      <c r="K9" s="80"/>
     </row>
     <row r="10" s="2" customFormat="true" ht="106.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="79" t="s">
-        <v>223</v>
+      <c r="B10" s="82" t="s">
+        <v>233</v>
       </c>
       <c r="C10" s="33" t="s">
         <v>35</v>
       </c>
       <c r="D10" s="33" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>224</v>
-      </c>
-      <c r="F10" s="115"/>
-      <c r="G10" s="77"/>
-      <c r="H10" s="77"/>
-      <c r="I10" s="77"/>
-      <c r="J10" s="77"/>
-      <c r="K10" s="77"/>
+        <v>234</v>
+      </c>
+      <c r="F10" s="120"/>
+      <c r="G10" s="80"/>
+      <c r="H10" s="80"/>
+      <c r="I10" s="80"/>
+      <c r="J10" s="80"/>
+      <c r="K10" s="80"/>
     </row>
     <row r="11" customFormat="false" ht="242.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
         <v>33</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F11" s="22"/>
-      <c r="G11" s="77"/>
-      <c r="H11" s="77"/>
-      <c r="I11" s="77"/>
-      <c r="J11" s="77"/>
-      <c r="K11" s="77"/>
+      <c r="G11" s="80"/>
+      <c r="H11" s="80"/>
+      <c r="I11" s="80"/>
+      <c r="J11" s="80"/>
+      <c r="K11" s="80"/>
     </row>
     <row r="12" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
         <v>33</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>40</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="E12" s="15"/>
       <c r="F12" s="23" t="s">
-        <v>229</v>
-      </c>
-      <c r="G12" s="77"/>
-      <c r="H12" s="77"/>
-      <c r="I12" s="77"/>
-      <c r="J12" s="77"/>
-      <c r="K12" s="77"/>
+        <v>239</v>
+      </c>
+      <c r="G12" s="80"/>
+      <c r="H12" s="80"/>
+      <c r="I12" s="80"/>
+      <c r="J12" s="80"/>
+      <c r="K12" s="80"/>
     </row>
     <row r="13" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
         <v>33</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>44</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="E13" s="15"/>
       <c r="F13" s="23"/>
-      <c r="G13" s="77"/>
-      <c r="H13" s="77"/>
-      <c r="I13" s="77"/>
-      <c r="J13" s="77"/>
-      <c r="K13" s="77"/>
+      <c r="G13" s="80"/>
+      <c r="H13" s="80"/>
+      <c r="I13" s="80"/>
+      <c r="J13" s="80"/>
+      <c r="K13" s="80"/>
     </row>
     <row r="14" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="83"/>
-      <c r="B14" s="84"/>
-      <c r="C14" s="84"/>
-      <c r="D14" s="84"/>
-      <c r="E14" s="84"/>
+      <c r="A14" s="86"/>
+      <c r="B14" s="87"/>
+      <c r="C14" s="87"/>
+      <c r="D14" s="87"/>
+      <c r="E14" s="87"/>
       <c r="F14" s="28"/>
-      <c r="G14" s="77"/>
-      <c r="H14" s="77"/>
-      <c r="I14" s="77"/>
-      <c r="J14" s="77"/>
-      <c r="K14" s="77"/>
+      <c r="G14" s="80"/>
+      <c r="H14" s="80"/>
+      <c r="I14" s="80"/>
+      <c r="J14" s="80"/>
+      <c r="K14" s="80"/>
     </row>
     <row r="15" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="29"/>
@@ -5984,230 +6283,230 @@
       <c r="D15" s="30"/>
       <c r="E15" s="30"/>
       <c r="F15" s="31"/>
-      <c r="G15" s="77"/>
-      <c r="H15" s="77"/>
-      <c r="I15" s="77"/>
-      <c r="J15" s="77"/>
-      <c r="K15" s="77"/>
+      <c r="G15" s="80"/>
+      <c r="H15" s="80"/>
+      <c r="I15" s="80"/>
+      <c r="J15" s="80"/>
+      <c r="K15" s="80"/>
     </row>
     <row r="16" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="32" t="s">
         <v>46</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="C16" s="33" t="s">
         <v>29</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="F16" s="34"/>
-      <c r="G16" s="77"/>
-      <c r="H16" s="77"/>
-      <c r="I16" s="77"/>
-      <c r="J16" s="77"/>
-      <c r="K16" s="77"/>
+      <c r="G16" s="80"/>
+      <c r="H16" s="80"/>
+      <c r="I16" s="80"/>
+      <c r="J16" s="80"/>
+      <c r="K16" s="80"/>
     </row>
     <row r="17" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
         <v>46</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="C17" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="F17" s="23"/>
-      <c r="G17" s="77"/>
-      <c r="H17" s="77"/>
-      <c r="I17" s="77"/>
-      <c r="J17" s="77"/>
-      <c r="K17" s="77"/>
+      <c r="G17" s="80"/>
+      <c r="H17" s="80"/>
+      <c r="I17" s="80"/>
+      <c r="J17" s="80"/>
+      <c r="K17" s="80"/>
     </row>
     <row r="18" customFormat="false" ht="184.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="42" t="s">
+      <c r="A18" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="B18" s="43" t="s">
-        <v>237</v>
-      </c>
-      <c r="C18" s="43" t="s">
+      <c r="B18" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="C18" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="43" t="s">
-        <v>238</v>
-      </c>
-      <c r="E18" s="43"/>
-      <c r="F18" s="39" t="s">
-        <v>239</v>
-      </c>
-      <c r="G18" s="77"/>
-      <c r="H18" s="77"/>
-      <c r="I18" s="77"/>
-      <c r="J18" s="77"/>
-      <c r="K18" s="77"/>
+      <c r="D18" s="15" t="s">
+        <v>248</v>
+      </c>
+      <c r="E18" s="15"/>
+      <c r="F18" s="23" t="s">
+        <v>249</v>
+      </c>
+      <c r="G18" s="80"/>
+      <c r="H18" s="80"/>
+      <c r="I18" s="80"/>
+      <c r="J18" s="80"/>
+      <c r="K18" s="80"/>
     </row>
     <row r="19" customFormat="false" ht="207.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="83" t="s">
+      <c r="A19" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="84" t="s">
-        <v>240</v>
-      </c>
-      <c r="C19" s="84" t="s">
+      <c r="B19" s="89" t="s">
+        <v>250</v>
+      </c>
+      <c r="C19" s="89" t="s">
         <v>44</v>
       </c>
-      <c r="D19" s="84" t="s">
-        <v>241</v>
-      </c>
-      <c r="E19" s="84"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="77"/>
-      <c r="H19" s="77"/>
-      <c r="I19" s="77"/>
-      <c r="J19" s="77"/>
-      <c r="K19" s="77"/>
+      <c r="D19" s="89" t="s">
+        <v>251</v>
+      </c>
+      <c r="E19" s="89"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="80"/>
+      <c r="H19" s="80"/>
+      <c r="I19" s="80"/>
+      <c r="J19" s="80"/>
+      <c r="K19" s="80"/>
     </row>
     <row r="20" customFormat="false" ht="207.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="83"/>
-      <c r="B20" s="84"/>
-      <c r="C20" s="84"/>
-      <c r="D20" s="84"/>
-      <c r="E20" s="84"/>
+      <c r="A20" s="86"/>
+      <c r="B20" s="87"/>
+      <c r="C20" s="87"/>
+      <c r="D20" s="87"/>
+      <c r="E20" s="87"/>
       <c r="F20" s="28"/>
-      <c r="G20" s="77"/>
-      <c r="H20" s="77"/>
-      <c r="I20" s="77"/>
-      <c r="J20" s="77"/>
-      <c r="K20" s="77"/>
+      <c r="G20" s="80"/>
+      <c r="H20" s="80"/>
+      <c r="I20" s="80"/>
+      <c r="J20" s="80"/>
+      <c r="K20" s="80"/>
     </row>
     <row r="21" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="116"/>
-      <c r="B21" s="117"/>
-      <c r="C21" s="117"/>
-      <c r="D21" s="117"/>
-      <c r="E21" s="117"/>
-      <c r="F21" s="118"/>
-      <c r="G21" s="77"/>
-      <c r="H21" s="77"/>
-      <c r="I21" s="77"/>
-      <c r="J21" s="77"/>
-      <c r="K21" s="77"/>
+      <c r="A21" s="121"/>
+      <c r="B21" s="122"/>
+      <c r="C21" s="122"/>
+      <c r="D21" s="122"/>
+      <c r="E21" s="122"/>
+      <c r="F21" s="123"/>
+      <c r="G21" s="80"/>
+      <c r="H21" s="80"/>
+      <c r="I21" s="80"/>
+      <c r="J21" s="80"/>
+      <c r="K21" s="80"/>
     </row>
     <row r="22" customFormat="false" ht="172.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="79" t="s">
-        <v>242</v>
+      <c r="B22" s="82" t="s">
+        <v>252</v>
       </c>
       <c r="C22" s="33" t="s">
         <v>35</v>
       </c>
       <c r="D22" s="33" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>243</v>
-      </c>
-      <c r="F22" s="115"/>
-      <c r="G22" s="77"/>
-      <c r="H22" s="77"/>
-      <c r="I22" s="77"/>
-      <c r="J22" s="77"/>
-      <c r="K22" s="77"/>
+        <v>253</v>
+      </c>
+      <c r="F22" s="120"/>
+      <c r="G22" s="80"/>
+      <c r="H22" s="80"/>
+      <c r="I22" s="80"/>
+      <c r="J22" s="80"/>
+      <c r="K22" s="80"/>
     </row>
     <row r="23" customFormat="false" ht="256.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="21" t="s">
         <v>57</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="C23" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="F23" s="22"/>
-      <c r="G23" s="77"/>
-      <c r="H23" s="77"/>
-      <c r="I23" s="77"/>
-      <c r="J23" s="77"/>
-      <c r="K23" s="77"/>
+      <c r="G23" s="80"/>
+      <c r="H23" s="80"/>
+      <c r="I23" s="80"/>
+      <c r="J23" s="80"/>
+      <c r="K23" s="80"/>
     </row>
     <row r="24" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="42" t="s">
+      <c r="A24" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="B24" s="43" t="s">
-        <v>246</v>
-      </c>
-      <c r="C24" s="43" t="s">
+      <c r="B24" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="C24" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D24" s="43" t="s">
-        <v>247</v>
-      </c>
-      <c r="E24" s="43"/>
-      <c r="F24" s="39" t="s">
-        <v>248</v>
-      </c>
-      <c r="G24" s="77"/>
-      <c r="H24" s="77"/>
-      <c r="I24" s="77"/>
-      <c r="J24" s="77"/>
-      <c r="K24" s="77"/>
+      <c r="D24" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="E24" s="15"/>
+      <c r="F24" s="23" t="s">
+        <v>258</v>
+      </c>
+      <c r="G24" s="80"/>
+      <c r="H24" s="80"/>
+      <c r="I24" s="80"/>
+      <c r="J24" s="80"/>
+      <c r="K24" s="80"/>
     </row>
     <row r="25" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="83" t="s">
+      <c r="A25" s="88" t="s">
         <v>57</v>
       </c>
-      <c r="B25" s="84" t="s">
-        <v>249</v>
-      </c>
-      <c r="C25" s="84" t="s">
+      <c r="B25" s="89" t="s">
+        <v>259</v>
+      </c>
+      <c r="C25" s="89" t="s">
         <v>44</v>
       </c>
-      <c r="D25" s="84" t="s">
-        <v>250</v>
-      </c>
-      <c r="E25" s="84"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="77"/>
-      <c r="H25" s="77"/>
-      <c r="I25" s="77"/>
-      <c r="J25" s="77"/>
-      <c r="K25" s="77"/>
+      <c r="D25" s="89" t="s">
+        <v>260</v>
+      </c>
+      <c r="E25" s="89"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="80"/>
+      <c r="H25" s="80"/>
+      <c r="I25" s="80"/>
+      <c r="J25" s="80"/>
+      <c r="K25" s="80"/>
     </row>
     <row r="26" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="83"/>
-      <c r="B26" s="84"/>
-      <c r="C26" s="84"/>
-      <c r="D26" s="84"/>
-      <c r="E26" s="84"/>
+      <c r="A26" s="86"/>
+      <c r="B26" s="87"/>
+      <c r="C26" s="87"/>
+      <c r="D26" s="87"/>
+      <c r="E26" s="87"/>
       <c r="F26" s="28"/>
-      <c r="G26" s="77"/>
-      <c r="H26" s="77"/>
-      <c r="I26" s="77"/>
-      <c r="J26" s="77"/>
-      <c r="K26" s="77"/>
+      <c r="G26" s="80"/>
+      <c r="H26" s="80"/>
+      <c r="I26" s="80"/>
+      <c r="J26" s="80"/>
+      <c r="K26" s="80"/>
     </row>
     <row r="27" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="29"/>
@@ -6216,190 +6515,190 @@
       <c r="D27" s="30"/>
       <c r="E27" s="30"/>
       <c r="F27" s="31"/>
-      <c r="G27" s="77"/>
-      <c r="H27" s="77"/>
-      <c r="I27" s="77"/>
-      <c r="J27" s="77"/>
-      <c r="K27" s="77"/>
+      <c r="G27" s="80"/>
+      <c r="H27" s="80"/>
+      <c r="I27" s="80"/>
+      <c r="J27" s="80"/>
+      <c r="K27" s="80"/>
     </row>
     <row r="28" customFormat="false" ht="114.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="32" t="s">
         <v>68</v>
       </c>
       <c r="B28" s="33" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="C28" s="33" t="s">
         <v>29</v>
       </c>
       <c r="D28" s="33" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="E28" s="33" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="F28" s="34"/>
-      <c r="G28" s="77"/>
-      <c r="H28" s="77"/>
-      <c r="I28" s="77"/>
-      <c r="J28" s="77"/>
-      <c r="K28" s="77"/>
+      <c r="G28" s="80"/>
+      <c r="H28" s="80"/>
+      <c r="I28" s="80"/>
+      <c r="J28" s="80"/>
+      <c r="K28" s="80"/>
     </row>
     <row r="29" customFormat="false" ht="195.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="21" t="s">
         <v>68</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="C29" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="F29" s="23"/>
-      <c r="G29" s="77"/>
-      <c r="H29" s="77"/>
-      <c r="I29" s="77"/>
-      <c r="J29" s="77"/>
-      <c r="K29" s="77"/>
+      <c r="G29" s="80"/>
+      <c r="H29" s="80"/>
+      <c r="I29" s="80"/>
+      <c r="J29" s="80"/>
+      <c r="K29" s="80"/>
     </row>
     <row r="30" customFormat="false" ht="199" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="42" t="s">
+      <c r="A30" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="B30" s="43" t="s">
-        <v>256</v>
-      </c>
-      <c r="C30" s="43" t="s">
+      <c r="B30" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="C30" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D30" s="43" t="s">
-        <v>257</v>
-      </c>
-      <c r="E30" s="43"/>
-      <c r="F30" s="39" t="s">
-        <v>258</v>
-      </c>
-      <c r="G30" s="77"/>
-      <c r="H30" s="77"/>
-      <c r="I30" s="77"/>
-      <c r="J30" s="77"/>
-      <c r="K30" s="77"/>
+      <c r="D30" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="E30" s="15"/>
+      <c r="F30" s="23" t="s">
+        <v>268</v>
+      </c>
+      <c r="G30" s="80"/>
+      <c r="H30" s="80"/>
+      <c r="I30" s="80"/>
+      <c r="J30" s="80"/>
+      <c r="K30" s="80"/>
     </row>
     <row r="31" customFormat="false" ht="153.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="83" t="s">
+      <c r="A31" s="88" t="s">
         <v>68</v>
       </c>
-      <c r="B31" s="84" t="s">
-        <v>259</v>
-      </c>
-      <c r="C31" s="84" t="s">
+      <c r="B31" s="89" t="s">
+        <v>269</v>
+      </c>
+      <c r="C31" s="89" t="s">
         <v>44</v>
       </c>
-      <c r="D31" s="84" t="s">
-        <v>260</v>
-      </c>
-      <c r="E31" s="84"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="77"/>
-      <c r="H31" s="77"/>
-      <c r="I31" s="77"/>
-      <c r="J31" s="77"/>
-      <c r="K31" s="77"/>
+      <c r="D31" s="89" t="s">
+        <v>270</v>
+      </c>
+      <c r="E31" s="89"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="80"/>
+      <c r="H31" s="80"/>
+      <c r="I31" s="80"/>
+      <c r="J31" s="80"/>
+      <c r="K31" s="80"/>
     </row>
     <row r="32" customFormat="false" ht="153.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="83"/>
-      <c r="B32" s="84"/>
-      <c r="C32" s="84"/>
-      <c r="D32" s="84"/>
-      <c r="E32" s="84"/>
+      <c r="A32" s="86"/>
+      <c r="B32" s="87"/>
+      <c r="C32" s="87"/>
+      <c r="D32" s="87"/>
+      <c r="E32" s="87"/>
       <c r="F32" s="28"/>
-      <c r="G32" s="77"/>
-      <c r="H32" s="77"/>
-      <c r="I32" s="77"/>
-      <c r="J32" s="77"/>
-      <c r="K32" s="77"/>
+      <c r="G32" s="80"/>
+      <c r="H32" s="80"/>
+      <c r="I32" s="80"/>
+      <c r="J32" s="80"/>
+      <c r="K32" s="80"/>
     </row>
     <row r="33" customFormat="false" ht="149.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="29"/>
-      <c r="B33" s="119"/>
-      <c r="C33" s="119"/>
-      <c r="D33" s="119"/>
-      <c r="E33" s="119"/>
-      <c r="F33" s="120"/>
-      <c r="G33" s="77"/>
-      <c r="H33" s="77"/>
-      <c r="I33" s="77"/>
-      <c r="J33" s="77"/>
-      <c r="K33" s="77"/>
+      <c r="B33" s="124"/>
+      <c r="C33" s="124"/>
+      <c r="D33" s="124"/>
+      <c r="E33" s="124"/>
+      <c r="F33" s="125"/>
+      <c r="G33" s="80"/>
+      <c r="H33" s="80"/>
+      <c r="I33" s="80"/>
+      <c r="J33" s="80"/>
+      <c r="K33" s="80"/>
     </row>
     <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G34" s="77"/>
-      <c r="H34" s="77"/>
-      <c r="I34" s="77"/>
-      <c r="J34" s="77"/>
-      <c r="K34" s="77"/>
+      <c r="G34" s="80"/>
+      <c r="H34" s="80"/>
+      <c r="I34" s="80"/>
+      <c r="J34" s="80"/>
+      <c r="K34" s="80"/>
     </row>
     <row r="35" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G35" s="77"/>
-      <c r="H35" s="77"/>
-      <c r="I35" s="77"/>
-      <c r="J35" s="77"/>
-      <c r="K35" s="77"/>
+      <c r="G35" s="80"/>
+      <c r="H35" s="80"/>
+      <c r="I35" s="80"/>
+      <c r="J35" s="80"/>
+      <c r="K35" s="80"/>
     </row>
     <row r="36" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G36" s="77"/>
-      <c r="H36" s="77"/>
-      <c r="I36" s="77"/>
-      <c r="J36" s="77"/>
-      <c r="K36" s="77"/>
+      <c r="G36" s="80"/>
+      <c r="H36" s="80"/>
+      <c r="I36" s="80"/>
+      <c r="J36" s="80"/>
+      <c r="K36" s="80"/>
     </row>
     <row r="37" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G37" s="77"/>
-      <c r="H37" s="77"/>
-      <c r="I37" s="77"/>
-      <c r="J37" s="77"/>
-      <c r="K37" s="77"/>
+      <c r="G37" s="80"/>
+      <c r="H37" s="80"/>
+      <c r="I37" s="80"/>
+      <c r="J37" s="80"/>
+      <c r="K37" s="80"/>
     </row>
     <row r="38" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G38" s="77"/>
-      <c r="H38" s="77"/>
-      <c r="I38" s="77"/>
-      <c r="J38" s="77"/>
-      <c r="K38" s="77"/>
+      <c r="G38" s="80"/>
+      <c r="H38" s="80"/>
+      <c r="I38" s="80"/>
+      <c r="J38" s="80"/>
+      <c r="K38" s="80"/>
     </row>
     <row r="39" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G39" s="77"/>
-      <c r="H39" s="77"/>
-      <c r="I39" s="77"/>
-      <c r="J39" s="77"/>
-      <c r="K39" s="77"/>
+      <c r="G39" s="80"/>
+      <c r="H39" s="80"/>
+      <c r="I39" s="80"/>
+      <c r="J39" s="80"/>
+      <c r="K39" s="80"/>
     </row>
     <row r="40" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G40" s="77"/>
-      <c r="H40" s="77"/>
-      <c r="I40" s="77"/>
-      <c r="J40" s="77"/>
-      <c r="K40" s="77"/>
+      <c r="G40" s="80"/>
+      <c r="H40" s="80"/>
+      <c r="I40" s="80"/>
+      <c r="J40" s="80"/>
+      <c r="K40" s="80"/>
     </row>
     <row r="41" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G41" s="77"/>
-      <c r="H41" s="77"/>
-      <c r="I41" s="77"/>
-      <c r="J41" s="77"/>
-      <c r="K41" s="77"/>
+      <c r="G41" s="80"/>
+      <c r="H41" s="80"/>
+      <c r="I41" s="80"/>
+      <c r="J41" s="80"/>
+      <c r="K41" s="80"/>
     </row>
     <row r="42" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G42" s="77"/>
-      <c r="H42" s="77"/>
-      <c r="I42" s="77"/>
-      <c r="J42" s="77"/>
-      <c r="K42" s="77"/>
+      <c r="G42" s="80"/>
+      <c r="H42" s="80"/>
+      <c r="I42" s="80"/>
+      <c r="J42" s="80"/>
+      <c r="K42" s="80"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -6431,484 +6730,484 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="3" width="26.32"/>
   </cols>
   <sheetData>
-    <row r="1" s="121" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="44" t="s">
+    <row r="1" s="126" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="42" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="42" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="45" t="s">
-        <v>261</v>
-      </c>
-      <c r="D1" s="45" t="s">
+      <c r="C1" s="43" t="s">
+        <v>271</v>
+      </c>
+      <c r="D1" s="43" t="s">
         <v>82</v>
       </c>
-      <c r="E1" s="45" t="s">
-        <v>262</v>
-      </c>
-      <c r="F1" s="45" t="s">
+      <c r="E1" s="43" t="s">
+        <v>272</v>
+      </c>
+      <c r="F1" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="45" t="s">
+      <c r="G1" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="45" t="s">
+      <c r="H1" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="I1" s="45" t="s">
+      <c r="I1" s="43" t="s">
         <v>46</v>
       </c>
-      <c r="J1" s="46" t="s">
+      <c r="J1" s="44" t="s">
         <v>68</v>
       </c>
       <c r="XFD1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="48" t="s">
-        <v>263</v>
-      </c>
-      <c r="B2" s="49" t="n">
+      <c r="A2" s="46" t="s">
+        <v>273</v>
+      </c>
+      <c r="B2" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="50" t="n">
+      <c r="C2" s="48" t="n">
         <v>1786239</v>
       </c>
-      <c r="D2" s="54" t="n">
+      <c r="D2" s="52" t="n">
         <v>1785037</v>
       </c>
-      <c r="E2" s="50" t="n">
+      <c r="E2" s="48" t="n">
         <v>1428029</v>
       </c>
-      <c r="F2" s="54" t="n">
+      <c r="F2" s="52" t="n">
         <v>1427700</v>
       </c>
-      <c r="G2" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H2" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I2" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J2" s="52" t="n">
+      <c r="G2" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H2" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I2" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J2" s="50" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="48" t="s">
-        <v>264</v>
-      </c>
-      <c r="B3" s="49" t="n">
+      <c r="A3" s="46" t="s">
+        <v>274</v>
+      </c>
+      <c r="B3" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="50" t="n">
+      <c r="C3" s="48" t="n">
         <v>349240</v>
       </c>
-      <c r="D3" s="54" t="n">
+      <c r="D3" s="52" t="n">
         <v>346201</v>
       </c>
-      <c r="E3" s="50" t="n">
+      <c r="E3" s="48" t="n">
         <v>276961</v>
       </c>
-      <c r="F3" s="54" t="n">
+      <c r="F3" s="52" t="n">
         <v>275565</v>
       </c>
-      <c r="G3" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H3" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I3" s="50" t="n">
+      <c r="G3" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H3" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I3" s="48" t="n">
         <v>9549</v>
       </c>
-      <c r="J3" s="52" t="n">
+      <c r="J3" s="50" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="48" t="s">
-        <v>265</v>
-      </c>
-      <c r="B4" s="49" t="n">
+      <c r="A4" s="46" t="s">
+        <v>275</v>
+      </c>
+      <c r="B4" s="47" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="50" t="n">
+      <c r="C4" s="48" t="n">
         <v>161323</v>
       </c>
-      <c r="D4" s="54" t="n">
+      <c r="D4" s="52" t="n">
         <v>161323</v>
       </c>
-      <c r="E4" s="50" t="n">
+      <c r="E4" s="48" t="n">
         <v>129058</v>
       </c>
-      <c r="F4" s="54" t="n">
+      <c r="F4" s="52" t="n">
         <v>129044</v>
       </c>
-      <c r="G4" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H4" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I4" s="50" t="n">
+      <c r="G4" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H4" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I4" s="48" t="n">
         <v>9994</v>
       </c>
-      <c r="J4" s="52" t="n">
+      <c r="J4" s="50" t="n">
         <v>9992</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="48" t="s">
-        <v>266</v>
-      </c>
-      <c r="B5" s="49" t="n">
+      <c r="A5" s="46" t="s">
+        <v>276</v>
+      </c>
+      <c r="B5" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="50" t="n">
+      <c r="C5" s="48" t="n">
         <v>95733</v>
       </c>
-      <c r="D5" s="54" t="n">
+      <c r="D5" s="52" t="n">
         <v>95729</v>
       </c>
-      <c r="E5" s="50" t="n">
+      <c r="E5" s="48" t="n">
         <v>76583</v>
       </c>
-      <c r="F5" s="54" t="n">
+      <c r="F5" s="52" t="n">
         <v>75502</v>
       </c>
-      <c r="G5" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H5" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I5" s="50" t="n">
+      <c r="G5" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H5" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I5" s="48" t="n">
         <v>9593</v>
       </c>
-      <c r="J5" s="52" t="n">
+      <c r="J5" s="50" t="n">
         <v>9989</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="48" t="s">
-        <v>172</v>
-      </c>
-      <c r="B6" s="49" t="n">
+      <c r="A6" s="46" t="s">
+        <v>182</v>
+      </c>
+      <c r="B6" s="47" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="50" t="n">
+      <c r="C6" s="48" t="n">
         <v>9531</v>
       </c>
-      <c r="D6" s="54" t="n">
+      <c r="D6" s="52" t="n">
         <v>9531</v>
       </c>
-      <c r="E6" s="50" t="n">
+      <c r="E6" s="48" t="n">
         <v>7625</v>
       </c>
-      <c r="F6" s="54" t="n">
+      <c r="F6" s="52" t="n">
         <v>7608</v>
       </c>
-      <c r="G6" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H6" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I6" s="50" t="n">
+      <c r="G6" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H6" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I6" s="48" t="n">
         <v>9990</v>
       </c>
-      <c r="J6" s="52" t="n">
+      <c r="J6" s="50" t="n">
         <v>9999</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="48" t="s">
-        <v>267</v>
-      </c>
-      <c r="B7" s="49" t="n">
+      <c r="A7" s="46" t="s">
+        <v>277</v>
+      </c>
+      <c r="B7" s="47" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="50" t="n">
+      <c r="C7" s="48" t="n">
         <v>8364</v>
       </c>
-      <c r="D7" s="54" t="n">
+      <c r="D7" s="52" t="n">
         <v>8364</v>
       </c>
-      <c r="E7" s="50" t="n">
+      <c r="E7" s="48" t="n">
         <v>6691</v>
       </c>
-      <c r="F7" s="54" t="n">
+      <c r="F7" s="52" t="n">
         <v>6423</v>
       </c>
-      <c r="G7" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H7" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I7" s="50" t="n">
+      <c r="G7" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H7" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I7" s="48" t="n">
         <v>9781</v>
       </c>
-      <c r="J7" s="52" t="n">
+      <c r="J7" s="50" t="n">
         <v>9944</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="48" t="s">
-        <v>268</v>
-      </c>
-      <c r="B8" s="49" t="n">
+      <c r="A8" s="46" t="s">
+        <v>278</v>
+      </c>
+      <c r="B8" s="47" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="50" t="n">
+      <c r="C8" s="48" t="n">
         <v>6860</v>
       </c>
-      <c r="D8" s="54" t="n">
+      <c r="D8" s="52" t="n">
         <v>6856</v>
       </c>
-      <c r="E8" s="50" t="n">
+      <c r="E8" s="48" t="n">
         <v>5485</v>
       </c>
-      <c r="F8" s="54" t="n">
+      <c r="F8" s="52" t="n">
         <v>5325</v>
       </c>
-      <c r="G8" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H8" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I8" s="50" t="n">
+      <c r="G8" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H8" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I8" s="48" t="n">
         <v>9873</v>
       </c>
-      <c r="J8" s="52" t="n">
+      <c r="J8" s="50" t="n">
         <v>9880</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="48" t="s">
-        <v>175</v>
-      </c>
-      <c r="B9" s="49" t="n">
+      <c r="A9" s="46" t="s">
+        <v>185</v>
+      </c>
+      <c r="B9" s="47" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="50" t="n">
+      <c r="C9" s="48" t="n">
         <v>5949</v>
       </c>
-      <c r="D9" s="54" t="n">
+      <c r="D9" s="52" t="n">
         <v>5949</v>
       </c>
-      <c r="E9" s="50" t="n">
+      <c r="E9" s="48" t="n">
         <v>4759</v>
       </c>
-      <c r="F9" s="54" t="n">
+      <c r="F9" s="52" t="n">
         <v>4732</v>
       </c>
-      <c r="G9" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H9" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I9" s="50" t="n">
+      <c r="G9" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H9" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I9" s="48" t="n">
         <v>9983</v>
       </c>
-      <c r="J9" s="52" t="n">
+      <c r="J9" s="50" t="n">
         <v>9992</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="48" t="s">
-        <v>269</v>
-      </c>
-      <c r="B10" s="49" t="n">
+      <c r="A10" s="46" t="s">
+        <v>279</v>
+      </c>
+      <c r="B10" s="47" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="50" t="n">
+      <c r="C10" s="48" t="n">
         <v>5508</v>
       </c>
-      <c r="D10" s="54" t="n">
+      <c r="D10" s="52" t="n">
         <v>5508</v>
       </c>
-      <c r="E10" s="50" t="n">
+      <c r="E10" s="48" t="n">
         <v>4406</v>
       </c>
-      <c r="F10" s="54" t="n">
+      <c r="F10" s="52" t="n">
         <v>4393</v>
       </c>
-      <c r="G10" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H10" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I10" s="50" t="n">
+      <c r="G10" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H10" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I10" s="48" t="n">
         <v>9995</v>
       </c>
-      <c r="J10" s="52" t="n">
+      <c r="J10" s="50" t="n">
         <v>9995</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="48" t="s">
-        <v>270</v>
-      </c>
-      <c r="B11" s="49" t="n">
+      <c r="A11" s="46" t="s">
+        <v>280</v>
+      </c>
+      <c r="B11" s="47" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="50" t="n">
+      <c r="C11" s="48" t="n">
         <v>5177</v>
       </c>
-      <c r="D11" s="54" t="n">
+      <c r="D11" s="52" t="n">
         <v>5123</v>
       </c>
-      <c r="E11" s="50" t="n">
+      <c r="E11" s="48" t="n">
         <v>4098</v>
       </c>
-      <c r="F11" s="54" t="n">
+      <c r="F11" s="52" t="n">
         <v>3980</v>
       </c>
-      <c r="G11" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H11" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I11" s="50" t="n">
+      <c r="G11" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H11" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I11" s="48" t="n">
         <v>9868</v>
       </c>
-      <c r="J11" s="52" t="n">
+      <c r="J11" s="50" t="n">
         <v>9881</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="48" t="s">
-        <v>271</v>
-      </c>
-      <c r="B12" s="49" t="n">
+      <c r="A12" s="46" t="s">
+        <v>281</v>
+      </c>
+      <c r="B12" s="47" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="50" t="n">
+      <c r="C12" s="48" t="n">
         <v>2734</v>
       </c>
-      <c r="D12" s="54" t="n">
+      <c r="D12" s="52" t="n">
         <v>2733</v>
       </c>
-      <c r="E12" s="50" t="n">
+      <c r="E12" s="48" t="n">
         <v>2187</v>
       </c>
-      <c r="F12" s="54" t="n">
+      <c r="F12" s="52" t="n">
         <v>2176</v>
       </c>
-      <c r="G12" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H12" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I12" s="50" t="n">
+      <c r="G12" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H12" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I12" s="48" t="n">
         <v>9971</v>
       </c>
-      <c r="J12" s="52" t="n">
+      <c r="J12" s="50" t="n">
         <v>9971</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="48" t="s">
-        <v>272</v>
-      </c>
-      <c r="B13" s="49" t="n">
+      <c r="A13" s="46" t="s">
+        <v>282</v>
+      </c>
+      <c r="B13" s="47" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="50" t="n">
+      <c r="C13" s="48" t="n">
         <v>1358</v>
       </c>
-      <c r="D13" s="54" t="n">
+      <c r="D13" s="52" t="n">
         <v>1357</v>
       </c>
-      <c r="E13" s="50" t="n">
+      <c r="E13" s="48" t="n">
         <v>1086</v>
       </c>
-      <c r="F13" s="54" t="n">
+      <c r="F13" s="52" t="n">
         <v>1076</v>
       </c>
-      <c r="G13" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H13" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I13" s="50" t="n">
+      <c r="G13" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H13" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I13" s="48" t="n">
         <v>9971</v>
       </c>
-      <c r="J13" s="52" t="n">
+      <c r="J13" s="50" t="n">
         <v>9971</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="48" t="s">
-        <v>273</v>
-      </c>
-      <c r="B14" s="49" t="n">
+      <c r="A14" s="46" t="s">
+        <v>283</v>
+      </c>
+      <c r="B14" s="47" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="50" t="n">
+      <c r="C14" s="48" t="n">
         <v>24</v>
       </c>
-      <c r="D14" s="54" t="n">
+      <c r="D14" s="52" t="n">
         <v>24</v>
       </c>
-      <c r="E14" s="50" t="n">
+      <c r="E14" s="48" t="n">
         <v>19</v>
       </c>
-      <c r="F14" s="54" t="n">
+      <c r="F14" s="52" t="n">
         <v>5</v>
       </c>
-      <c r="G14" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H14" s="54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I14" s="50" t="n">
+      <c r="G14" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H14" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I14" s="48" t="n">
         <v>9998</v>
       </c>
-      <c r="J14" s="52" t="n">
+      <c r="J14" s="50" t="n">
         <v>9998</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="122" t="s">
-        <v>180</v>
-      </c>
-      <c r="B15" s="56" t="n">
+      <c r="A15" s="127" t="s">
+        <v>190</v>
+      </c>
+      <c r="B15" s="54" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="57" t="n">
+      <c r="C15" s="55" t="n">
         <v>12</v>
       </c>
-      <c r="D15" s="57" t="n">
+      <c r="D15" s="55" t="n">
         <v>12</v>
       </c>
-      <c r="E15" s="57" t="n">
+      <c r="E15" s="55" t="n">
         <v>10</v>
       </c>
-      <c r="F15" s="57" t="n">
+      <c r="F15" s="55" t="n">
         <v>10</v>
       </c>
-      <c r="G15" s="57" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H15" s="59" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I15" s="57" t="n">
+      <c r="G15" s="55" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H15" s="57" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I15" s="55" t="n">
         <v>9995</v>
       </c>
-      <c r="J15" s="60" t="n">
+      <c r="J15" s="58" t="n">
         <v>9995</v>
       </c>
     </row>
@@ -6950,9 +7249,9 @@
       <c r="J17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E18" s="61"/>
-      <c r="F18" s="49"/>
-      <c r="G18" s="49"/>
+      <c r="E18" s="59"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="47"/>
     </row>
     <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
@@ -6961,13 +7260,13 @@
       <c r="C19" s="3" t="n">
         <v>122</v>
       </c>
-      <c r="D19" s="50" t="n">
+      <c r="D19" s="48" t="n">
         <v>48</v>
       </c>
-      <c r="E19" s="49" t="n">
+      <c r="E19" s="47" t="n">
         <v>48</v>
       </c>
-      <c r="F19" s="49" t="n">
+      <c r="F19" s="47" t="n">
         <v>48</v>
       </c>
       <c r="G19" s="3" t="n">
@@ -6979,7 +7278,7 @@
       <c r="I19" s="2"/>
     </row>
     <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J34" s="50"/>
+      <c r="J34" s="48"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/TFG1/02_datasets/metadata/METADATA.xlsx
+++ b/TFG1/02_datasets/metadata/METADATA.xlsx
@@ -1276,11 +1276,31 @@
 Pd_BCCC17__RUS_SMOTE_ENN__v1__val__5.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">pd_BCCC17__RUS_SMOTE_ENN__v1__training_v1__1_5.ipynb
-pd_BCCC17__RUS_SMOTE_ENN__v1__training_v1__2_5.ipynb
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pd_BCCC17__RUS_SMOTE_ENN__v1__training_v1__1_5.ipynb
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code PL"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pd_BCCC17__RUS_SMOTE_ENN__v1__training_v1__2_5.ipynb
 pd_BCCC17__RUS_SMOTE_ENN__v1__training_v1__3_5.ipynb
 pd_BCCC17__RUS_SMOTE_ENN__v1__training_v1__4_5.ipynb
 pd_BCCC17__RUS_SMOTE_ENN__v1__training_v1__5_5.ipynb</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">pd_BCCC17__RUS_SMOTE_ENN__v1__train__1.csv
@@ -1813,7 +1833,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="127">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1970,11 +1990,195 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1982,198 +2186,6 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2296,6 +2308,10 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -2985,20 +3001,20 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="213.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="39" t="s">
+      <c r="A26" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="B26" s="40" t="s">
+      <c r="B26" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="C26" s="40" t="s">
+      <c r="C26" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="D26" s="40" t="s">
+      <c r="D26" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="E26" s="40"/>
-      <c r="F26" s="41"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="23"/>
     </row>
     <row r="27" customFormat="false" ht="213.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="26"/>
@@ -3077,20 +3093,20 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="165.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="39" t="s">
+      <c r="A32" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="B32" s="40" t="s">
+      <c r="B32" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="C32" s="40" t="s">
+      <c r="C32" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="D32" s="40" t="s">
+      <c r="D32" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="E32" s="40"/>
-      <c r="F32" s="41"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="23"/>
     </row>
     <row r="33" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="26"/>
@@ -3135,137 +3151,137 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="65" t="s">
+      <c r="B1" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="65" t="s">
+      <c r="C1" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="65" t="s">
+      <c r="D1" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="65" t="s">
+      <c r="E1" s="62" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="179.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="66"/>
-      <c r="B2" s="67" t="s">
+      <c r="A2" s="63"/>
+      <c r="B2" s="64" t="s">
         <v>284</v>
       </c>
-      <c r="C2" s="68" t="s">
+      <c r="C2" s="65" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="68" t="s">
+      <c r="D2" s="65" t="s">
         <v>218</v>
       </c>
-      <c r="E2" s="68" t="s">
+      <c r="E2" s="65" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="101.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="67"/>
-      <c r="B3" s="67" t="s">
+      <c r="A3" s="64"/>
+      <c r="B3" s="64" t="s">
         <v>286</v>
       </c>
-      <c r="C3" s="67" t="s">
+      <c r="C3" s="64" t="s">
         <v>115</v>
       </c>
-      <c r="D3" s="68" t="s">
+      <c r="D3" s="65" t="s">
         <v>285</v>
       </c>
-      <c r="E3" s="68" t="s">
+      <c r="E3" s="65" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="86.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="67"/>
-      <c r="B4" s="67" t="s">
+      <c r="A4" s="64"/>
+      <c r="B4" s="64" t="s">
         <v>288</v>
       </c>
-      <c r="C4" s="67" t="s">
+      <c r="C4" s="64" t="s">
         <v>118</v>
       </c>
-      <c r="D4" s="68" t="s">
+      <c r="D4" s="65" t="s">
         <v>287</v>
       </c>
-      <c r="E4" s="68" t="s">
+      <c r="E4" s="65" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="89.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="67"/>
-      <c r="B5" s="67" t="s">
+      <c r="A5" s="64"/>
+      <c r="B5" s="64" t="s">
         <v>290</v>
       </c>
-      <c r="C5" s="68" t="s">
+      <c r="C5" s="65" t="s">
         <v>121</v>
       </c>
-      <c r="D5" s="68" t="s">
+      <c r="D5" s="65" t="s">
         <v>289</v>
       </c>
-      <c r="E5" s="67"/>
+      <c r="E5" s="64"/>
     </row>
     <row r="6" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="66"/>
-      <c r="B6" s="67" t="s">
+      <c r="A6" s="63"/>
+      <c r="B6" s="64" t="s">
         <v>291</v>
       </c>
-      <c r="C6" s="68" t="s">
+      <c r="C6" s="65" t="s">
         <v>292</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="65" t="s">
         <v>218</v>
       </c>
-      <c r="E6" s="68" t="s">
+      <c r="E6" s="65" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="86.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="67"/>
-      <c r="B7" s="67" t="s">
+      <c r="A7" s="64"/>
+      <c r="B7" s="64" t="s">
         <v>286</v>
       </c>
-      <c r="C7" s="67" t="s">
+      <c r="C7" s="64" t="s">
         <v>115</v>
       </c>
-      <c r="D7" s="68" t="s">
+      <c r="D7" s="65" t="s">
         <v>285</v>
       </c>
-      <c r="E7" s="68" t="s">
+      <c r="E7" s="65" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="107.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="69"/>
-      <c r="B8" s="69" t="s">
+      <c r="A8" s="66"/>
+      <c r="B8" s="66" t="s">
         <v>288</v>
       </c>
-      <c r="C8" s="69" t="s">
+      <c r="C8" s="66" t="s">
         <v>118</v>
       </c>
-      <c r="D8" s="70" t="s">
+      <c r="D8" s="67" t="s">
         <v>287</v>
       </c>
-      <c r="E8" s="70" t="s">
+      <c r="E8" s="67" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="123.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="71"/>
-      <c r="B9" s="71" t="s">
+      <c r="A9" s="68"/>
+      <c r="B9" s="68" t="s">
         <v>290</v>
       </c>
-      <c r="C9" s="72" t="s">
+      <c r="C9" s="69" t="s">
         <v>121</v>
       </c>
-      <c r="D9" s="72" t="s">
+      <c r="D9" s="69" t="s">
         <v>289</v>
       </c>
-      <c r="E9" s="71"/>
+      <c r="E9" s="68"/>
     </row>
     <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -3304,576 +3320,576 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="31.21"/>
   </cols>
   <sheetData>
-    <row r="1" s="45" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="42" t="s">
+    <row r="1" s="42" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="42" t="s">
+      <c r="B1" s="39" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="43" t="s">
+      <c r="C1" s="40" t="s">
         <v>81</v>
       </c>
-      <c r="D1" s="43" t="s">
+      <c r="D1" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="E1" s="43" t="s">
+      <c r="E1" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="F1" s="43" t="s">
+      <c r="F1" s="40" t="s">
         <v>84</v>
       </c>
-      <c r="G1" s="43" t="s">
+      <c r="G1" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="43" t="s">
+      <c r="H1" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="I1" s="44" t="s">
+      <c r="I1" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="J1" s="43" t="s">
+      <c r="J1" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="K1" s="44" t="s">
+      <c r="K1" s="41" t="s">
         <v>68</v>
       </c>
       <c r="XFD1" s="2"/>
     </row>
     <row r="2" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="47" t="n">
+      <c r="B2" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="48" t="n">
+      <c r="C2" s="45" t="n">
         <v>13484658</v>
       </c>
-      <c r="D2" s="48" t="n">
+      <c r="D2" s="45" t="n">
         <v>13445443</v>
       </c>
-      <c r="E2" s="48" t="n">
+      <c r="E2" s="45" t="n">
         <v>450000</v>
       </c>
-      <c r="F2" s="48" t="n">
+      <c r="F2" s="45" t="n">
         <v>360000</v>
       </c>
-      <c r="G2" s="48" t="n">
+      <c r="G2" s="45" t="n">
         <v>339865</v>
       </c>
-      <c r="H2" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I2" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J2" s="48" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K2" s="50" t="n">
+      <c r="H2" s="46" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I2" s="46" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J2" s="45" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K2" s="47" t="n">
         <v>10000</v>
       </c>
       <c r="XFD2" s="2"/>
     </row>
     <row r="3" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="B3" s="47" t="n">
+      <c r="B3" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="48" t="n">
+      <c r="C3" s="45" t="n">
         <v>686012</v>
       </c>
-      <c r="D3" s="48" t="n">
+      <c r="D3" s="45" t="n">
         <v>668461</v>
       </c>
-      <c r="E3" s="48" t="n">
+      <c r="E3" s="45" t="n">
         <v>450000</v>
       </c>
-      <c r="F3" s="48" t="n">
+      <c r="F3" s="45" t="n">
         <v>360000</v>
       </c>
-      <c r="G3" s="48" t="n">
+      <c r="G3" s="45" t="n">
         <v>359280</v>
       </c>
-      <c r="H3" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I3" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J3" s="48" t="n">
+      <c r="H3" s="46" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I3" s="46" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J3" s="45" t="n">
         <v>9840</v>
       </c>
-      <c r="K3" s="50" t="n">
+      <c r="K3" s="47" t="n">
         <v>9993</v>
       </c>
       <c r="XFD3" s="2"/>
     </row>
     <row r="4" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="48" t="s">
         <v>87</v>
       </c>
-      <c r="B4" s="47" t="n">
+      <c r="B4" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="48" t="n">
+      <c r="C4" s="45" t="n">
         <v>576191</v>
       </c>
-      <c r="D4" s="48" t="n">
+      <c r="D4" s="45" t="n">
         <v>576175</v>
       </c>
-      <c r="E4" s="48" t="n">
+      <c r="E4" s="45" t="n">
         <v>450000</v>
       </c>
-      <c r="F4" s="48" t="n">
+      <c r="F4" s="45" t="n">
         <v>360000</v>
       </c>
-      <c r="G4" s="48" t="n">
+      <c r="G4" s="45" t="n">
         <v>359369</v>
       </c>
-      <c r="H4" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I4" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J4" s="48" t="n">
+      <c r="H4" s="46" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I4" s="46" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J4" s="45" t="n">
         <v>9974</v>
       </c>
-      <c r="K4" s="50" t="n">
+      <c r="K4" s="47" t="n">
         <v>9968</v>
       </c>
       <c r="XFD4" s="2"/>
     </row>
     <row r="5" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="51" t="s">
+      <c r="A5" s="48" t="s">
         <v>88</v>
       </c>
-      <c r="B5" s="47" t="n">
+      <c r="B5" s="44" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="48" t="n">
+      <c r="C5" s="45" t="n">
         <v>461912</v>
       </c>
-      <c r="D5" s="48" t="n">
+      <c r="D5" s="45" t="n">
         <v>434873</v>
       </c>
-      <c r="E5" s="52" t="n">
+      <c r="E5" s="49" t="n">
         <v>434873</v>
       </c>
-      <c r="F5" s="48" t="n">
+      <c r="F5" s="45" t="n">
         <v>347898</v>
       </c>
-      <c r="G5" s="48" t="n">
+      <c r="G5" s="45" t="n">
         <v>346118</v>
       </c>
-      <c r="H5" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I5" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J5" s="48" t="n">
+      <c r="H5" s="46" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I5" s="46" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J5" s="45" t="n">
         <v>9855</v>
       </c>
-      <c r="K5" s="50" t="n">
+      <c r="K5" s="47" t="n">
         <v>9914</v>
       </c>
       <c r="XFD5" s="2"/>
     </row>
     <row r="6" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="48" t="s">
         <v>89</v>
       </c>
-      <c r="B6" s="47" t="n">
+      <c r="B6" s="44" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="48" t="n">
+      <c r="C6" s="45" t="n">
         <v>286191</v>
       </c>
-      <c r="D6" s="48" t="n">
+      <c r="D6" s="45" t="n">
         <v>282310</v>
       </c>
-      <c r="E6" s="52" t="n">
+      <c r="E6" s="49" t="n">
         <v>282310</v>
       </c>
-      <c r="F6" s="48" t="n">
+      <c r="F6" s="45" t="n">
         <v>225848</v>
       </c>
-      <c r="G6" s="48" t="n">
+      <c r="G6" s="45" t="n">
         <v>225602</v>
       </c>
-      <c r="H6" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I6" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J6" s="48" t="n">
+      <c r="H6" s="46" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I6" s="46" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J6" s="45" t="n">
         <v>9971</v>
       </c>
-      <c r="K6" s="50" t="n">
+      <c r="K6" s="47" t="n">
         <v>10000</v>
       </c>
       <c r="XFD6" s="2"/>
     </row>
     <row r="7" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="51" t="s">
+      <c r="A7" s="48" t="s">
         <v>90</v>
       </c>
-      <c r="B7" s="47" t="n">
+      <c r="B7" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="48" t="n">
+      <c r="C7" s="45" t="n">
         <v>161934</v>
       </c>
-      <c r="D7" s="48" t="n">
+      <c r="D7" s="45" t="n">
         <v>161897</v>
       </c>
-      <c r="E7" s="52" t="n">
+      <c r="E7" s="49" t="n">
         <v>161897</v>
       </c>
-      <c r="F7" s="48" t="n">
+      <c r="F7" s="45" t="n">
         <v>129517</v>
       </c>
-      <c r="G7" s="48" t="n">
+      <c r="G7" s="45" t="n">
         <v>108526</v>
       </c>
-      <c r="H7" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I7" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J7" s="48" t="n">
+      <c r="H7" s="46" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I7" s="46" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J7" s="45" t="n">
         <v>8820</v>
       </c>
-      <c r="K7" s="50" t="n">
+      <c r="K7" s="47" t="n">
         <v>9998</v>
       </c>
       <c r="XFD7" s="2"/>
     </row>
     <row r="8" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="51" t="s">
+      <c r="A8" s="48" t="s">
         <v>91</v>
       </c>
-      <c r="B8" s="47" t="n">
+      <c r="B8" s="44" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="48" t="n">
+      <c r="C8" s="45" t="n">
         <v>187589</v>
       </c>
-      <c r="D8" s="48" t="n">
+      <c r="D8" s="45" t="n">
         <v>117322</v>
       </c>
-      <c r="E8" s="52" t="n">
+      <c r="E8" s="49" t="n">
         <v>117322</v>
       </c>
-      <c r="F8" s="48" t="n">
+      <c r="F8" s="45" t="n">
         <v>93857</v>
       </c>
-      <c r="G8" s="48" t="n">
+      <c r="G8" s="45" t="n">
         <v>93112</v>
       </c>
-      <c r="H8" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I8" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J8" s="48" t="n">
+      <c r="H8" s="46" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I8" s="46" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J8" s="45" t="n">
         <v>9896</v>
       </c>
-      <c r="K8" s="50" t="n">
+      <c r="K8" s="47" t="n">
         <v>9967</v>
       </c>
       <c r="XFD8" s="2"/>
     </row>
     <row r="9" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="51" t="s">
+      <c r="A9" s="48" t="s">
         <v>92</v>
       </c>
-      <c r="B9" s="47" t="n">
+      <c r="B9" s="44" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="48" t="n">
+      <c r="C9" s="45" t="n">
         <v>41508</v>
       </c>
-      <c r="D9" s="48" t="n">
+      <c r="D9" s="45" t="n">
         <v>41455</v>
       </c>
-      <c r="E9" s="52" t="n">
+      <c r="E9" s="49" t="n">
         <v>41455</v>
       </c>
-      <c r="F9" s="48" t="n">
+      <c r="F9" s="45" t="n">
         <v>33164</v>
       </c>
-      <c r="G9" s="48" t="n">
+      <c r="G9" s="45" t="n">
         <v>31187</v>
       </c>
-      <c r="H9" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I9" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J9" s="48" t="n">
+      <c r="H9" s="46" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I9" s="46" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J9" s="45" t="n">
         <v>9533</v>
       </c>
-      <c r="K9" s="50" t="n">
+      <c r="K9" s="47" t="n">
         <v>9974</v>
       </c>
       <c r="XFD9" s="2"/>
     </row>
     <row r="10" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="51" t="s">
+      <c r="A10" s="48" t="s">
         <v>93</v>
       </c>
-      <c r="B10" s="47" t="n">
+      <c r="B10" s="44" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="48" t="n">
+      <c r="C10" s="45" t="n">
         <v>193360</v>
       </c>
-      <c r="D10" s="48" t="n">
+      <c r="D10" s="45" t="n">
         <v>39352</v>
       </c>
-      <c r="E10" s="52" t="n">
+      <c r="E10" s="49" t="n">
         <v>39352</v>
       </c>
-      <c r="F10" s="48" t="n">
+      <c r="F10" s="45" t="n">
         <v>31482</v>
       </c>
-      <c r="G10" s="48" t="n">
+      <c r="G10" s="45" t="n">
         <v>31432</v>
       </c>
-      <c r="H10" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I10" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J10" s="48" t="n">
+      <c r="H10" s="46" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I10" s="46" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J10" s="45" t="n">
         <v>9986</v>
       </c>
-      <c r="K10" s="50" t="n">
+      <c r="K10" s="47" t="n">
         <v>10000</v>
       </c>
       <c r="XFD10" s="2"/>
     </row>
     <row r="11" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="51" t="s">
+      <c r="A11" s="48" t="s">
         <v>94</v>
       </c>
-      <c r="B11" s="47" t="n">
+      <c r="B11" s="44" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="48" t="n">
+      <c r="C11" s="45" t="n">
         <v>139890</v>
       </c>
-      <c r="D11" s="48" t="n">
+      <c r="D11" s="45" t="n">
         <v>19462</v>
       </c>
-      <c r="E11" s="52" t="n">
+      <c r="E11" s="49" t="n">
         <v>19462</v>
       </c>
-      <c r="F11" s="48" t="n">
+      <c r="F11" s="45" t="n">
         <v>15570</v>
       </c>
-      <c r="G11" s="48" t="n">
+      <c r="G11" s="45" t="n">
         <v>15570</v>
       </c>
-      <c r="H11" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I11" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J11" s="48" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K11" s="50" t="n">
+      <c r="H11" s="46" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I11" s="46" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J11" s="45" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K11" s="47" t="n">
         <v>10000</v>
       </c>
       <c r="XFD11" s="2"/>
     </row>
     <row r="12" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="51" t="s">
+      <c r="A12" s="48" t="s">
         <v>95</v>
       </c>
-      <c r="B12" s="47" t="n">
+      <c r="B12" s="44" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="48" t="n">
+      <c r="C12" s="45" t="n">
         <v>10990</v>
       </c>
-      <c r="D12" s="48" t="n">
+      <c r="D12" s="45" t="n">
         <v>10285</v>
       </c>
-      <c r="E12" s="52" t="n">
+      <c r="E12" s="49" t="n">
         <v>10285</v>
       </c>
-      <c r="F12" s="48" t="n">
+      <c r="F12" s="45" t="n">
         <v>8228</v>
       </c>
-      <c r="G12" s="48" t="n">
+      <c r="G12" s="45" t="n">
         <v>7975</v>
       </c>
-      <c r="H12" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I12" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J12" s="48" t="n">
+      <c r="H12" s="46" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I12" s="46" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J12" s="45" t="n">
         <v>9838</v>
       </c>
-      <c r="K12" s="50" t="n">
+      <c r="K12" s="47" t="n">
         <v>9939</v>
       </c>
       <c r="XFD12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="51" t="s">
+      <c r="A13" s="48" t="s">
         <v>96</v>
       </c>
-      <c r="B13" s="47" t="n">
+      <c r="B13" s="44" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="48" t="n">
+      <c r="C13" s="45" t="n">
         <v>1730</v>
       </c>
-      <c r="D13" s="48" t="n">
+      <c r="D13" s="45" t="n">
         <v>1730</v>
       </c>
-      <c r="E13" s="52" t="n">
+      <c r="E13" s="49" t="n">
         <v>1730</v>
       </c>
-      <c r="F13" s="48" t="n">
+      <c r="F13" s="45" t="n">
         <v>1384</v>
       </c>
-      <c r="G13" s="48" t="n">
+      <c r="G13" s="45" t="n">
         <v>1378</v>
       </c>
-      <c r="H13" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I13" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J13" s="48" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K13" s="50" t="n">
+      <c r="H13" s="46" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I13" s="46" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J13" s="45" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K13" s="47" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="51" t="s">
+      <c r="A14" s="48" t="s">
         <v>97</v>
       </c>
-      <c r="B14" s="47" t="n">
+      <c r="B14" s="44" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="48" t="n">
+      <c r="C14" s="45" t="n">
         <v>611</v>
       </c>
-      <c r="D14" s="48" t="n">
+      <c r="D14" s="45" t="n">
         <v>611</v>
       </c>
-      <c r="E14" s="52" t="n">
+      <c r="E14" s="49" t="n">
         <v>611</v>
       </c>
-      <c r="F14" s="48" t="n">
+      <c r="F14" s="45" t="n">
         <v>489</v>
       </c>
-      <c r="G14" s="48" t="n">
+      <c r="G14" s="45" t="n">
         <v>211</v>
       </c>
-      <c r="H14" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I14" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J14" s="48" t="n">
+      <c r="H14" s="46" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I14" s="46" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J14" s="45" t="n">
         <v>9624</v>
       </c>
-      <c r="K14" s="50" t="n">
+      <c r="K14" s="47" t="n">
         <v>9593</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="51" t="s">
+      <c r="A15" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="B15" s="47" t="n">
+      <c r="B15" s="44" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="48" t="n">
+      <c r="C15" s="45" t="n">
         <v>230</v>
       </c>
-      <c r="D15" s="48" t="n">
+      <c r="D15" s="45" t="n">
         <v>230</v>
       </c>
-      <c r="E15" s="52" t="n">
+      <c r="E15" s="49" t="n">
         <v>230</v>
       </c>
-      <c r="F15" s="48" t="n">
+      <c r="F15" s="45" t="n">
         <v>184</v>
       </c>
-      <c r="G15" s="48" t="n">
+      <c r="G15" s="45" t="n">
         <v>66</v>
       </c>
-      <c r="H15" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I15" s="49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J15" s="48" t="n">
+      <c r="H15" s="46" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I15" s="46" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J15" s="45" t="n">
         <v>9673</v>
       </c>
-      <c r="K15" s="50" t="n">
+      <c r="K15" s="47" t="n">
         <v>9655</v>
       </c>
       <c r="XFD15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="53" t="s">
+      <c r="A16" s="50" t="s">
         <v>99</v>
       </c>
-      <c r="B16" s="54" t="n">
+      <c r="B16" s="51" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="55" t="n">
+      <c r="C16" s="52" t="n">
         <v>87</v>
       </c>
-      <c r="D16" s="55" t="n">
+      <c r="D16" s="52" t="n">
         <v>87</v>
       </c>
-      <c r="E16" s="55" t="n">
+      <c r="E16" s="52" t="n">
         <v>87</v>
       </c>
-      <c r="F16" s="55" t="n">
+      <c r="F16" s="52" t="n">
         <v>70</v>
       </c>
-      <c r="G16" s="56" t="n">
+      <c r="G16" s="53" t="n">
         <v>70</v>
       </c>
-      <c r="H16" s="57" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I16" s="57" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J16" s="55" t="n">
+      <c r="H16" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I16" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J16" s="52" t="n">
         <v>9987</v>
       </c>
-      <c r="K16" s="58" t="n">
+      <c r="K16" s="55" t="n">
         <v>9986</v>
       </c>
     </row>
@@ -3916,18 +3932,18 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E18" s="59"/>
-      <c r="F18" s="47"/>
+      <c r="E18" s="56"/>
+      <c r="F18" s="44"/>
       <c r="G18" s="3"/>
-      <c r="H18" s="59"/>
-      <c r="I18" s="48"/>
+      <c r="H18" s="56"/>
+      <c r="I18" s="45"/>
     </row>
     <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E19" s="59"/>
-      <c r="F19" s="47"/>
+      <c r="E19" s="56"/>
+      <c r="F19" s="44"/>
       <c r="G19" s="3"/>
-      <c r="H19" s="48"/>
-      <c r="I19" s="48"/>
+      <c r="H19" s="45"/>
+      <c r="I19" s="45"/>
     </row>
     <row r="20" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
@@ -3948,23 +3964,23 @@
       <c r="G20" s="3" t="n">
         <v>56</v>
       </c>
-      <c r="H20" s="48" t="n">
+      <c r="H20" s="45" t="n">
         <v>56</v>
       </c>
-      <c r="I20" s="48" t="n">
+      <c r="I20" s="45" t="n">
         <v>56</v>
       </c>
       <c r="XFD20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G21" s="3"/>
-      <c r="H21" s="48"/>
-      <c r="I21" s="48"/>
+      <c r="H21" s="45"/>
+      <c r="I21" s="45"/>
     </row>
     <row r="22" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G22" s="3"/>
-      <c r="H22" s="48"/>
-      <c r="I22" s="48"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="45"/>
     </row>
     <row r="23" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G23" s="3"/>
@@ -3975,293 +3991,261 @@
     <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G25" s="3"/>
     </row>
-    <row r="26" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="60" t="s">
+    <row r="26" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="57" t="s">
         <v>101</v>
       </c>
-      <c r="B26" s="60" t="s">
+      <c r="B26" s="57" t="s">
         <v>102</v>
       </c>
-      <c r="C26" s="60" t="s">
+      <c r="C26" s="57" t="s">
         <v>103</v>
       </c>
-      <c r="D26" s="60" t="s">
+      <c r="D26" s="57" t="s">
         <v>104</v>
       </c>
-      <c r="E26" s="60" t="s">
+      <c r="E26" s="57" t="s">
         <v>105</v>
       </c>
-      <c r="F26" s="60" t="s">
+      <c r="F26" s="57" t="s">
         <v>106</v>
       </c>
-      <c r="G26" s="60" t="s">
+      <c r="G26" s="57" t="s">
         <v>107</v>
       </c>
-      <c r="H26" s="60" t="s">
+      <c r="H26" s="57" t="s">
         <v>108</v>
       </c>
-      <c r="I26" s="60" t="s">
+      <c r="I26" s="57" t="s">
         <v>109</v>
       </c>
-      <c r="J26" s="61" t="s">
+      <c r="J26" s="58" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="62" t="n">
+    <row r="27" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="59" t="n">
         <v>1</v>
       </c>
-      <c r="B27" s="62" t="s">
+      <c r="B27" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="C27" s="48"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="48"/>
-      <c r="F27" s="48"/>
-      <c r="G27" s="48"/>
-      <c r="H27" s="48"/>
-      <c r="I27" s="48"/>
-      <c r="J27" s="48"/>
-    </row>
-    <row r="28" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="62" t="n">
+      <c r="C27" s="45"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="45"/>
+      <c r="H27" s="45"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="45"/>
+    </row>
+    <row r="28" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="59" t="n">
         <v>2</v>
       </c>
-      <c r="B28" s="62" t="s">
+      <c r="B28" s="59" t="s">
         <v>46</v>
       </c>
-      <c r="C28" s="48"/>
-      <c r="D28" s="48"/>
-      <c r="E28" s="48"/>
-      <c r="F28" s="48"/>
-      <c r="G28" s="48"/>
-      <c r="H28" s="48"/>
-      <c r="I28" s="48"/>
-      <c r="J28" s="48"/>
-    </row>
-    <row r="29" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="62" t="n">
+      <c r="C28" s="45"/>
+      <c r="D28" s="45"/>
+      <c r="E28" s="45"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="45"/>
+      <c r="H28" s="45"/>
+      <c r="I28" s="45"/>
+      <c r="J28" s="45"/>
+    </row>
+    <row r="29" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="59" t="n">
         <v>3</v>
       </c>
-      <c r="B29" s="62" t="s">
+      <c r="B29" s="59" t="s">
         <v>57</v>
       </c>
-      <c r="C29" s="63"/>
-      <c r="D29" s="63"/>
-      <c r="E29" s="63"/>
-      <c r="F29" s="63"/>
-      <c r="G29" s="63"/>
-      <c r="H29" s="63"/>
-      <c r="I29" s="63"/>
-      <c r="J29" s="64"/>
-    </row>
-    <row r="30" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="62" t="n">
+      <c r="C29" s="60"/>
+      <c r="D29" s="60"/>
+      <c r="E29" s="60"/>
+      <c r="F29" s="60"/>
+      <c r="G29" s="60"/>
+      <c r="H29" s="60"/>
+      <c r="I29" s="60"/>
+      <c r="J29" s="61"/>
+    </row>
+    <row r="30" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="59" t="n">
         <v>4</v>
       </c>
-      <c r="B30" s="62" t="s">
+      <c r="B30" s="59" t="s">
         <v>68</v>
       </c>
-      <c r="C30" s="48"/>
-      <c r="D30" s="48"/>
-      <c r="E30" s="48"/>
-      <c r="F30" s="48"/>
-      <c r="G30" s="48"/>
-      <c r="H30" s="48"/>
-      <c r="I30" s="48"/>
-      <c r="J30" s="48"/>
+      <c r="C30" s="45"/>
+      <c r="D30" s="45"/>
+      <c r="E30" s="45"/>
+      <c r="F30" s="45"/>
+      <c r="G30" s="45"/>
+      <c r="H30" s="45"/>
+      <c r="I30" s="45"/>
+      <c r="J30" s="45"/>
     </row>
     <row r="31" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="48"/>
-      <c r="B31" s="48"/>
-      <c r="C31" s="48"/>
-      <c r="D31" s="48"/>
-      <c r="E31" s="48"/>
-      <c r="F31" s="48"/>
-      <c r="G31" s="48"/>
-      <c r="H31" s="48"/>
-      <c r="J31" s="0"/>
-      <c r="K31" s="0"/>
+      <c r="A31" s="45"/>
+      <c r="B31" s="45"/>
+      <c r="C31" s="45"/>
+      <c r="D31" s="45"/>
+      <c r="E31" s="45"/>
+      <c r="F31" s="45"/>
+      <c r="G31" s="45"/>
+      <c r="H31" s="45"/>
     </row>
     <row r="32" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="48"/>
-      <c r="B32" s="48"/>
-      <c r="C32" s="48"/>
-      <c r="D32" s="48"/>
-      <c r="E32" s="48"/>
-      <c r="F32" s="48"/>
-      <c r="G32" s="48"/>
-      <c r="H32" s="48"/>
-      <c r="J32" s="0"/>
-      <c r="K32" s="0"/>
+      <c r="A32" s="45"/>
+      <c r="B32" s="45"/>
+      <c r="C32" s="45"/>
+      <c r="D32" s="45"/>
+      <c r="E32" s="45"/>
+      <c r="F32" s="45"/>
+      <c r="G32" s="45"/>
+      <c r="H32" s="45"/>
     </row>
     <row r="33" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="48"/>
-      <c r="B33" s="48"/>
-      <c r="C33" s="48"/>
-      <c r="D33" s="48"/>
-      <c r="E33" s="48"/>
-      <c r="F33" s="48"/>
-      <c r="G33" s="48"/>
-      <c r="H33" s="48"/>
-      <c r="J33" s="0"/>
-      <c r="K33" s="0"/>
+      <c r="A33" s="45"/>
+      <c r="B33" s="45"/>
+      <c r="C33" s="45"/>
+      <c r="D33" s="45"/>
+      <c r="E33" s="45"/>
+      <c r="F33" s="45"/>
+      <c r="G33" s="45"/>
+      <c r="H33" s="45"/>
     </row>
     <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="48"/>
-      <c r="B34" s="48"/>
-      <c r="C34" s="48"/>
-      <c r="D34" s="48"/>
-      <c r="E34" s="48"/>
-      <c r="F34" s="48"/>
-      <c r="G34" s="48"/>
-      <c r="H34" s="48"/>
-      <c r="J34" s="0"/>
-      <c r="K34" s="0"/>
+      <c r="A34" s="45"/>
+      <c r="B34" s="45"/>
+      <c r="C34" s="45"/>
+      <c r="D34" s="45"/>
+      <c r="E34" s="45"/>
+      <c r="F34" s="45"/>
+      <c r="G34" s="45"/>
+      <c r="H34" s="45"/>
     </row>
     <row r="35" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="48"/>
-      <c r="B35" s="48"/>
-      <c r="C35" s="48"/>
-      <c r="D35" s="48"/>
-      <c r="E35" s="48"/>
-      <c r="F35" s="48"/>
-      <c r="G35" s="48"/>
-      <c r="H35" s="48"/>
-      <c r="J35" s="0"/>
-      <c r="K35" s="0"/>
+      <c r="A35" s="45"/>
+      <c r="B35" s="45"/>
+      <c r="C35" s="45"/>
+      <c r="D35" s="45"/>
+      <c r="E35" s="45"/>
+      <c r="F35" s="45"/>
+      <c r="G35" s="45"/>
+      <c r="H35" s="45"/>
     </row>
     <row r="36" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="48"/>
-      <c r="B36" s="48"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
-      <c r="H36" s="48"/>
-      <c r="J36" s="0"/>
-      <c r="K36" s="0"/>
+      <c r="A36" s="45"/>
+      <c r="B36" s="45"/>
+      <c r="C36" s="45"/>
+      <c r="D36" s="45"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45"/>
+      <c r="H36" s="45"/>
     </row>
     <row r="37" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="48"/>
-      <c r="B37" s="48"/>
-      <c r="C37" s="48"/>
-      <c r="D37" s="48"/>
-      <c r="E37" s="48"/>
-      <c r="F37" s="48"/>
-      <c r="G37" s="48"/>
-      <c r="H37" s="48"/>
-      <c r="J37" s="0"/>
-      <c r="K37" s="0"/>
+      <c r="A37" s="45"/>
+      <c r="B37" s="45"/>
+      <c r="C37" s="45"/>
+      <c r="D37" s="45"/>
+      <c r="E37" s="45"/>
+      <c r="F37" s="45"/>
+      <c r="G37" s="45"/>
+      <c r="H37" s="45"/>
     </row>
     <row r="38" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="48"/>
-      <c r="B38" s="48"/>
-      <c r="C38" s="48"/>
-      <c r="D38" s="48"/>
-      <c r="E38" s="48"/>
-      <c r="F38" s="48"/>
-      <c r="G38" s="48"/>
-      <c r="H38" s="48"/>
-      <c r="J38" s="0"/>
-      <c r="K38" s="0"/>
+      <c r="A38" s="45"/>
+      <c r="B38" s="45"/>
+      <c r="C38" s="45"/>
+      <c r="D38" s="45"/>
+      <c r="E38" s="45"/>
+      <c r="F38" s="45"/>
+      <c r="G38" s="45"/>
+      <c r="H38" s="45"/>
     </row>
     <row r="39" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="48"/>
-      <c r="B39" s="48"/>
-      <c r="C39" s="48"/>
-      <c r="D39" s="48"/>
-      <c r="E39" s="48"/>
-      <c r="F39" s="48"/>
-      <c r="G39" s="48"/>
-      <c r="H39" s="48"/>
-      <c r="J39" s="0"/>
-      <c r="K39" s="0"/>
+      <c r="A39" s="45"/>
+      <c r="B39" s="45"/>
+      <c r="C39" s="45"/>
+      <c r="D39" s="45"/>
+      <c r="E39" s="45"/>
+      <c r="F39" s="45"/>
+      <c r="G39" s="45"/>
+      <c r="H39" s="45"/>
     </row>
     <row r="40" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="48"/>
-      <c r="B40" s="48"/>
-      <c r="C40" s="48"/>
-      <c r="D40" s="48"/>
-      <c r="E40" s="48"/>
-      <c r="F40" s="48"/>
-      <c r="G40" s="48"/>
-      <c r="H40" s="48"/>
-      <c r="J40" s="0"/>
-      <c r="K40" s="0"/>
+      <c r="A40" s="45"/>
+      <c r="B40" s="45"/>
+      <c r="C40" s="45"/>
+      <c r="D40" s="45"/>
+      <c r="E40" s="45"/>
+      <c r="F40" s="45"/>
+      <c r="G40" s="45"/>
+      <c r="H40" s="45"/>
     </row>
     <row r="41" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="48"/>
-      <c r="B41" s="48"/>
-      <c r="C41" s="48"/>
-      <c r="D41" s="48"/>
-      <c r="E41" s="48"/>
-      <c r="F41" s="48"/>
-      <c r="G41" s="48"/>
-      <c r="H41" s="48"/>
-      <c r="J41" s="0"/>
-      <c r="K41" s="0"/>
+      <c r="A41" s="45"/>
+      <c r="B41" s="45"/>
+      <c r="C41" s="45"/>
+      <c r="D41" s="45"/>
+      <c r="E41" s="45"/>
+      <c r="F41" s="45"/>
+      <c r="G41" s="45"/>
+      <c r="H41" s="45"/>
     </row>
     <row r="42" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="48"/>
-      <c r="B42" s="48"/>
-      <c r="C42" s="48"/>
-      <c r="D42" s="48"/>
-      <c r="E42" s="48"/>
-      <c r="F42" s="48"/>
-      <c r="G42" s="48"/>
-      <c r="H42" s="48"/>
-      <c r="J42" s="0"/>
-      <c r="K42" s="0"/>
+      <c r="A42" s="45"/>
+      <c r="B42" s="45"/>
+      <c r="C42" s="45"/>
+      <c r="D42" s="45"/>
+      <c r="E42" s="45"/>
+      <c r="F42" s="45"/>
+      <c r="G42" s="45"/>
+      <c r="H42" s="45"/>
     </row>
     <row r="43" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="48"/>
-      <c r="B43" s="48"/>
-      <c r="C43" s="48"/>
-      <c r="D43" s="48"/>
-      <c r="E43" s="48"/>
-      <c r="F43" s="48"/>
-      <c r="G43" s="48"/>
-      <c r="H43" s="48"/>
-      <c r="J43" s="0"/>
-      <c r="K43" s="0"/>
+      <c r="A43" s="45"/>
+      <c r="B43" s="45"/>
+      <c r="C43" s="45"/>
+      <c r="D43" s="45"/>
+      <c r="E43" s="45"/>
+      <c r="F43" s="45"/>
+      <c r="G43" s="45"/>
+      <c r="H43" s="45"/>
     </row>
     <row r="44" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="48"/>
-      <c r="B44" s="48"/>
-      <c r="C44" s="48"/>
-      <c r="D44" s="48"/>
-      <c r="E44" s="48"/>
-      <c r="F44" s="48"/>
-      <c r="G44" s="48"/>
-      <c r="H44" s="48"/>
-      <c r="J44" s="0"/>
-      <c r="K44" s="0"/>
+      <c r="A44" s="45"/>
+      <c r="B44" s="45"/>
+      <c r="C44" s="45"/>
+      <c r="D44" s="45"/>
+      <c r="E44" s="45"/>
+      <c r="F44" s="45"/>
+      <c r="G44" s="45"/>
+      <c r="H44" s="45"/>
     </row>
     <row r="45" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="48"/>
-      <c r="B45" s="48"/>
-      <c r="C45" s="48"/>
-      <c r="D45" s="48"/>
-      <c r="E45" s="48"/>
-      <c r="F45" s="48"/>
-      <c r="G45" s="48"/>
-      <c r="H45" s="48"/>
-      <c r="J45" s="0"/>
-      <c r="K45" s="0"/>
+      <c r="A45" s="45"/>
+      <c r="B45" s="45"/>
+      <c r="C45" s="45"/>
+      <c r="D45" s="45"/>
+      <c r="E45" s="45"/>
+      <c r="F45" s="45"/>
+      <c r="G45" s="45"/>
+      <c r="H45" s="45"/>
     </row>
     <row r="46" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="48"/>
-      <c r="B46" s="48"/>
-      <c r="C46" s="48"/>
-      <c r="D46" s="48"/>
-      <c r="E46" s="48"/>
-      <c r="F46" s="48"/>
-      <c r="G46" s="48"/>
-      <c r="H46" s="48"/>
-      <c r="J46" s="0"/>
-      <c r="K46" s="0"/>
+      <c r="A46" s="45"/>
+      <c r="B46" s="45"/>
+      <c r="C46" s="45"/>
+      <c r="D46" s="45"/>
+      <c r="E46" s="45"/>
+      <c r="F46" s="45"/>
+      <c r="G46" s="45"/>
+      <c r="H46" s="45"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4290,79 +4274,79 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="65" t="s">
+      <c r="B1" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="65" t="s">
+      <c r="C1" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="65" t="s">
+      <c r="D1" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="65" t="s">
+      <c r="E1" s="62" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="179.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="66"/>
-      <c r="B2" s="67" t="s">
+      <c r="A2" s="63"/>
+      <c r="B2" s="64" t="s">
         <v>111</v>
       </c>
-      <c r="C2" s="68" t="s">
+      <c r="C2" s="65" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="68" t="s">
+      <c r="D2" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="68" t="s">
+      <c r="E2" s="65" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="101.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="69"/>
-      <c r="B3" s="69" t="s">
+      <c r="A3" s="66"/>
+      <c r="B3" s="66" t="s">
         <v>114</v>
       </c>
-      <c r="C3" s="69" t="s">
+      <c r="C3" s="66" t="s">
         <v>115</v>
       </c>
-      <c r="D3" s="70" t="s">
+      <c r="D3" s="67" t="s">
         <v>113</v>
       </c>
-      <c r="E3" s="70" t="s">
+      <c r="E3" s="67" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="86.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="71"/>
-      <c r="B4" s="71" t="s">
+      <c r="A4" s="68"/>
+      <c r="B4" s="68" t="s">
         <v>117</v>
       </c>
-      <c r="C4" s="71" t="s">
+      <c r="C4" s="68" t="s">
         <v>118</v>
       </c>
-      <c r="D4" s="72" t="s">
+      <c r="D4" s="69" t="s">
         <v>116</v>
       </c>
-      <c r="E4" s="72" t="s">
+      <c r="E4" s="69" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="89.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="71"/>
-      <c r="B5" s="71" t="s">
+      <c r="A5" s="68"/>
+      <c r="B5" s="68" t="s">
         <v>120</v>
       </c>
-      <c r="C5" s="72" t="s">
+      <c r="C5" s="69" t="s">
         <v>121</v>
       </c>
-      <c r="D5" s="72" t="s">
+      <c r="D5" s="69" t="s">
         <v>119</v>
       </c>
-      <c r="E5" s="71"/>
+      <c r="E5" s="68"/>
     </row>
     <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -4389,21 +4373,21 @@
   <sheetFormatPr defaultColWidth="10.18359375" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="73" width="92.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="74" width="56.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="73" width="61.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="73" width="68.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="70" width="92.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="71" width="56.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="70" width="61.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="70" width="68.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="59.58"/>
   </cols>
   <sheetData>
-    <row r="1" s="78" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="75" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="75" t="s">
+      <c r="C1" s="72" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
@@ -4412,11 +4396,11 @@
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="76" t="s">
+      <c r="F1" s="73" t="s">
         <v>122</v>
       </c>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="74"/>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6"/>
@@ -4432,9 +4416,9 @@
       <c r="E2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="79"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
     </row>
     <row r="3" customFormat="false" ht="201.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6"/>
@@ -4450,9 +4434,9 @@
       <c r="E3" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="F3" s="81"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
     </row>
     <row r="4" customFormat="false" ht="76.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6"/>
@@ -4468,9 +4452,9 @@
       <c r="E4" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="81"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="80"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
     </row>
     <row r="5" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6"/>
@@ -4486,9 +4470,9 @@
       <c r="E5" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="81"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
     </row>
     <row r="6" s="2" customFormat="true" ht="73.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
@@ -4504,9 +4488,9 @@
       <c r="E6" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F6" s="81"/>
-      <c r="G6" s="80"/>
-      <c r="H6" s="80"/>
+      <c r="F6" s="78"/>
+      <c r="G6" s="77"/>
+      <c r="H6" s="77"/>
     </row>
     <row r="7" s="2" customFormat="true" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
@@ -4524,7 +4508,7 @@
       <c r="E7" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="F7" s="79"/>
+      <c r="F7" s="76"/>
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
     </row>
@@ -4544,9 +4528,9 @@
       <c r="E8" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="F8" s="79"/>
-      <c r="G8" s="80"/>
-      <c r="H8" s="80"/>
+      <c r="F8" s="76"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="77"/>
     </row>
     <row r="9" s="2" customFormat="true" ht="241.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
@@ -4564,15 +4548,15 @@
       <c r="E9" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="F9" s="79"/>
-      <c r="G9" s="80"/>
-      <c r="H9" s="80"/>
+      <c r="F9" s="76"/>
+      <c r="G9" s="77"/>
+      <c r="H9" s="77"/>
     </row>
     <row r="10" s="2" customFormat="true" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="82" t="s">
+      <c r="B10" s="79" t="s">
         <v>138</v>
       </c>
       <c r="C10" s="33" t="s">
@@ -4584,11 +4568,11 @@
       <c r="E10" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="F10" s="83"/>
-      <c r="G10" s="80"/>
-      <c r="H10" s="80"/>
-    </row>
-    <row r="11" s="85" customFormat="true" ht="225.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F10" s="80"/>
+      <c r="G10" s="77"/>
+      <c r="H10" s="77"/>
+    </row>
+    <row r="11" s="82" customFormat="true" ht="225.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
         <v>33</v>
       </c>
@@ -4604,9 +4588,9 @@
       <c r="E11" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="F11" s="84"/>
-      <c r="G11" s="80"/>
-      <c r="H11" s="80"/>
+      <c r="F11" s="81"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
     </row>
     <row r="12" customFormat="false" ht="176.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
@@ -4625,8 +4609,8 @@
       <c r="F12" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="G12" s="80"/>
-      <c r="H12" s="80"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="77"/>
     </row>
     <row r="13" customFormat="false" ht="211.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
@@ -4643,18 +4627,18 @@
       </c>
       <c r="E13" s="15"/>
       <c r="F13" s="23"/>
-      <c r="G13" s="80"/>
-      <c r="H13" s="80"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="77"/>
     </row>
     <row r="14" customFormat="false" ht="211.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="86"/>
-      <c r="B14" s="87"/>
-      <c r="C14" s="87"/>
-      <c r="D14" s="87"/>
-      <c r="E14" s="87"/>
+      <c r="A14" s="83"/>
+      <c r="B14" s="84"/>
+      <c r="C14" s="84"/>
+      <c r="D14" s="84"/>
+      <c r="E14" s="84"/>
       <c r="F14" s="28"/>
-      <c r="G14" s="80"/>
-      <c r="H14" s="80"/>
+      <c r="G14" s="77"/>
+      <c r="H14" s="77"/>
     </row>
     <row r="15" customFormat="false" ht="211.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="29"/>
@@ -4663,8 +4647,8 @@
       <c r="D15" s="30"/>
       <c r="E15" s="30"/>
       <c r="F15" s="31"/>
-      <c r="G15" s="80"/>
-      <c r="H15" s="80"/>
+      <c r="G15" s="77"/>
+      <c r="H15" s="77"/>
     </row>
     <row r="16" customFormat="false" ht="159.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="32" t="s">
@@ -4683,8 +4667,8 @@
         <v>149</v>
       </c>
       <c r="F16" s="34"/>
-      <c r="G16" s="85"/>
-      <c r="H16" s="85"/>
+      <c r="G16" s="82"/>
+      <c r="H16" s="82"/>
     </row>
     <row r="17" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="35" t="s">
@@ -4723,27 +4707,27 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="88" t="s">
+      <c r="A19" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="89" t="s">
+      <c r="B19" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="C19" s="89" t="s">
+      <c r="C19" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="D19" s="89" t="s">
+      <c r="D19" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="E19" s="89"/>
-      <c r="F19" s="41"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="23"/>
     </row>
     <row r="20" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="86"/>
-      <c r="B20" s="87"/>
-      <c r="C20" s="87"/>
-      <c r="D20" s="87"/>
-      <c r="E20" s="87"/>
+      <c r="A20" s="83"/>
+      <c r="B20" s="84"/>
+      <c r="C20" s="84"/>
+      <c r="D20" s="84"/>
+      <c r="E20" s="84"/>
       <c r="F20" s="28"/>
     </row>
     <row r="21" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4758,7 +4742,7 @@
       <c r="A22" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="82" t="s">
+      <c r="B22" s="79" t="s">
         <v>157</v>
       </c>
       <c r="C22" s="33" t="s">
@@ -4770,9 +4754,9 @@
       <c r="E22" s="33" t="s">
         <v>158</v>
       </c>
-      <c r="F22" s="83"/>
-      <c r="G22" s="80"/>
-      <c r="H22" s="80"/>
+      <c r="F22" s="80"/>
+      <c r="G22" s="77"/>
+      <c r="H22" s="77"/>
     </row>
     <row r="23" customFormat="false" ht="210.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="21" t="s">
@@ -4790,57 +4774,57 @@
       <c r="E23" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="F23" s="84"/>
-      <c r="G23" s="80"/>
-      <c r="H23" s="80"/>
+      <c r="F23" s="81"/>
+      <c r="G23" s="77"/>
+      <c r="H23" s="77"/>
     </row>
     <row r="24" customFormat="false" ht="177.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="88" t="s">
+      <c r="A24" s="85" t="s">
         <v>57</v>
       </c>
-      <c r="B24" s="89" t="s">
+      <c r="B24" s="86" t="s">
         <v>161</v>
       </c>
-      <c r="C24" s="89" t="s">
+      <c r="C24" s="86" t="s">
         <v>40</v>
       </c>
-      <c r="D24" s="89" t="s">
+      <c r="D24" s="86" t="s">
         <v>162</v>
       </c>
-      <c r="E24" s="89"/>
-      <c r="F24" s="41" t="s">
+      <c r="E24" s="86"/>
+      <c r="F24" s="87" t="s">
         <v>163</v>
       </c>
-      <c r="G24" s="80"/>
-      <c r="H24" s="80"/>
+      <c r="G24" s="77"/>
+      <c r="H24" s="77"/>
     </row>
     <row r="25" customFormat="false" ht="202.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="86" t="s">
+      <c r="A25" s="83" t="s">
         <v>57</v>
       </c>
-      <c r="B25" s="87" t="s">
+      <c r="B25" s="84" t="s">
         <v>164</v>
       </c>
-      <c r="C25" s="87" t="s">
+      <c r="C25" s="84" t="s">
         <v>44</v>
       </c>
-      <c r="D25" s="87" t="s">
+      <c r="D25" s="84" t="s">
         <v>165</v>
       </c>
-      <c r="E25" s="87"/>
+      <c r="E25" s="84"/>
       <c r="F25" s="28"/>
-      <c r="G25" s="80"/>
-      <c r="H25" s="80"/>
+      <c r="G25" s="77"/>
+      <c r="H25" s="77"/>
     </row>
     <row r="26" customFormat="false" ht="202.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="86"/>
-      <c r="B26" s="87"/>
-      <c r="C26" s="87"/>
-      <c r="D26" s="87"/>
-      <c r="E26" s="87"/>
+      <c r="A26" s="83"/>
+      <c r="B26" s="84"/>
+      <c r="C26" s="84"/>
+      <c r="D26" s="84"/>
+      <c r="E26" s="84"/>
       <c r="F26" s="28"/>
-      <c r="G26" s="80"/>
-      <c r="H26" s="80"/>
+      <c r="G26" s="77"/>
+      <c r="H26" s="77"/>
     </row>
     <row r="27" customFormat="false" ht="202.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="29"/>
@@ -4849,8 +4833,8 @@
       <c r="D27" s="30"/>
       <c r="E27" s="30"/>
       <c r="F27" s="31"/>
-      <c r="G27" s="80"/>
-      <c r="H27" s="80"/>
+      <c r="G27" s="77"/>
+      <c r="H27" s="77"/>
     </row>
     <row r="28" customFormat="false" ht="156.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="32" t="s">
@@ -4869,8 +4853,8 @@
         <v>168</v>
       </c>
       <c r="F28" s="34"/>
-      <c r="G28" s="80"/>
-      <c r="H28" s="80"/>
+      <c r="G28" s="77"/>
+      <c r="H28" s="77"/>
     </row>
     <row r="29" customFormat="false" ht="248.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="35" t="s">
@@ -4889,8 +4873,8 @@
         <v>170</v>
       </c>
       <c r="F29" s="36"/>
-      <c r="G29" s="80"/>
-      <c r="H29" s="80"/>
+      <c r="G29" s="77"/>
+      <c r="H29" s="77"/>
     </row>
     <row r="30" customFormat="false" ht="100.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="21" t="s">
@@ -4909,114 +4893,114 @@
       <c r="F30" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="G30" s="80"/>
-      <c r="H30" s="80"/>
+      <c r="G30" s="77"/>
+      <c r="H30" s="77"/>
     </row>
     <row r="31" customFormat="false" ht="108.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="88" t="s">
+      <c r="A31" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="B31" s="89" t="s">
+      <c r="B31" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="C31" s="89" t="s">
+      <c r="C31" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="D31" s="89" t="s">
+      <c r="D31" s="15" t="s">
         <v>175</v>
       </c>
-      <c r="E31" s="89"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="80"/>
-      <c r="H31" s="80"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="77"/>
+      <c r="H31" s="77"/>
     </row>
     <row r="32" customFormat="false" ht="108.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="86"/>
-      <c r="B32" s="87"/>
-      <c r="C32" s="87"/>
-      <c r="D32" s="87"/>
-      <c r="E32" s="87"/>
+      <c r="A32" s="83"/>
+      <c r="B32" s="84"/>
+      <c r="C32" s="84"/>
+      <c r="D32" s="84"/>
+      <c r="E32" s="84"/>
       <c r="F32" s="28"/>
-      <c r="G32" s="80"/>
-      <c r="H32" s="80"/>
+      <c r="G32" s="77"/>
+      <c r="H32" s="77"/>
     </row>
     <row r="33" customFormat="false" ht="130.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="29"/>
-      <c r="B33" s="90"/>
+      <c r="B33" s="88"/>
       <c r="C33" s="30"/>
-      <c r="D33" s="90"/>
-      <c r="E33" s="90"/>
-      <c r="F33" s="91"/>
-      <c r="G33" s="80"/>
-      <c r="H33" s="80"/>
+      <c r="D33" s="88"/>
+      <c r="E33" s="88"/>
+      <c r="F33" s="89"/>
+      <c r="G33" s="77"/>
+      <c r="H33" s="77"/>
     </row>
     <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G34" s="80"/>
-      <c r="H34" s="80"/>
+      <c r="G34" s="77"/>
+      <c r="H34" s="77"/>
     </row>
     <row r="35" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G35" s="80"/>
-      <c r="H35" s="80"/>
+      <c r="G35" s="77"/>
+      <c r="H35" s="77"/>
     </row>
     <row r="36" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G36" s="80"/>
-      <c r="H36" s="80"/>
+      <c r="G36" s="77"/>
+      <c r="H36" s="77"/>
     </row>
     <row r="37" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G37" s="80"/>
-      <c r="H37" s="80"/>
+      <c r="G37" s="77"/>
+      <c r="H37" s="77"/>
     </row>
     <row r="38" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G38" s="80"/>
-      <c r="H38" s="80"/>
+      <c r="G38" s="77"/>
+      <c r="H38" s="77"/>
     </row>
     <row r="39" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G39" s="80"/>
-      <c r="H39" s="80"/>
+      <c r="G39" s="77"/>
+      <c r="H39" s="77"/>
     </row>
     <row r="40" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G40" s="80"/>
-      <c r="H40" s="80"/>
+      <c r="G40" s="77"/>
+      <c r="H40" s="77"/>
     </row>
     <row r="41" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G41" s="80"/>
-      <c r="H41" s="80"/>
+      <c r="G41" s="77"/>
+      <c r="H41" s="77"/>
     </row>
     <row r="42" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G42" s="80"/>
-      <c r="H42" s="80"/>
+      <c r="G42" s="77"/>
+      <c r="H42" s="77"/>
     </row>
     <row r="43" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G43" s="80"/>
-      <c r="H43" s="80"/>
+      <c r="G43" s="77"/>
+      <c r="H43" s="77"/>
     </row>
     <row r="44" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G44" s="80"/>
-      <c r="H44" s="80"/>
+      <c r="G44" s="77"/>
+      <c r="H44" s="77"/>
     </row>
     <row r="45" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G45" s="80"/>
-      <c r="H45" s="80"/>
+      <c r="G45" s="77"/>
+      <c r="H45" s="77"/>
     </row>
     <row r="46" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G46" s="80"/>
-      <c r="H46" s="80"/>
+      <c r="G46" s="77"/>
+      <c r="H46" s="77"/>
     </row>
     <row r="47" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G47" s="80"/>
-      <c r="H47" s="80"/>
+      <c r="G47" s="77"/>
+      <c r="H47" s="77"/>
     </row>
     <row r="48" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G48" s="80"/>
-      <c r="H48" s="80"/>
+      <c r="G48" s="77"/>
+      <c r="H48" s="77"/>
     </row>
     <row r="49" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G49" s="80"/>
-      <c r="H49" s="80"/>
+      <c r="G49" s="77"/>
+      <c r="H49" s="77"/>
     </row>
     <row r="50" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G50" s="80"/>
-      <c r="H50" s="80"/>
+      <c r="G50" s="77"/>
+      <c r="H50" s="77"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -5048,531 +5032,531 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="11" style="3" width="10.16"/>
   </cols>
   <sheetData>
-    <row r="1" s="95" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="42" t="s">
+    <row r="1" s="93" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="43" t="s">
+      <c r="B1" s="40" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="43" t="s">
+      <c r="C1" s="40" t="s">
         <v>176</v>
       </c>
-      <c r="D1" s="43" t="s">
+      <c r="D1" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="E1" s="92" t="s">
+      <c r="E1" s="90" t="s">
         <v>177</v>
       </c>
-      <c r="F1" s="92" t="s">
+      <c r="F1" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="93" t="s">
+      <c r="G1" s="91" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="93" t="s">
+      <c r="H1" s="91" t="s">
         <v>57</v>
       </c>
-      <c r="I1" s="93" t="s">
+      <c r="I1" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="J1" s="93" t="s">
+      <c r="J1" s="91" t="s">
         <v>68</v>
       </c>
-      <c r="K1" s="94"/>
+      <c r="K1" s="92"/>
       <c r="XFD1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="96" t="s">
+      <c r="A2" s="94" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="97" t="n">
+      <c r="B2" s="95" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="97" t="n">
+      <c r="C2" s="95" t="n">
         <v>2273097</v>
       </c>
-      <c r="D2" s="98" t="n">
+      <c r="D2" s="96" t="n">
         <v>2095051</v>
       </c>
-      <c r="E2" s="48" t="n">
+      <c r="E2" s="45" t="n">
         <v>1676040</v>
       </c>
-      <c r="F2" s="52" t="n">
+      <c r="F2" s="49" t="n">
         <v>1661804</v>
       </c>
-      <c r="G2" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H2" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I2" s="48" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J2" s="50" t="n">
+      <c r="G2" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H2" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I2" s="45" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J2" s="47" t="n">
         <v>10000</v>
       </c>
       <c r="L2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="96" t="s">
+      <c r="A3" s="94" t="s">
         <v>178</v>
       </c>
-      <c r="B3" s="97" t="n">
+      <c r="B3" s="95" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="97" t="n">
+      <c r="C3" s="95" t="n">
         <v>231073</v>
       </c>
-      <c r="D3" s="98" t="n">
+      <c r="D3" s="96" t="n">
         <v>172846</v>
       </c>
-      <c r="E3" s="48" t="n">
+      <c r="E3" s="45" t="n">
         <v>138277</v>
       </c>
-      <c r="F3" s="52" t="n">
+      <c r="F3" s="49" t="n">
         <v>135226</v>
       </c>
-      <c r="G3" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H3" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I3" s="48" t="n">
+      <c r="G3" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H3" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I3" s="45" t="n">
         <v>9656</v>
       </c>
-      <c r="J3" s="50" t="n">
+      <c r="J3" s="47" t="n">
         <v>9968</v>
       </c>
       <c r="L3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="96" t="s">
+      <c r="A4" s="94" t="s">
         <v>179</v>
       </c>
-      <c r="B4" s="97" t="n">
+      <c r="B4" s="95" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="97" t="n">
+      <c r="C4" s="95" t="n">
         <v>128027</v>
       </c>
-      <c r="D4" s="98" t="n">
+      <c r="D4" s="96" t="n">
         <v>128014</v>
       </c>
-      <c r="E4" s="48" t="n">
+      <c r="E4" s="45" t="n">
         <v>102411</v>
       </c>
-      <c r="F4" s="52" t="n">
+      <c r="F4" s="49" t="n">
         <v>101341</v>
       </c>
-      <c r="G4" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H4" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I4" s="48" t="n">
+      <c r="G4" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H4" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I4" s="45" t="n">
         <v>9765</v>
       </c>
-      <c r="J4" s="50" t="n">
+      <c r="J4" s="47" t="n">
         <v>9995</v>
       </c>
       <c r="L4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="96" t="s">
+      <c r="A5" s="94" t="s">
         <v>180</v>
       </c>
-      <c r="B5" s="97" t="n">
+      <c r="B5" s="95" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="97" t="n">
+      <c r="C5" s="95" t="n">
         <v>158930</v>
       </c>
-      <c r="D5" s="98" t="n">
+      <c r="D5" s="96" t="n">
         <v>90694</v>
       </c>
-      <c r="E5" s="48" t="n">
+      <c r="E5" s="45" t="n">
         <v>72555</v>
       </c>
-      <c r="F5" s="52" t="n">
+      <c r="F5" s="49" t="n">
         <v>66678</v>
       </c>
-      <c r="G5" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H5" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I5" s="48" t="n">
+      <c r="G5" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H5" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I5" s="45" t="n">
         <v>9712</v>
       </c>
-      <c r="J5" s="50" t="n">
+      <c r="J5" s="47" t="n">
         <v>9960</v>
       </c>
       <c r="L5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="96" t="s">
+      <c r="A6" s="94" t="s">
         <v>181</v>
       </c>
-      <c r="B6" s="97" t="n">
+      <c r="B6" s="95" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="97" t="n">
+      <c r="C6" s="95" t="n">
         <v>10293</v>
       </c>
-      <c r="D6" s="98" t="n">
+      <c r="D6" s="96" t="n">
         <v>10286</v>
       </c>
-      <c r="E6" s="48" t="n">
+      <c r="E6" s="45" t="n">
         <v>8229</v>
       </c>
-      <c r="F6" s="52" t="n">
+      <c r="F6" s="49" t="n">
         <v>7672</v>
       </c>
-      <c r="G6" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H6" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I6" s="48" t="n">
+      <c r="G6" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H6" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I6" s="45" t="n">
         <v>9913</v>
       </c>
-      <c r="J6" s="50" t="n">
+      <c r="J6" s="47" t="n">
         <v>9958</v>
       </c>
       <c r="L6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="96" t="s">
+      <c r="A7" s="94" t="s">
         <v>182</v>
       </c>
-      <c r="B7" s="97" t="n">
+      <c r="B7" s="95" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="97" t="n">
+      <c r="C7" s="95" t="n">
         <v>7938</v>
       </c>
-      <c r="D7" s="98" t="n">
+      <c r="D7" s="96" t="n">
         <v>5931</v>
       </c>
-      <c r="E7" s="48" t="n">
+      <c r="E7" s="45" t="n">
         <v>4745</v>
       </c>
-      <c r="F7" s="52" t="n">
+      <c r="F7" s="49" t="n">
         <v>4648</v>
       </c>
-      <c r="G7" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H7" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I7" s="48" t="n">
+      <c r="G7" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H7" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I7" s="45" t="n">
         <v>9908</v>
       </c>
-      <c r="J7" s="50" t="n">
+      <c r="J7" s="47" t="n">
         <v>9923</v>
       </c>
       <c r="L7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="96" t="s">
+      <c r="A8" s="94" t="s">
         <v>183</v>
       </c>
-      <c r="B8" s="97" t="n">
+      <c r="B8" s="95" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="97" t="n">
+      <c r="C8" s="95" t="n">
         <v>5796</v>
       </c>
-      <c r="D8" s="98" t="n">
+      <c r="D8" s="96" t="n">
         <v>5385</v>
       </c>
-      <c r="E8" s="48" t="n">
+      <c r="E8" s="45" t="n">
         <v>4308</v>
       </c>
-      <c r="F8" s="52" t="n">
+      <c r="F8" s="49" t="n">
         <v>4034</v>
       </c>
-      <c r="G8" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H8" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I8" s="48" t="n">
+      <c r="G8" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H8" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I8" s="45" t="n">
         <v>9637</v>
       </c>
-      <c r="J8" s="50" t="n">
+      <c r="J8" s="47" t="n">
         <v>9785</v>
       </c>
       <c r="L8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="96" t="s">
+      <c r="A9" s="94" t="s">
         <v>184</v>
       </c>
-      <c r="B9" s="97" t="n">
+      <c r="B9" s="95" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="97" t="n">
+      <c r="C9" s="95" t="n">
         <v>5499</v>
       </c>
-      <c r="D9" s="98" t="n">
+      <c r="D9" s="96" t="n">
         <v>5228</v>
       </c>
-      <c r="E9" s="48" t="n">
+      <c r="E9" s="45" t="n">
         <v>4182</v>
       </c>
-      <c r="F9" s="52" t="n">
+      <c r="F9" s="49" t="n">
         <v>3921</v>
       </c>
-      <c r="G9" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H9" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I9" s="48" t="n">
+      <c r="G9" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H9" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I9" s="45" t="n">
         <v>9814</v>
       </c>
-      <c r="J9" s="50" t="n">
+      <c r="J9" s="47" t="n">
         <v>9872</v>
       </c>
       <c r="L9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="96" t="s">
+      <c r="A10" s="94" t="s">
         <v>185</v>
       </c>
-      <c r="B10" s="97" t="n">
+      <c r="B10" s="95" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="97" t="n">
+      <c r="C10" s="95" t="n">
         <v>5897</v>
       </c>
-      <c r="D10" s="98" t="n">
+      <c r="D10" s="96" t="n">
         <v>3219</v>
       </c>
-      <c r="E10" s="48" t="n">
+      <c r="E10" s="45" t="n">
         <v>2575</v>
       </c>
-      <c r="F10" s="52" t="n">
+      <c r="F10" s="49" t="n">
         <v>2369</v>
       </c>
-      <c r="G10" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H10" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I10" s="48" t="n">
+      <c r="G10" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H10" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I10" s="45" t="n">
         <v>9622</v>
       </c>
-      <c r="J10" s="50" t="n">
+      <c r="J10" s="47" t="n">
         <v>9637</v>
       </c>
       <c r="L10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="96" t="s">
+      <c r="A11" s="94" t="s">
         <v>89</v>
       </c>
-      <c r="B11" s="97" t="n">
+      <c r="B11" s="95" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="97" t="n">
+      <c r="C11" s="95" t="n">
         <v>1966</v>
       </c>
-      <c r="D11" s="98" t="n">
+      <c r="D11" s="96" t="n">
         <v>1948</v>
       </c>
-      <c r="E11" s="48" t="n">
+      <c r="E11" s="45" t="n">
         <v>1558</v>
       </c>
-      <c r="F11" s="52" t="n">
+      <c r="F11" s="49" t="n">
         <v>717</v>
       </c>
-      <c r="G11" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H11" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I11" s="48" t="n">
+      <c r="G11" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H11" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I11" s="45" t="n">
         <v>9832</v>
       </c>
-      <c r="J11" s="50" t="n">
+      <c r="J11" s="47" t="n">
         <v>9979</v>
       </c>
       <c r="L11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="96" t="s">
+      <c r="A12" s="94" t="s">
         <v>186</v>
       </c>
-      <c r="B12" s="97" t="n">
+      <c r="B12" s="95" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="97" t="n">
+      <c r="C12" s="95" t="n">
         <v>1507</v>
       </c>
-      <c r="D12" s="98" t="n">
+      <c r="D12" s="96" t="n">
         <v>1470</v>
       </c>
-      <c r="E12" s="48" t="n">
+      <c r="E12" s="45" t="n">
         <v>1176</v>
       </c>
-      <c r="F12" s="52" t="n">
+      <c r="F12" s="49" t="n">
         <v>469</v>
       </c>
-      <c r="G12" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H12" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I12" s="48" t="n">
+      <c r="G12" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H12" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I12" s="45" t="n">
         <v>5782</v>
       </c>
-      <c r="J12" s="50" t="n">
+      <c r="J12" s="47" t="n">
         <v>5793</v>
       </c>
       <c r="L12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="96" t="s">
+      <c r="A13" s="94" t="s">
         <v>187</v>
       </c>
-      <c r="B13" s="97" t="n">
+      <c r="B13" s="95" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="97" t="n">
+      <c r="C13" s="95" t="n">
         <v>652</v>
       </c>
-      <c r="D13" s="98" t="n">
+      <c r="D13" s="96" t="n">
         <v>652</v>
       </c>
-      <c r="E13" s="48" t="n">
+      <c r="E13" s="45" t="n">
         <v>522</v>
       </c>
-      <c r="F13" s="52" t="n">
+      <c r="F13" s="49" t="n">
         <v>47</v>
       </c>
-      <c r="G13" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H13" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I13" s="48" t="n">
+      <c r="G13" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H13" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I13" s="45" t="n">
         <v>5862</v>
       </c>
-      <c r="J13" s="50" t="n">
+      <c r="J13" s="47" t="n">
         <v>5871</v>
       </c>
       <c r="L13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="96" t="s">
+      <c r="A14" s="94" t="s">
         <v>188</v>
       </c>
-      <c r="B14" s="97" t="n">
+      <c r="B14" s="95" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="97" t="n">
+      <c r="C14" s="95" t="n">
         <v>36</v>
       </c>
-      <c r="D14" s="98" t="n">
+      <c r="D14" s="96" t="n">
         <v>36</v>
       </c>
-      <c r="E14" s="48" t="n">
+      <c r="E14" s="45" t="n">
         <v>29</v>
       </c>
-      <c r="F14" s="49" t="n">
+      <c r="F14" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H14" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I14" s="48" t="n">
+      <c r="G14" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H14" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I14" s="45" t="n">
         <v>9904</v>
       </c>
-      <c r="J14" s="50" t="n">
+      <c r="J14" s="47" t="n">
         <v>9934</v>
       </c>
       <c r="L14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="96" t="s">
+      <c r="A15" s="94" t="s">
         <v>189</v>
       </c>
-      <c r="B15" s="97" t="n">
+      <c r="B15" s="95" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="97" t="n">
+      <c r="C15" s="95" t="n">
         <v>21</v>
       </c>
-      <c r="D15" s="98" t="n">
+      <c r="D15" s="96" t="n">
         <v>21</v>
       </c>
-      <c r="E15" s="48" t="n">
+      <c r="E15" s="45" t="n">
         <v>17</v>
       </c>
-      <c r="F15" s="49" t="n">
+      <c r="F15" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H15" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I15" s="48" t="n">
+      <c r="G15" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H15" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I15" s="45" t="n">
         <v>9725</v>
       </c>
-      <c r="J15" s="50" t="n">
+      <c r="J15" s="47" t="n">
         <v>9727</v>
       </c>
       <c r="L15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="99" t="s">
+      <c r="A16" s="97" t="s">
         <v>190</v>
       </c>
-      <c r="B16" s="100" t="n">
+      <c r="B16" s="98" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="100" t="n">
+      <c r="C16" s="98" t="n">
         <v>11</v>
       </c>
-      <c r="D16" s="100" t="n">
+      <c r="D16" s="98" t="n">
         <v>11</v>
       </c>
-      <c r="E16" s="55" t="n">
+      <c r="E16" s="52" t="n">
         <v>9</v>
       </c>
-      <c r="F16" s="55" t="n">
+      <c r="F16" s="52" t="n">
         <v>9</v>
       </c>
-      <c r="G16" s="55" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H16" s="55" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I16" s="55" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J16" s="58" t="n">
+      <c r="G16" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H16" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I16" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J16" s="55" t="n">
         <v>10000</v>
       </c>
       <c r="L16" s="2"/>
@@ -5613,23 +5597,23 @@
       <c r="L17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E18" s="59"/>
-      <c r="F18" s="47"/>
+      <c r="E18" s="56"/>
+      <c r="F18" s="44"/>
       <c r="L18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E19" s="59"/>
-      <c r="F19" s="47"/>
+      <c r="E19" s="56"/>
+      <c r="F19" s="44"/>
       <c r="L19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="94" t="s">
+      <c r="A20" s="92" t="s">
         <v>100</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>79</v>
       </c>
-      <c r="D20" s="48" t="n">
+      <c r="D20" s="45" t="n">
         <v>48</v>
       </c>
       <c r="E20" s="3" t="n">
@@ -5647,54 +5631,54 @@
       <c r="L20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="48"/>
+      <c r="B21" s="45"/>
       <c r="L21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="48"/>
+      <c r="B22" s="45"/>
       <c r="L22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="48"/>
+      <c r="B23" s="45"/>
       <c r="L23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="48"/>
+      <c r="B24" s="45"/>
       <c r="L24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="48"/>
+      <c r="B25" s="45"/>
       <c r="L25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="48"/>
+      <c r="B26" s="45"/>
     </row>
     <row r="27" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="48"/>
+      <c r="B27" s="45"/>
     </row>
     <row r="28" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="48"/>
+      <c r="B28" s="45"/>
     </row>
     <row r="29" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="48"/>
+      <c r="B29" s="45"/>
     </row>
     <row r="30" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="48"/>
+      <c r="B30" s="45"/>
     </row>
     <row r="31" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="48"/>
+      <c r="B31" s="45"/>
     </row>
     <row r="32" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="48"/>
+      <c r="B32" s="45"/>
     </row>
     <row r="33" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="48"/>
+      <c r="B33" s="45"/>
     </row>
     <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="48"/>
+      <c r="B34" s="45"/>
     </row>
     <row r="35" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="48"/>
+      <c r="B35" s="45"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -5715,87 +5699,87 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultColWidth="10.16796875" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="101" width="45.65"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="101" width="74.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="101" width="74.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="101" width="55.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="101" width="52.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="99" width="45.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="99" width="74.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="99" width="74.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="99" width="55.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="99" width="52.63"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="65" t="s">
+      <c r="B1" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="65" t="s">
+      <c r="C1" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="65" t="s">
+      <c r="D1" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="65" t="s">
+      <c r="E1" s="62" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="179.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="66"/>
-      <c r="B2" s="67" t="s">
+      <c r="A2" s="63"/>
+      <c r="B2" s="64" t="s">
         <v>191</v>
       </c>
-      <c r="C2" s="68" t="s">
+      <c r="C2" s="65" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="68" t="s">
+      <c r="D2" s="65" t="s">
         <v>124</v>
       </c>
-      <c r="E2" s="68" t="s">
+      <c r="E2" s="65" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="131.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="67"/>
-      <c r="B3" s="67" t="s">
+      <c r="A3" s="64"/>
+      <c r="B3" s="64" t="s">
         <v>193</v>
       </c>
-      <c r="C3" s="67" t="s">
+      <c r="C3" s="64" t="s">
         <v>115</v>
       </c>
-      <c r="D3" s="68" t="s">
+      <c r="D3" s="65" t="s">
         <v>192</v>
       </c>
-      <c r="E3" s="68" t="s">
+      <c r="E3" s="65" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="141.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="67"/>
-      <c r="B4" s="67" t="s">
+      <c r="A4" s="64"/>
+      <c r="B4" s="64" t="s">
         <v>195</v>
       </c>
-      <c r="C4" s="67" t="s">
+      <c r="C4" s="64" t="s">
         <v>118</v>
       </c>
-      <c r="D4" s="68" t="s">
+      <c r="D4" s="65" t="s">
         <v>194</v>
       </c>
-      <c r="E4" s="68" t="s">
+      <c r="E4" s="65" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="176.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="67"/>
-      <c r="B5" s="67" t="s">
+      <c r="A5" s="64"/>
+      <c r="B5" s="64" t="s">
         <v>197</v>
       </c>
-      <c r="C5" s="68" t="s">
+      <c r="C5" s="65" t="s">
         <v>121</v>
       </c>
-      <c r="D5" s="68" t="s">
+      <c r="D5" s="65" t="s">
         <v>196</v>
       </c>
-      <c r="E5" s="67"/>
+      <c r="E5" s="64"/>
     </row>
     <row r="6" customFormat="false" ht="168.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
@@ -5817,138 +5801,138 @@
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultColWidth="10.16796875" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="101" width="45.65"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="101" width="74.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="101" width="74.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="101" width="55.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="101" width="52.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="99" width="45.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="99" width="74.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="99" width="74.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="99" width="55.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="99" width="52.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="71.46"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="65" t="s">
+      <c r="B1" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="65" t="s">
+      <c r="C1" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="65" t="s">
+      <c r="D1" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="65" t="s">
+      <c r="E1" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="102" t="s">
+      <c r="F1" s="100" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="179.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="63" t="s">
         <v>199</v>
       </c>
-      <c r="B2" s="67" t="s">
+      <c r="B2" s="64" t="s">
         <v>191</v>
       </c>
-      <c r="C2" s="68" t="s">
+      <c r="C2" s="65" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="68" t="s">
+      <c r="D2" s="65" t="s">
         <v>124</v>
       </c>
-      <c r="E2" s="68" t="s">
+      <c r="E2" s="65" t="s">
         <v>192</v>
       </c>
       <c r="F2" s="16"/>
     </row>
     <row r="3" customFormat="false" ht="179.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="66" t="s">
+      <c r="A3" s="63" t="s">
         <v>200</v>
       </c>
-      <c r="B3" s="67" t="s">
+      <c r="B3" s="64" t="s">
         <v>193</v>
       </c>
-      <c r="C3" s="68" t="s">
+      <c r="C3" s="65" t="s">
         <v>201</v>
       </c>
-      <c r="D3" s="68" t="s">
+      <c r="D3" s="65" t="s">
         <v>192</v>
       </c>
-      <c r="E3" s="68" t="s">
+      <c r="E3" s="65" t="s">
         <v>202</v>
       </c>
       <c r="F3" s="16"/>
     </row>
     <row r="4" customFormat="false" ht="131.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="103" t="s">
+      <c r="A4" s="101" t="s">
         <v>203</v>
       </c>
-      <c r="B4" s="104" t="s">
+      <c r="B4" s="102" t="s">
         <v>204</v>
       </c>
-      <c r="C4" s="105" t="s">
+      <c r="C4" s="103" t="s">
         <v>205</v>
       </c>
-      <c r="D4" s="105" t="s">
+      <c r="D4" s="103" t="s">
         <v>206</v>
       </c>
-      <c r="E4" s="105"/>
-      <c r="F4" s="106"/>
+      <c r="E4" s="103"/>
+      <c r="F4" s="104"/>
     </row>
     <row r="5" customFormat="false" ht="131.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="107" t="s">
+      <c r="A5" s="105" t="s">
         <v>207</v>
       </c>
-      <c r="B5" s="108" t="s">
+      <c r="B5" s="106" t="s">
         <v>208</v>
       </c>
-      <c r="C5" s="109" t="s">
+      <c r="C5" s="107" t="s">
         <v>209</v>
       </c>
-      <c r="D5" s="109" t="s">
+      <c r="D5" s="107" t="s">
         <v>206</v>
       </c>
-      <c r="E5" s="109"/>
-      <c r="F5" s="110"/>
+      <c r="E5" s="107"/>
+      <c r="F5" s="108"/>
     </row>
     <row r="6" customFormat="false" ht="141.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="111" t="s">
+      <c r="A6" s="109" t="s">
         <v>210</v>
       </c>
-      <c r="B6" s="112" t="s">
+      <c r="B6" s="110" t="s">
         <v>211</v>
       </c>
-      <c r="C6" s="112" t="s">
+      <c r="C6" s="110" t="s">
         <v>212</v>
       </c>
-      <c r="D6" s="113" t="s">
+      <c r="D6" s="111" t="s">
         <v>202</v>
       </c>
-      <c r="E6" s="113" t="s">
+      <c r="E6" s="111" t="s">
         <v>213</v>
       </c>
-      <c r="F6" s="114"/>
+      <c r="F6" s="112"/>
     </row>
     <row r="7" customFormat="false" ht="176.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="115" t="s">
+      <c r="A7" s="113" t="s">
         <v>210</v>
       </c>
-      <c r="B7" s="116" t="s">
+      <c r="B7" s="114" t="s">
         <v>214</v>
       </c>
-      <c r="C7" s="117" t="s">
+      <c r="C7" s="115" t="s">
         <v>205</v>
       </c>
-      <c r="D7" s="117" t="s">
+      <c r="D7" s="115" t="s">
         <v>215</v>
       </c>
-      <c r="E7" s="116"/>
-      <c r="F7" s="118"/>
+      <c r="E7" s="114"/>
+      <c r="F7" s="116"/>
     </row>
     <row r="8" customFormat="false" ht="168.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="119" t="s">
+      <c r="A8" s="117" t="s">
         <v>216</v>
       </c>
     </row>
@@ -5998,11 +5982,11 @@
       <c r="F1" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="80"/>
-      <c r="K1" s="80"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
     </row>
     <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6"/>
@@ -6017,11 +6001,11 @@
         <v>9</v>
       </c>
       <c r="F2" s="8"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
-      <c r="J2" s="80"/>
-      <c r="K2" s="80"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
     </row>
     <row r="3" customFormat="false" ht="74.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6"/>
@@ -6038,11 +6022,11 @@
         <v>9</v>
       </c>
       <c r="F3" s="8"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="80"/>
-      <c r="K3" s="80"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
+      <c r="K3" s="77"/>
     </row>
     <row r="4" customFormat="false" ht="173.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6"/>
@@ -6059,11 +6043,11 @@
         <v>222</v>
       </c>
       <c r="F4" s="8"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="80"/>
-      <c r="I4" s="80"/>
-      <c r="J4" s="80"/>
-      <c r="K4" s="80"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
+      <c r="K4" s="77"/>
     </row>
     <row r="5" customFormat="false" ht="85.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6"/>
@@ -6080,11 +6064,11 @@
         <v>9</v>
       </c>
       <c r="F5" s="8"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="80"/>
-      <c r="J5" s="80"/>
-      <c r="K5" s="80"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
+      <c r="K5" s="77"/>
     </row>
     <row r="6" s="2" customFormat="true" ht="75.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
@@ -6101,11 +6085,11 @@
         <v>225</v>
       </c>
       <c r="F6" s="8"/>
-      <c r="G6" s="80"/>
-      <c r="H6" s="80"/>
-      <c r="I6" s="80"/>
-      <c r="J6" s="80"/>
-      <c r="K6" s="80"/>
+      <c r="G6" s="77"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
+      <c r="J6" s="77"/>
+      <c r="K6" s="77"/>
     </row>
     <row r="7" s="2" customFormat="true" ht="224.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
@@ -6144,11 +6128,11 @@
         <v>230</v>
       </c>
       <c r="F8" s="8"/>
-      <c r="G8" s="80"/>
-      <c r="H8" s="80"/>
-      <c r="I8" s="80"/>
-      <c r="J8" s="80"/>
-      <c r="K8" s="80"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="77"/>
+      <c r="I8" s="77"/>
+      <c r="J8" s="77"/>
+      <c r="K8" s="77"/>
     </row>
     <row r="9" s="2" customFormat="true" ht="238.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
@@ -6167,17 +6151,17 @@
         <v>232</v>
       </c>
       <c r="F9" s="8"/>
-      <c r="G9" s="80"/>
-      <c r="H9" s="80"/>
-      <c r="I9" s="80"/>
-      <c r="J9" s="80"/>
-      <c r="K9" s="80"/>
+      <c r="G9" s="77"/>
+      <c r="H9" s="77"/>
+      <c r="I9" s="77"/>
+      <c r="J9" s="77"/>
+      <c r="K9" s="77"/>
     </row>
     <row r="10" s="2" customFormat="true" ht="106.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="82" t="s">
+      <c r="B10" s="79" t="s">
         <v>233</v>
       </c>
       <c r="C10" s="33" t="s">
@@ -6189,12 +6173,12 @@
       <c r="E10" s="33" t="s">
         <v>234</v>
       </c>
-      <c r="F10" s="120"/>
-      <c r="G10" s="80"/>
-      <c r="H10" s="80"/>
-      <c r="I10" s="80"/>
-      <c r="J10" s="80"/>
-      <c r="K10" s="80"/>
+      <c r="F10" s="118"/>
+      <c r="G10" s="77"/>
+      <c r="H10" s="77"/>
+      <c r="I10" s="77"/>
+      <c r="J10" s="77"/>
+      <c r="K10" s="77"/>
     </row>
     <row r="11" customFormat="false" ht="242.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
@@ -6213,11 +6197,11 @@
         <v>236</v>
       </c>
       <c r="F11" s="22"/>
-      <c r="G11" s="80"/>
-      <c r="H11" s="80"/>
-      <c r="I11" s="80"/>
-      <c r="J11" s="80"/>
-      <c r="K11" s="80"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="77"/>
+      <c r="J11" s="77"/>
+      <c r="K11" s="77"/>
     </row>
     <row r="12" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
@@ -6236,11 +6220,11 @@
       <c r="F12" s="23" t="s">
         <v>239</v>
       </c>
-      <c r="G12" s="80"/>
-      <c r="H12" s="80"/>
-      <c r="I12" s="80"/>
-      <c r="J12" s="80"/>
-      <c r="K12" s="80"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="77"/>
+      <c r="I12" s="77"/>
+      <c r="J12" s="77"/>
+      <c r="K12" s="77"/>
     </row>
     <row r="13" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
@@ -6257,37 +6241,37 @@
       </c>
       <c r="E13" s="15"/>
       <c r="F13" s="23"/>
-      <c r="G13" s="80"/>
-      <c r="H13" s="80"/>
-      <c r="I13" s="80"/>
-      <c r="J13" s="80"/>
-      <c r="K13" s="80"/>
-    </row>
-    <row r="14" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="86"/>
-      <c r="B14" s="87"/>
-      <c r="C14" s="87"/>
-      <c r="D14" s="87"/>
-      <c r="E14" s="87"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="77"/>
+      <c r="I13" s="77"/>
+      <c r="J13" s="77"/>
+      <c r="K13" s="77"/>
+    </row>
+    <row r="14" customFormat="false" ht="130.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="83"/>
+      <c r="B14" s="84"/>
+      <c r="C14" s="84"/>
+      <c r="D14" s="84"/>
+      <c r="E14" s="84"/>
       <c r="F14" s="28"/>
-      <c r="G14" s="80"/>
-      <c r="H14" s="80"/>
-      <c r="I14" s="80"/>
-      <c r="J14" s="80"/>
-      <c r="K14" s="80"/>
-    </row>
-    <row r="15" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G14" s="77"/>
+      <c r="H14" s="77"/>
+      <c r="I14" s="77"/>
+      <c r="J14" s="77"/>
+      <c r="K14" s="77"/>
+    </row>
+    <row r="15" customFormat="false" ht="114.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="29"/>
       <c r="B15" s="30"/>
       <c r="C15" s="30"/>
       <c r="D15" s="30"/>
       <c r="E15" s="30"/>
       <c r="F15" s="31"/>
-      <c r="G15" s="80"/>
-      <c r="H15" s="80"/>
-      <c r="I15" s="80"/>
-      <c r="J15" s="80"/>
-      <c r="K15" s="80"/>
+      <c r="G15" s="77"/>
+      <c r="H15" s="77"/>
+      <c r="I15" s="77"/>
+      <c r="J15" s="77"/>
+      <c r="K15" s="77"/>
     </row>
     <row r="16" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="32" t="s">
@@ -6306,11 +6290,11 @@
         <v>244</v>
       </c>
       <c r="F16" s="34"/>
-      <c r="G16" s="80"/>
-      <c r="H16" s="80"/>
-      <c r="I16" s="80"/>
-      <c r="J16" s="80"/>
-      <c r="K16" s="80"/>
+      <c r="G16" s="77"/>
+      <c r="H16" s="77"/>
+      <c r="I16" s="77"/>
+      <c r="J16" s="77"/>
+      <c r="K16" s="77"/>
     </row>
     <row r="17" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
@@ -6329,87 +6313,87 @@
         <v>246</v>
       </c>
       <c r="F17" s="23"/>
-      <c r="G17" s="80"/>
-      <c r="H17" s="80"/>
-      <c r="I17" s="80"/>
-      <c r="J17" s="80"/>
-      <c r="K17" s="80"/>
+      <c r="G17" s="77"/>
+      <c r="H17" s="77"/>
+      <c r="I17" s="77"/>
+      <c r="J17" s="77"/>
+      <c r="K17" s="77"/>
     </row>
     <row r="18" customFormat="false" ht="184.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="85" t="s">
         <v>46</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="119" t="s">
         <v>247</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="86" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="86" t="s">
         <v>248</v>
       </c>
-      <c r="E18" s="15"/>
-      <c r="F18" s="23" t="s">
+      <c r="E18" s="86"/>
+      <c r="F18" s="87" t="s">
         <v>249</v>
       </c>
-      <c r="G18" s="80"/>
-      <c r="H18" s="80"/>
-      <c r="I18" s="80"/>
-      <c r="J18" s="80"/>
-      <c r="K18" s="80"/>
+      <c r="G18" s="77"/>
+      <c r="H18" s="77"/>
+      <c r="I18" s="77"/>
+      <c r="J18" s="77"/>
+      <c r="K18" s="77"/>
     </row>
     <row r="19" customFormat="false" ht="207.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="88" t="s">
+      <c r="A19" s="83" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="89" t="s">
+      <c r="B19" s="84" t="s">
         <v>250</v>
       </c>
-      <c r="C19" s="89" t="s">
+      <c r="C19" s="84" t="s">
         <v>44</v>
       </c>
-      <c r="D19" s="89" t="s">
+      <c r="D19" s="84" t="s">
         <v>251</v>
       </c>
-      <c r="E19" s="89"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="80"/>
-      <c r="H19" s="80"/>
-      <c r="I19" s="80"/>
-      <c r="J19" s="80"/>
-      <c r="K19" s="80"/>
+      <c r="E19" s="84"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="77"/>
+      <c r="H19" s="77"/>
+      <c r="I19" s="77"/>
+      <c r="J19" s="77"/>
+      <c r="K19" s="77"/>
     </row>
     <row r="20" customFormat="false" ht="207.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="86"/>
-      <c r="B20" s="87"/>
-      <c r="C20" s="87"/>
-      <c r="D20" s="87"/>
-      <c r="E20" s="87"/>
+      <c r="A20" s="83"/>
+      <c r="B20" s="84"/>
+      <c r="C20" s="84"/>
+      <c r="D20" s="84"/>
+      <c r="E20" s="84"/>
       <c r="F20" s="28"/>
-      <c r="G20" s="80"/>
-      <c r="H20" s="80"/>
-      <c r="I20" s="80"/>
-      <c r="J20" s="80"/>
-      <c r="K20" s="80"/>
+      <c r="G20" s="77"/>
+      <c r="H20" s="77"/>
+      <c r="I20" s="77"/>
+      <c r="J20" s="77"/>
+      <c r="K20" s="77"/>
     </row>
     <row r="21" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="121"/>
-      <c r="B21" s="122"/>
-      <c r="C21" s="122"/>
-      <c r="D21" s="122"/>
-      <c r="E21" s="122"/>
-      <c r="F21" s="123"/>
-      <c r="G21" s="80"/>
-      <c r="H21" s="80"/>
-      <c r="I21" s="80"/>
-      <c r="J21" s="80"/>
-      <c r="K21" s="80"/>
+      <c r="A21" s="120"/>
+      <c r="B21" s="121"/>
+      <c r="C21" s="121"/>
+      <c r="D21" s="121"/>
+      <c r="E21" s="121"/>
+      <c r="F21" s="122"/>
+      <c r="G21" s="77"/>
+      <c r="H21" s="77"/>
+      <c r="I21" s="77"/>
+      <c r="J21" s="77"/>
+      <c r="K21" s="77"/>
     </row>
     <row r="22" customFormat="false" ht="172.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="82" t="s">
+      <c r="B22" s="79" t="s">
         <v>252</v>
       </c>
       <c r="C22" s="33" t="s">
@@ -6421,12 +6405,12 @@
       <c r="E22" s="33" t="s">
         <v>253</v>
       </c>
-      <c r="F22" s="120"/>
-      <c r="G22" s="80"/>
-      <c r="H22" s="80"/>
-      <c r="I22" s="80"/>
-      <c r="J22" s="80"/>
-      <c r="K22" s="80"/>
+      <c r="F22" s="118"/>
+      <c r="G22" s="77"/>
+      <c r="H22" s="77"/>
+      <c r="I22" s="77"/>
+      <c r="J22" s="77"/>
+      <c r="K22" s="77"/>
     </row>
     <row r="23" customFormat="false" ht="256.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="21" t="s">
@@ -6445,11 +6429,11 @@
         <v>255</v>
       </c>
       <c r="F23" s="22"/>
-      <c r="G23" s="80"/>
-      <c r="H23" s="80"/>
-      <c r="I23" s="80"/>
-      <c r="J23" s="80"/>
-      <c r="K23" s="80"/>
+      <c r="G23" s="77"/>
+      <c r="H23" s="77"/>
+      <c r="I23" s="77"/>
+      <c r="J23" s="77"/>
+      <c r="K23" s="77"/>
     </row>
     <row r="24" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="21" t="s">
@@ -6468,45 +6452,45 @@
       <c r="F24" s="23" t="s">
         <v>258</v>
       </c>
-      <c r="G24" s="80"/>
-      <c r="H24" s="80"/>
-      <c r="I24" s="80"/>
-      <c r="J24" s="80"/>
-      <c r="K24" s="80"/>
+      <c r="G24" s="77"/>
+      <c r="H24" s="77"/>
+      <c r="I24" s="77"/>
+      <c r="J24" s="77"/>
+      <c r="K24" s="77"/>
     </row>
     <row r="25" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="88" t="s">
+      <c r="A25" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="B25" s="89" t="s">
+      <c r="B25" s="15" t="s">
         <v>259</v>
       </c>
-      <c r="C25" s="89" t="s">
+      <c r="C25" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="D25" s="89" t="s">
+      <c r="D25" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="E25" s="89"/>
-      <c r="F25" s="41"/>
-      <c r="G25" s="80"/>
-      <c r="H25" s="80"/>
-      <c r="I25" s="80"/>
-      <c r="J25" s="80"/>
-      <c r="K25" s="80"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="77"/>
+      <c r="H25" s="77"/>
+      <c r="I25" s="77"/>
+      <c r="J25" s="77"/>
+      <c r="K25" s="77"/>
     </row>
     <row r="26" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="86"/>
-      <c r="B26" s="87"/>
-      <c r="C26" s="87"/>
-      <c r="D26" s="87"/>
-      <c r="E26" s="87"/>
+      <c r="A26" s="83"/>
+      <c r="B26" s="84"/>
+      <c r="C26" s="84"/>
+      <c r="D26" s="84"/>
+      <c r="E26" s="84"/>
       <c r="F26" s="28"/>
-      <c r="G26" s="80"/>
-      <c r="H26" s="80"/>
-      <c r="I26" s="80"/>
-      <c r="J26" s="80"/>
-      <c r="K26" s="80"/>
+      <c r="G26" s="77"/>
+      <c r="H26" s="77"/>
+      <c r="I26" s="77"/>
+      <c r="J26" s="77"/>
+      <c r="K26" s="77"/>
     </row>
     <row r="27" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="29"/>
@@ -6515,11 +6499,11 @@
       <c r="D27" s="30"/>
       <c r="E27" s="30"/>
       <c r="F27" s="31"/>
-      <c r="G27" s="80"/>
-      <c r="H27" s="80"/>
-      <c r="I27" s="80"/>
-      <c r="J27" s="80"/>
-      <c r="K27" s="80"/>
+      <c r="G27" s="77"/>
+      <c r="H27" s="77"/>
+      <c r="I27" s="77"/>
+      <c r="J27" s="77"/>
+      <c r="K27" s="77"/>
     </row>
     <row r="28" customFormat="false" ht="114.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="32" t="s">
@@ -6538,11 +6522,11 @@
         <v>263</v>
       </c>
       <c r="F28" s="34"/>
-      <c r="G28" s="80"/>
-      <c r="H28" s="80"/>
-      <c r="I28" s="80"/>
-      <c r="J28" s="80"/>
-      <c r="K28" s="80"/>
+      <c r="G28" s="77"/>
+      <c r="H28" s="77"/>
+      <c r="I28" s="77"/>
+      <c r="J28" s="77"/>
+      <c r="K28" s="77"/>
     </row>
     <row r="29" customFormat="false" ht="195.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="21" t="s">
@@ -6561,11 +6545,11 @@
         <v>265</v>
       </c>
       <c r="F29" s="23"/>
-      <c r="G29" s="80"/>
-      <c r="H29" s="80"/>
-      <c r="I29" s="80"/>
-      <c r="J29" s="80"/>
-      <c r="K29" s="80"/>
+      <c r="G29" s="77"/>
+      <c r="H29" s="77"/>
+      <c r="I29" s="77"/>
+      <c r="J29" s="77"/>
+      <c r="K29" s="77"/>
     </row>
     <row r="30" customFormat="false" ht="199" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="21" t="s">
@@ -6584,121 +6568,121 @@
       <c r="F30" s="23" t="s">
         <v>268</v>
       </c>
-      <c r="G30" s="80"/>
-      <c r="H30" s="80"/>
-      <c r="I30" s="80"/>
-      <c r="J30" s="80"/>
-      <c r="K30" s="80"/>
+      <c r="G30" s="77"/>
+      <c r="H30" s="77"/>
+      <c r="I30" s="77"/>
+      <c r="J30" s="77"/>
+      <c r="K30" s="77"/>
     </row>
     <row r="31" customFormat="false" ht="153.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="88" t="s">
+      <c r="A31" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="B31" s="89" t="s">
+      <c r="B31" s="15" t="s">
         <v>269</v>
       </c>
-      <c r="C31" s="89" t="s">
+      <c r="C31" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="D31" s="89" t="s">
+      <c r="D31" s="15" t="s">
         <v>270</v>
       </c>
-      <c r="E31" s="89"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="80"/>
-      <c r="H31" s="80"/>
-      <c r="I31" s="80"/>
-      <c r="J31" s="80"/>
-      <c r="K31" s="80"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="77"/>
+      <c r="H31" s="77"/>
+      <c r="I31" s="77"/>
+      <c r="J31" s="77"/>
+      <c r="K31" s="77"/>
     </row>
     <row r="32" customFormat="false" ht="153.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="86"/>
-      <c r="B32" s="87"/>
-      <c r="C32" s="87"/>
-      <c r="D32" s="87"/>
-      <c r="E32" s="87"/>
+      <c r="A32" s="83"/>
+      <c r="B32" s="84"/>
+      <c r="C32" s="84"/>
+      <c r="D32" s="84"/>
+      <c r="E32" s="84"/>
       <c r="F32" s="28"/>
-      <c r="G32" s="80"/>
-      <c r="H32" s="80"/>
-      <c r="I32" s="80"/>
-      <c r="J32" s="80"/>
-      <c r="K32" s="80"/>
+      <c r="G32" s="77"/>
+      <c r="H32" s="77"/>
+      <c r="I32" s="77"/>
+      <c r="J32" s="77"/>
+      <c r="K32" s="77"/>
     </row>
     <row r="33" customFormat="false" ht="149.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="29"/>
-      <c r="B33" s="124"/>
-      <c r="C33" s="124"/>
-      <c r="D33" s="124"/>
-      <c r="E33" s="124"/>
-      <c r="F33" s="125"/>
-      <c r="G33" s="80"/>
-      <c r="H33" s="80"/>
-      <c r="I33" s="80"/>
-      <c r="J33" s="80"/>
-      <c r="K33" s="80"/>
+      <c r="B33" s="123"/>
+      <c r="C33" s="123"/>
+      <c r="D33" s="123"/>
+      <c r="E33" s="123"/>
+      <c r="F33" s="124"/>
+      <c r="G33" s="77"/>
+      <c r="H33" s="77"/>
+      <c r="I33" s="77"/>
+      <c r="J33" s="77"/>
+      <c r="K33" s="77"/>
     </row>
     <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G34" s="80"/>
-      <c r="H34" s="80"/>
-      <c r="I34" s="80"/>
-      <c r="J34" s="80"/>
-      <c r="K34" s="80"/>
+      <c r="G34" s="77"/>
+      <c r="H34" s="77"/>
+      <c r="I34" s="77"/>
+      <c r="J34" s="77"/>
+      <c r="K34" s="77"/>
     </row>
     <row r="35" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G35" s="80"/>
-      <c r="H35" s="80"/>
-      <c r="I35" s="80"/>
-      <c r="J35" s="80"/>
-      <c r="K35" s="80"/>
+      <c r="G35" s="77"/>
+      <c r="H35" s="77"/>
+      <c r="I35" s="77"/>
+      <c r="J35" s="77"/>
+      <c r="K35" s="77"/>
     </row>
     <row r="36" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G36" s="80"/>
-      <c r="H36" s="80"/>
-      <c r="I36" s="80"/>
-      <c r="J36" s="80"/>
-      <c r="K36" s="80"/>
+      <c r="G36" s="77"/>
+      <c r="H36" s="77"/>
+      <c r="I36" s="77"/>
+      <c r="J36" s="77"/>
+      <c r="K36" s="77"/>
     </row>
     <row r="37" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G37" s="80"/>
-      <c r="H37" s="80"/>
-      <c r="I37" s="80"/>
-      <c r="J37" s="80"/>
-      <c r="K37" s="80"/>
+      <c r="G37" s="77"/>
+      <c r="H37" s="77"/>
+      <c r="I37" s="77"/>
+      <c r="J37" s="77"/>
+      <c r="K37" s="77"/>
     </row>
     <row r="38" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G38" s="80"/>
-      <c r="H38" s="80"/>
-      <c r="I38" s="80"/>
-      <c r="J38" s="80"/>
-      <c r="K38" s="80"/>
+      <c r="G38" s="77"/>
+      <c r="H38" s="77"/>
+      <c r="I38" s="77"/>
+      <c r="J38" s="77"/>
+      <c r="K38" s="77"/>
     </row>
     <row r="39" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G39" s="80"/>
-      <c r="H39" s="80"/>
-      <c r="I39" s="80"/>
-      <c r="J39" s="80"/>
-      <c r="K39" s="80"/>
+      <c r="G39" s="77"/>
+      <c r="H39" s="77"/>
+      <c r="I39" s="77"/>
+      <c r="J39" s="77"/>
+      <c r="K39" s="77"/>
     </row>
     <row r="40" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G40" s="80"/>
-      <c r="H40" s="80"/>
-      <c r="I40" s="80"/>
-      <c r="J40" s="80"/>
-      <c r="K40" s="80"/>
+      <c r="G40" s="77"/>
+      <c r="H40" s="77"/>
+      <c r="I40" s="77"/>
+      <c r="J40" s="77"/>
+      <c r="K40" s="77"/>
     </row>
     <row r="41" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G41" s="80"/>
-      <c r="H41" s="80"/>
-      <c r="I41" s="80"/>
-      <c r="J41" s="80"/>
-      <c r="K41" s="80"/>
+      <c r="G41" s="77"/>
+      <c r="H41" s="77"/>
+      <c r="I41" s="77"/>
+      <c r="J41" s="77"/>
+      <c r="K41" s="77"/>
     </row>
     <row r="42" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G42" s="80"/>
-      <c r="H42" s="80"/>
-      <c r="I42" s="80"/>
-      <c r="J42" s="80"/>
-      <c r="K42" s="80"/>
+      <c r="G42" s="77"/>
+      <c r="H42" s="77"/>
+      <c r="I42" s="77"/>
+      <c r="J42" s="77"/>
+      <c r="K42" s="77"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -6730,484 +6714,484 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="3" width="26.32"/>
   </cols>
   <sheetData>
-    <row r="1" s="126" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="42" t="s">
+    <row r="1" s="125" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="42" t="s">
+      <c r="B1" s="39" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="43" t="s">
+      <c r="C1" s="40" t="s">
         <v>271</v>
       </c>
-      <c r="D1" s="43" t="s">
+      <c r="D1" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="E1" s="43" t="s">
+      <c r="E1" s="40" t="s">
         <v>272</v>
       </c>
-      <c r="F1" s="43" t="s">
+      <c r="F1" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="43" t="s">
+      <c r="G1" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="43" t="s">
+      <c r="H1" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="I1" s="43" t="s">
+      <c r="I1" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="J1" s="44" t="s">
+      <c r="J1" s="41" t="s">
         <v>68</v>
       </c>
       <c r="XFD1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="43" t="s">
         <v>273</v>
       </c>
-      <c r="B2" s="47" t="n">
+      <c r="B2" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="48" t="n">
+      <c r="C2" s="45" t="n">
         <v>1786239</v>
       </c>
-      <c r="D2" s="52" t="n">
+      <c r="D2" s="49" t="n">
         <v>1785037</v>
       </c>
-      <c r="E2" s="48" t="n">
+      <c r="E2" s="45" t="n">
         <v>1428029</v>
       </c>
-      <c r="F2" s="52" t="n">
+      <c r="F2" s="49" t="n">
         <v>1427700</v>
       </c>
-      <c r="G2" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H2" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I2" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J2" s="50" t="n">
+      <c r="G2" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H2" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I2" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J2" s="47" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="43" t="s">
         <v>274</v>
       </c>
-      <c r="B3" s="47" t="n">
+      <c r="B3" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="48" t="n">
+      <c r="C3" s="45" t="n">
         <v>349240</v>
       </c>
-      <c r="D3" s="52" t="n">
+      <c r="D3" s="49" t="n">
         <v>346201</v>
       </c>
-      <c r="E3" s="48" t="n">
+      <c r="E3" s="45" t="n">
         <v>276961</v>
       </c>
-      <c r="F3" s="52" t="n">
+      <c r="F3" s="49" t="n">
         <v>275565</v>
       </c>
-      <c r="G3" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H3" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I3" s="48" t="n">
+      <c r="G3" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H3" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I3" s="45" t="n">
         <v>9549</v>
       </c>
-      <c r="J3" s="50" t="n">
+      <c r="J3" s="47" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="46" t="s">
+      <c r="A4" s="43" t="s">
         <v>275</v>
       </c>
-      <c r="B4" s="47" t="n">
+      <c r="B4" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="48" t="n">
+      <c r="C4" s="45" t="n">
         <v>161323</v>
       </c>
-      <c r="D4" s="52" t="n">
+      <c r="D4" s="49" t="n">
         <v>161323</v>
       </c>
-      <c r="E4" s="48" t="n">
+      <c r="E4" s="45" t="n">
         <v>129058</v>
       </c>
-      <c r="F4" s="52" t="n">
+      <c r="F4" s="49" t="n">
         <v>129044</v>
       </c>
-      <c r="G4" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H4" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I4" s="48" t="n">
+      <c r="G4" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H4" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I4" s="45" t="n">
         <v>9994</v>
       </c>
-      <c r="J4" s="50" t="n">
+      <c r="J4" s="47" t="n">
         <v>9992</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="46" t="s">
+      <c r="A5" s="43" t="s">
         <v>276</v>
       </c>
-      <c r="B5" s="47" t="n">
+      <c r="B5" s="44" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="48" t="n">
+      <c r="C5" s="45" t="n">
         <v>95733</v>
       </c>
-      <c r="D5" s="52" t="n">
+      <c r="D5" s="49" t="n">
         <v>95729</v>
       </c>
-      <c r="E5" s="48" t="n">
+      <c r="E5" s="45" t="n">
         <v>76583</v>
       </c>
-      <c r="F5" s="52" t="n">
+      <c r="F5" s="49" t="n">
         <v>75502</v>
       </c>
-      <c r="G5" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H5" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I5" s="48" t="n">
+      <c r="G5" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H5" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I5" s="45" t="n">
         <v>9593</v>
       </c>
-      <c r="J5" s="50" t="n">
+      <c r="J5" s="47" t="n">
         <v>9989</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="46" t="s">
+      <c r="A6" s="43" t="s">
         <v>182</v>
       </c>
-      <c r="B6" s="47" t="n">
+      <c r="B6" s="44" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="48" t="n">
+      <c r="C6" s="45" t="n">
         <v>9531</v>
       </c>
-      <c r="D6" s="52" t="n">
+      <c r="D6" s="49" t="n">
         <v>9531</v>
       </c>
-      <c r="E6" s="48" t="n">
+      <c r="E6" s="45" t="n">
         <v>7625</v>
       </c>
-      <c r="F6" s="52" t="n">
+      <c r="F6" s="49" t="n">
         <v>7608</v>
       </c>
-      <c r="G6" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H6" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I6" s="48" t="n">
+      <c r="G6" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H6" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I6" s="45" t="n">
         <v>9990</v>
       </c>
-      <c r="J6" s="50" t="n">
+      <c r="J6" s="47" t="n">
         <v>9999</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="46" t="s">
+      <c r="A7" s="43" t="s">
         <v>277</v>
       </c>
-      <c r="B7" s="47" t="n">
+      <c r="B7" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="48" t="n">
+      <c r="C7" s="45" t="n">
         <v>8364</v>
       </c>
-      <c r="D7" s="52" t="n">
+      <c r="D7" s="49" t="n">
         <v>8364</v>
       </c>
-      <c r="E7" s="48" t="n">
+      <c r="E7" s="45" t="n">
         <v>6691</v>
       </c>
-      <c r="F7" s="52" t="n">
+      <c r="F7" s="49" t="n">
         <v>6423</v>
       </c>
-      <c r="G7" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H7" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I7" s="48" t="n">
+      <c r="G7" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H7" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I7" s="45" t="n">
         <v>9781</v>
       </c>
-      <c r="J7" s="50" t="n">
+      <c r="J7" s="47" t="n">
         <v>9944</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="46" t="s">
+      <c r="A8" s="43" t="s">
         <v>278</v>
       </c>
-      <c r="B8" s="47" t="n">
+      <c r="B8" s="44" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="48" t="n">
+      <c r="C8" s="45" t="n">
         <v>6860</v>
       </c>
-      <c r="D8" s="52" t="n">
+      <c r="D8" s="49" t="n">
         <v>6856</v>
       </c>
-      <c r="E8" s="48" t="n">
+      <c r="E8" s="45" t="n">
         <v>5485</v>
       </c>
-      <c r="F8" s="52" t="n">
+      <c r="F8" s="49" t="n">
         <v>5325</v>
       </c>
-      <c r="G8" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H8" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I8" s="48" t="n">
+      <c r="G8" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H8" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I8" s="45" t="n">
         <v>9873</v>
       </c>
-      <c r="J8" s="50" t="n">
+      <c r="J8" s="47" t="n">
         <v>9880</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="46" t="s">
+      <c r="A9" s="43" t="s">
         <v>185</v>
       </c>
-      <c r="B9" s="47" t="n">
+      <c r="B9" s="44" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="48" t="n">
+      <c r="C9" s="45" t="n">
         <v>5949</v>
       </c>
-      <c r="D9" s="52" t="n">
+      <c r="D9" s="49" t="n">
         <v>5949</v>
       </c>
-      <c r="E9" s="48" t="n">
+      <c r="E9" s="45" t="n">
         <v>4759</v>
       </c>
-      <c r="F9" s="52" t="n">
+      <c r="F9" s="49" t="n">
         <v>4732</v>
       </c>
-      <c r="G9" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H9" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I9" s="48" t="n">
+      <c r="G9" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H9" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I9" s="45" t="n">
         <v>9983</v>
       </c>
-      <c r="J9" s="50" t="n">
+      <c r="J9" s="47" t="n">
         <v>9992</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="46" t="s">
+      <c r="A10" s="43" t="s">
         <v>279</v>
       </c>
-      <c r="B10" s="47" t="n">
+      <c r="B10" s="44" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="48" t="n">
+      <c r="C10" s="45" t="n">
         <v>5508</v>
       </c>
-      <c r="D10" s="52" t="n">
+      <c r="D10" s="49" t="n">
         <v>5508</v>
       </c>
-      <c r="E10" s="48" t="n">
+      <c r="E10" s="45" t="n">
         <v>4406</v>
       </c>
-      <c r="F10" s="52" t="n">
+      <c r="F10" s="49" t="n">
         <v>4393</v>
       </c>
-      <c r="G10" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H10" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I10" s="48" t="n">
+      <c r="G10" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H10" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I10" s="45" t="n">
         <v>9995</v>
       </c>
-      <c r="J10" s="50" t="n">
+      <c r="J10" s="47" t="n">
         <v>9995</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="46" t="s">
+      <c r="A11" s="43" t="s">
         <v>280</v>
       </c>
-      <c r="B11" s="47" t="n">
+      <c r="B11" s="44" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="48" t="n">
+      <c r="C11" s="45" t="n">
         <v>5177</v>
       </c>
-      <c r="D11" s="52" t="n">
+      <c r="D11" s="49" t="n">
         <v>5123</v>
       </c>
-      <c r="E11" s="48" t="n">
+      <c r="E11" s="45" t="n">
         <v>4098</v>
       </c>
-      <c r="F11" s="52" t="n">
+      <c r="F11" s="49" t="n">
         <v>3980</v>
       </c>
-      <c r="G11" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H11" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I11" s="48" t="n">
+      <c r="G11" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H11" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I11" s="45" t="n">
         <v>9868</v>
       </c>
-      <c r="J11" s="50" t="n">
+      <c r="J11" s="47" t="n">
         <v>9881</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="46" t="s">
+      <c r="A12" s="43" t="s">
         <v>281</v>
       </c>
-      <c r="B12" s="47" t="n">
+      <c r="B12" s="44" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="48" t="n">
+      <c r="C12" s="45" t="n">
         <v>2734</v>
       </c>
-      <c r="D12" s="52" t="n">
+      <c r="D12" s="49" t="n">
         <v>2733</v>
       </c>
-      <c r="E12" s="48" t="n">
+      <c r="E12" s="45" t="n">
         <v>2187</v>
       </c>
-      <c r="F12" s="52" t="n">
+      <c r="F12" s="49" t="n">
         <v>2176</v>
       </c>
-      <c r="G12" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H12" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I12" s="48" t="n">
+      <c r="G12" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H12" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I12" s="45" t="n">
         <v>9971</v>
       </c>
-      <c r="J12" s="50" t="n">
+      <c r="J12" s="47" t="n">
         <v>9971</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="46" t="s">
+      <c r="A13" s="43" t="s">
         <v>282</v>
       </c>
-      <c r="B13" s="47" t="n">
+      <c r="B13" s="44" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="48" t="n">
+      <c r="C13" s="45" t="n">
         <v>1358</v>
       </c>
-      <c r="D13" s="52" t="n">
+      <c r="D13" s="49" t="n">
         <v>1357</v>
       </c>
-      <c r="E13" s="48" t="n">
+      <c r="E13" s="45" t="n">
         <v>1086</v>
       </c>
-      <c r="F13" s="52" t="n">
+      <c r="F13" s="49" t="n">
         <v>1076</v>
       </c>
-      <c r="G13" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H13" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I13" s="48" t="n">
+      <c r="G13" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H13" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I13" s="45" t="n">
         <v>9971</v>
       </c>
-      <c r="J13" s="50" t="n">
+      <c r="J13" s="47" t="n">
         <v>9971</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="46" t="s">
+      <c r="A14" s="43" t="s">
         <v>283</v>
       </c>
-      <c r="B14" s="47" t="n">
+      <c r="B14" s="44" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="48" t="n">
+      <c r="C14" s="45" t="n">
         <v>24</v>
       </c>
-      <c r="D14" s="52" t="n">
+      <c r="D14" s="49" t="n">
         <v>24</v>
       </c>
-      <c r="E14" s="48" t="n">
+      <c r="E14" s="45" t="n">
         <v>19</v>
       </c>
-      <c r="F14" s="52" t="n">
+      <c r="F14" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="G14" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H14" s="52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I14" s="48" t="n">
+      <c r="G14" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H14" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I14" s="45" t="n">
         <v>9998</v>
       </c>
-      <c r="J14" s="50" t="n">
+      <c r="J14" s="47" t="n">
         <v>9998</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="127" t="s">
+      <c r="A15" s="126" t="s">
         <v>190</v>
       </c>
-      <c r="B15" s="54" t="n">
+      <c r="B15" s="51" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="55" t="n">
+      <c r="C15" s="52" t="n">
         <v>12</v>
       </c>
-      <c r="D15" s="55" t="n">
+      <c r="D15" s="52" t="n">
         <v>12</v>
       </c>
-      <c r="E15" s="55" t="n">
+      <c r="E15" s="52" t="n">
         <v>10</v>
       </c>
-      <c r="F15" s="55" t="n">
+      <c r="F15" s="52" t="n">
         <v>10</v>
       </c>
-      <c r="G15" s="55" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H15" s="57" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I15" s="55" t="n">
+      <c r="G15" s="52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H15" s="54" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I15" s="52" t="n">
         <v>9995</v>
       </c>
-      <c r="J15" s="58" t="n">
+      <c r="J15" s="55" t="n">
         <v>9995</v>
       </c>
     </row>
@@ -7249,9 +7233,9 @@
       <c r="J17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E18" s="59"/>
-      <c r="F18" s="47"/>
-      <c r="G18" s="47"/>
+      <c r="E18" s="56"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="44"/>
     </row>
     <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
@@ -7260,13 +7244,13 @@
       <c r="C19" s="3" t="n">
         <v>122</v>
       </c>
-      <c r="D19" s="48" t="n">
+      <c r="D19" s="45" t="n">
         <v>48</v>
       </c>
-      <c r="E19" s="47" t="n">
+      <c r="E19" s="44" t="n">
         <v>48</v>
       </c>
-      <c r="F19" s="47" t="n">
+      <c r="F19" s="44" t="n">
         <v>48</v>
       </c>
       <c r="G19" s="3" t="n">
@@ -7278,7 +7262,7 @@
       <c r="I19" s="2"/>
     </row>
     <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J34" s="48"/>
+      <c r="J34" s="45"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/TFG1/02_datasets/metadata/METADATA.xlsx
+++ b/TFG1/02_datasets/metadata/METADATA.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="318">
   <si>
     <t xml:space="preserve">TÉCNICA</t>
   </si>
@@ -254,6 +254,17 @@
 Pd_CIC18__RUS_SMOTE__v1__val__5.csv</t>
   </si>
   <si>
+    <t xml:space="preserve">pd_CIC18__RUS_SMOTE__v1__test_final_v1.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_CIC18__RUS_SMOTE__v1__val__1.csv
+pd_CIC18__RUS_SMOTE__v1__val__2.csvv
+pd_CIC18__RUS_SMOTE__v1__val__3.cs
+pd_CIC18__RUS_SMOTE__v1__val__4.csv
+Pd_CIC18__RUS_SMOTE__v1__train__5.csv
+Pd_CIC18__RUS_SMOTE__v1__val__5.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">RUS/SMOTE + ENN</t>
   </si>
   <si>
@@ -326,6 +337,17 @@
 Pd_CIC18__RUS_SMOTE_ENN__v1__val__5.csv</t>
   </si>
   <si>
+    <t xml:space="preserve">pd_CIC18__RUS_SMOTE_ENN__v1__test_final_v1.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_CIC18__RUS_SMOTE_ENN__v1__val__1.csv
+pd_CIC18__RUS_SMOTE_ENN__v1__val__2.csvv
+pd_CIC18__RUS_SMOTE_ENN__v1__val__3.cs
+pd_CIC18__RUS_SMOTE_ENN__v1__val__4.csv
+Pd_CIC18__RUS_SMOTE_ENN__v1__train__5.csv
+Pd_CIC18__RUS_SMOTE_ENN__v1__val__5.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">NearMiss/SMOTE</t>
   </si>
   <si>
@@ -407,6 +429,17 @@
 Pd_CIC18__NearMiss_SMOTE__v1__val__5.csv</t>
   </si>
   <si>
+    <t xml:space="preserve">pd_CIC18__NearMiss_SMOTE__v1__test_final_v1.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_CIC18__NearMiss_SMOTE__v1__val__1.csv
+pd_CIC18__NearMiss_SMOTE__v1__val__2.csvv
+pd_CIC18__NearMiss_SMOTE__v1__val__3.cs
+pd_CIC18__NearMiss_SMOTE__v1__val__4.csv
+Pd_CIC18__NearMiss_SMOTE__v1__train__5.csv
+Pd_CIC18__NearMiss_SMOTE__v1__val__5.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">NearMiss/SMOTE + ENN</t>
   </si>
   <si>
@@ -479,6 +512,17 @@
 Pd_CIC18__NearMiss_SMOTE_ENN__v1__val__5.csv</t>
   </si>
   <si>
+    <t xml:space="preserve">pd_CIC18__NearMiss_ENN__v1__test_final_v1.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_CIC18__NearMiss_ENN__v1__val__1.csv
+pd_CIC18__NearMiss_ENN__v1__val__2.csvv
+pd_CIC18__NearMiss_ENN__v1__val__3.cs
+pd_CIC18__NearMiss_ENN__v1__val__4.csv
+Pd_CIC18__NearMiss_ENN__v1__train__5.csv
+Pd_CIC18__NearMiss_ENN__v1__val__5.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">CLASE ORIGINAL</t>
   </si>
   <si>
@@ -757,6 +801,17 @@
 Pd_CIC17__RUS_SMOTE__v1__val__5.csv</t>
   </si>
   <si>
+    <t xml:space="preserve">pd_CIC17__RUS_SMOTE__v1__test_final_v1.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_CIC17__RUS_SMOTE__v1__val__1.csv
+pd_CIC17__RUS_SMOTE__v1__val__2.csvv
+pd_CIC17__RUS_SMOTE__v1__val__3.cs
+pd_CIC17__RUS_SMOTE__v1__val__4.csv
+Pd_CIC17__RUS_SMOTE__v1__train__5.csv
+Pd_CIC17__RUS_SMOTE__v1__val__5.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">CIC17__RUS_SMOTE__v1__ENN_v1.ipynb</t>
   </si>
   <si>
@@ -818,6 +873,17 @@
 pd_CIC17__RUS_SMOTE_ENN__v1__train__4.csv
 pd_CIC17__RUS_SMOTE_ENN__v1__val__4.csv
 pd_CIC17__RUS_SMOTE_ENN__v1__train__5.csv
+Pd_CIC17__RUS_SMOTE_ENN__v1__val__5.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_CIC17__RUS_SMOTE_ENN__v1__test_final_v1.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_CIC17__RUS_SMOTE_ENN__v1__val__1.csv
+pd_CIC17__RUS_SMOTE_ENN__v1__val__2.csvv
+pd_CIC17__RUS_SMOTE_ENN__v1__val__3.cs
+pd_CIC17__RUS_SMOTE_ENN__v1__val__4.csv
+Pd_CIC17__RUS_SMOTE_ENN__v1__train__5.csv
 Pd_CIC17__RUS_SMOTE_ENN__v1__val__5.csv</t>
   </si>
   <si>
@@ -914,6 +980,17 @@
 Pd_CIC17__NearMiss_SMOTE__v1__val__5.csv</t>
   </si>
   <si>
+    <t xml:space="preserve">pd_CIC17__NearMiss_SMOTE__v1__test_final_v1.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_CIC17__NearMiss_SMOTE__v1__val__1.csv
+pd_CIC17__NearMiss_SMOTE__v1__val__2.csvv
+pd_CIC17__NearMiss_SMOTE__v1__val__3.cs
+pd_CIC17__NearMiss_SMOTE__v1__val__4.csv
+Pd_CIC17__NearMiss_SMOTE__v1__train__5.csv
+Pd_CIC17__NearMiss_SMOTE__v1__val__5.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">CIC17__NearMiss_SMOTE__v1__ENN_v1.ipynb</t>
   </si>
   <si>
@@ -978,6 +1055,17 @@
 Pd_CIC17__NearMiss_SMOTE_ENN__v1__val__5.csv</t>
   </si>
   <si>
+    <t xml:space="preserve">pd_CIC17__NearMiss_ENN__v1__test_final_v1.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_CIC17__NearMiss_ENN__v1__val__1.csv
+pd_CIC17__NearMiss_ENN__v1__val__2.csvv
+pd_CIC17__NearMiss_ENN__v1__val__3.cs
+pd_CIC17__NearMiss_ENN__v1__val__4.csv
+Pd_CIC17__NearMiss_ENN__v1__train__5.csv
+Pd_CIC17__NearMiss_ENN__v1__val__5.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">ORIGINAL (CIC17)</t>
   </si>
   <si>
@@ -1249,6 +1337,17 @@
 Pd_BCCC17__RUS_SMOTE__v1__val__5.csv</t>
   </si>
   <si>
+    <t xml:space="preserve">pd_BCCC17__RUS_SMOTE__v1__test_final_v1.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_BCCC17__RUS_SMOTE__v1__val__1.csv
+pd_BCCC17__RUS_SMOTE__v1__val__2.csvv
+pd_BCCC17__RUS_SMOTE__v1__val__3.cs
+pd_BCCC17__RUS_SMOTE__v1__val__4.csv
+Pd_BCCC17__RUS_SMOTE__v1__train__5.csv
+Pd_BCCC17__RUS_SMOTE__v1__val__5.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">BCCC17__RUS_SMOTE__v1__ENN_v1.ipynb</t>
   </si>
   <si>
@@ -1276,31 +1375,11 @@
 Pd_BCCC17__RUS_SMOTE_ENN__v1__val__5.csv</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">pd_BCCC17__RUS_SMOTE_ENN__v1__training_v1__1_5.ipynb
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">pd_BCCC17__RUS_SMOTE_ENN__v1__training_v1__2_5.ipynb
+    <t xml:space="preserve">pd_BCCC17__RUS_SMOTE_ENN__v1__training_v1__1_5.ipynb
+pd_BCCC17__RUS_SMOTE_ENN__v1__training_v1__2_5.ipynb
 pd_BCCC17__RUS_SMOTE_ENN__v1__training_v1__3_5.ipynb
 pd_BCCC17__RUS_SMOTE_ENN__v1__training_v1__4_5.ipynb
 pd_BCCC17__RUS_SMOTE_ENN__v1__training_v1__5_5.ipynb</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">pd_BCCC17__RUS_SMOTE_ENN__v1__train__1.csv
@@ -1330,6 +1409,17 @@
 pd_BCCC17__RUS_SMOTE_ENN__v1__train__4.csv
 pd_BCCC17__RUS_SMOTE_ENN__v1__val__4.csv
 pd_BCCC17__RUS_SMOTE_ENN__v1__train__5.csv
+Pd_BCCC17__RUS_SMOTE_ENN__v1__val__5.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_BCCC17__RUS_SMOTE_ENN__v1__test_final_v1.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_BCCC17__RUS_SMOTE_ENN__v1__val__1.csv
+pd_BCCC17__RUS_SMOTE_ENN__v1__val__2.csvv
+pd_BCCC17__RUS_SMOTE_ENN__v1__val__3.cs
+pd_BCCC17__RUS_SMOTE_ENN__v1__val__4.csv
+Pd_BCCC17__RUS_SMOTE_ENN__v1__train__5.csv
 Pd_BCCC17__RUS_SMOTE_ENN__v1__val__5.csv</t>
   </si>
   <si>
@@ -1396,6 +1486,17 @@
 Pd_BCCC17__NearMiss_SMOTE__v1__val__5.csv</t>
   </si>
   <si>
+    <t xml:space="preserve">pd_BCCC17__NearMiss_SMOTE__v1__test_final_v1.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_BCCC17__NearMiss_SMOTE__v1__val__1.csv
+pd_BCCC17__NearMiss_SMOTE__v1__val__2.csvv
+pd_BCCC17__NearMiss_SMOTE__v1__val__3.cs
+pd_BCCC17__NearMiss_SMOTE__v1__val__4.csv
+Pd_BCCC17__NearMiss_SMOTE__v1__train__5.csv
+Pd_BCCC17__NearMiss_SMOTE__v1__val__5.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">BCCC17__NearMiss_SMOTE__v1__ENN_v1.ipynb</t>
   </si>
   <si>
@@ -1458,6 +1559,17 @@
 pd_BCCC17__NearMiss_SMOTE_ENN__v1__val__4.csv
 pd_BCCC17__NearMiss_SMOTE_ENN__v1__train__5.csv
 Pd_BCCC17__NearMiss_SMOTE_ENN__v1__val__5.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_BCCC17__NearMiss_ENN__v1__test_final_v1.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd_BCCC17__NearMiss_ENN__v1__val__1.csv
+pd_BCCC17__NearMiss_ENN__v1__val__2.csvv
+pd_BCCC17__NearMiss_ENN__v1__val__3.cs
+pd_BCCC17__NearMiss_ENN__v1__val__4.csv
+Pd_BCCC17__NearMiss_ENN__v1__train__5.csv
+Pd_BCCC17__NearMiss_ENN__v1__val__5.csv</t>
   </si>
   <si>
     <t xml:space="preserve">ORIGINAL (BCCC17)</t>
@@ -1833,7 +1945,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="128">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1938,6 +2050,254 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1946,246 +2306,6 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2308,10 +2428,6 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -2845,98 +2961,114 @@
       <c r="F14" s="23"/>
     </row>
     <row r="15" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="26"/>
-      <c r="B15" s="27"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="28"/>
+      <c r="A15" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" s="25"/>
+      <c r="F15" s="23"/>
     </row>
     <row r="16" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="29"/>
-      <c r="B16" s="30"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="31"/>
+      <c r="A16" s="26"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="28"/>
     </row>
     <row r="17" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="B17" s="33" t="s">
-        <v>47</v>
-      </c>
-      <c r="C17" s="33" t="s">
+      <c r="A17" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="33" t="s">
+      <c r="D17" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="E17" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="F17" s="31"/>
+    </row>
+    <row r="18" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="F17" s="34"/>
-    </row>
-    <row r="18" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="35" t="s">
-        <v>46</v>
-      </c>
       <c r="B18" s="11" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C18" s="11" t="s">
         <v>24</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="F18" s="36"/>
+        <v>53</v>
+      </c>
+      <c r="F18" s="33"/>
     </row>
     <row r="19" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C19" s="15" t="s">
         <v>40</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E19" s="15"/>
       <c r="F19" s="23" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="24" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B20" s="25" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C20" s="25" t="s">
         <v>44</v>
       </c>
       <c r="D20" s="25" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E20" s="25"/>
       <c r="F20" s="23"/>
     </row>
     <row r="21" customFormat="false" ht="127.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="26"/>
-      <c r="B21" s="27"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="27"/>
-      <c r="F21" s="28"/>
+      <c r="A21" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="E21" s="35"/>
+      <c r="F21" s="36"/>
     </row>
     <row r="22" customFormat="false" ht="98.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="37"/>
@@ -2944,14 +3076,14 @@
       <c r="C22" s="38"/>
       <c r="D22" s="38"/>
       <c r="E22" s="38"/>
-      <c r="F22" s="31"/>
+      <c r="F22" s="28"/>
     </row>
     <row r="23" s="2" customFormat="true" ht="119.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="17" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C23" s="19" t="s">
         <v>35</v>
@@ -2960,169 +3092,185 @@
         <v>25</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F23" s="20"/>
     </row>
     <row r="24" s="2" customFormat="true" ht="271.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="21" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C24" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F24" s="22"/>
     </row>
     <row r="25" customFormat="false" ht="299.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="21" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E25" s="15"/>
       <c r="F25" s="23" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="213.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="24" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B26" s="25" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C26" s="25" t="s">
         <v>44</v>
       </c>
       <c r="D26" s="25" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E26" s="25"/>
       <c r="F26" s="23"/>
     </row>
     <row r="27" customFormat="false" ht="213.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="26"/>
-      <c r="B27" s="27"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="27"/>
-      <c r="F27" s="28"/>
+      <c r="A27" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="C27" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="D27" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="E27" s="35"/>
+      <c r="F27" s="36"/>
     </row>
     <row r="28" customFormat="false" ht="144.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="29"/>
-      <c r="B28" s="30"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="30"/>
-      <c r="F28" s="31"/>
+      <c r="A28" s="26"/>
+      <c r="B28" s="27"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="27"/>
+      <c r="F28" s="28"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="32" t="s">
-        <v>68</v>
-      </c>
-      <c r="B29" s="33" t="s">
-        <v>69</v>
-      </c>
-      <c r="C29" s="33" t="s">
+      <c r="A29" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="B29" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="C29" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="D29" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="E29" s="33" t="s">
-        <v>71</v>
-      </c>
-      <c r="F29" s="34"/>
+      <c r="D29" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="E29" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="F29" s="31"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
     </row>
     <row r="30" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="35" t="s">
-        <v>68</v>
+      <c r="A30" s="32" t="s">
+        <v>74</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C30" s="11" t="s">
         <v>24</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="F30" s="36"/>
+        <v>79</v>
+      </c>
+      <c r="F30" s="33"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="191.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="21" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C31" s="15" t="s">
         <v>40</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="E31" s="15"/>
       <c r="F31" s="23" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="165.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="24" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B32" s="25" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C32" s="25" t="s">
         <v>44</v>
       </c>
       <c r="D32" s="25" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E32" s="25"/>
       <c r="F32" s="23"/>
     </row>
-    <row r="33" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="26"/>
-      <c r="B33" s="27"/>
-      <c r="C33" s="27"/>
-      <c r="D33" s="27"/>
-      <c r="E33" s="27"/>
-      <c r="F33" s="28"/>
+    <row r="33" customFormat="false" ht="89.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="B33" s="35" t="s">
+        <v>85</v>
+      </c>
+      <c r="C33" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="D33" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="E33" s="35"/>
+      <c r="F33" s="36"/>
     </row>
     <row r="34" customFormat="false" ht="127.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="29"/>
-      <c r="B34" s="30"/>
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="30"/>
-      <c r="F34" s="31"/>
+      <c r="A34" s="26"/>
+      <c r="B34" s="27"/>
+      <c r="C34" s="27"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="27"/>
+      <c r="F34" s="28"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3170,116 +3318,116 @@
     <row r="2" customFormat="false" ht="179.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="63"/>
       <c r="B2" s="64" t="s">
-        <v>284</v>
+        <v>308</v>
       </c>
       <c r="C2" s="65" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D2" s="65" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="E2" s="65" t="s">
-        <v>285</v>
+        <v>309</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="101.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="64"/>
       <c r="B3" s="64" t="s">
-        <v>286</v>
+        <v>310</v>
       </c>
       <c r="C3" s="64" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="D3" s="65" t="s">
-        <v>285</v>
+        <v>309</v>
       </c>
       <c r="E3" s="65" t="s">
-        <v>287</v>
+        <v>311</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="86.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="64"/>
       <c r="B4" s="64" t="s">
-        <v>288</v>
+        <v>312</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D4" s="65" t="s">
-        <v>287</v>
+        <v>311</v>
       </c>
       <c r="E4" s="65" t="s">
-        <v>289</v>
+        <v>313</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="89.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="64"/>
       <c r="B5" s="64" t="s">
-        <v>290</v>
+        <v>314</v>
       </c>
       <c r="C5" s="65" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="D5" s="65" t="s">
-        <v>289</v>
+        <v>313</v>
       </c>
       <c r="E5" s="64"/>
     </row>
     <row r="6" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="63"/>
       <c r="B6" s="64" t="s">
-        <v>291</v>
+        <v>315</v>
       </c>
       <c r="C6" s="65" t="s">
-        <v>292</v>
+        <v>316</v>
       </c>
       <c r="D6" s="65" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="E6" s="65" t="s">
-        <v>293</v>
+        <v>317</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="86.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="64"/>
       <c r="B7" s="64" t="s">
-        <v>286</v>
+        <v>310</v>
       </c>
       <c r="C7" s="64" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="D7" s="65" t="s">
-        <v>285</v>
+        <v>309</v>
       </c>
       <c r="E7" s="65" t="s">
-        <v>287</v>
+        <v>311</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="107.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="66"/>
       <c r="B8" s="66" t="s">
-        <v>288</v>
+        <v>312</v>
       </c>
       <c r="C8" s="66" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D8" s="67" t="s">
-        <v>287</v>
+        <v>311</v>
       </c>
       <c r="E8" s="67" t="s">
-        <v>289</v>
+        <v>313</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="123.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="68"/>
       <c r="B9" s="68" t="s">
-        <v>290</v>
+        <v>314</v>
       </c>
       <c r="C9" s="69" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="D9" s="69" t="s">
-        <v>289</v>
+        <v>313</v>
       </c>
       <c r="E9" s="68"/>
     </row>
@@ -3322,22 +3470,22 @@
   <sheetData>
     <row r="1" s="42" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="39" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="B1" s="39" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C1" s="40" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D1" s="40" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="E1" s="40" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="F1" s="40" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G1" s="40" t="s">
         <v>27</v>
@@ -3346,19 +3494,19 @@
         <v>33</v>
       </c>
       <c r="I1" s="41" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="J1" s="40" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K1" s="41" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="XFD1" s="2"/>
     </row>
     <row r="2" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="43" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="B2" s="44" t="n">
         <v>0</v>
@@ -3394,7 +3542,7 @@
     </row>
     <row r="3" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="48" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="B3" s="44" t="n">
         <v>1</v>
@@ -3430,7 +3578,7 @@
     </row>
     <row r="4" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="48" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B4" s="44" t="n">
         <v>2</v>
@@ -3466,7 +3614,7 @@
     </row>
     <row r="5" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="48" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="B5" s="44" t="n">
         <v>3</v>
@@ -3502,7 +3650,7 @@
     </row>
     <row r="6" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="48" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="B6" s="44" t="n">
         <v>4</v>
@@ -3538,7 +3686,7 @@
     </row>
     <row r="7" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="48" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="B7" s="44" t="n">
         <v>5</v>
@@ -3574,7 +3722,7 @@
     </row>
     <row r="8" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="48" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="B8" s="44" t="n">
         <v>6</v>
@@ -3610,7 +3758,7 @@
     </row>
     <row r="9" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="48" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="B9" s="44" t="n">
         <v>7</v>
@@ -3646,7 +3794,7 @@
     </row>
     <row r="10" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="48" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="B10" s="44" t="n">
         <v>8</v>
@@ -3682,7 +3830,7 @@
     </row>
     <row r="11" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="48" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="B11" s="44" t="n">
         <v>9</v>
@@ -3718,7 +3866,7 @@
     </row>
     <row r="12" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="48" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="B12" s="44" t="n">
         <v>10</v>
@@ -3754,7 +3902,7 @@
     </row>
     <row r="13" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="48" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="B13" s="44" t="n">
         <v>11</v>
@@ -3789,7 +3937,7 @@
     </row>
     <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="48" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="B14" s="44" t="n">
         <v>12</v>
@@ -3824,7 +3972,7 @@
     </row>
     <row r="15" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="48" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="B15" s="44" t="n">
         <v>13</v>
@@ -3860,7 +4008,7 @@
     </row>
     <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="50" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="B16" s="51" t="n">
         <v>14</v>
@@ -3947,7 +4095,7 @@
     </row>
     <row r="20" s="3" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>84</v>
@@ -3993,34 +4141,34 @@
     </row>
     <row r="26" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="57" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="B26" s="57" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C26" s="57" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="D26" s="57" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="E26" s="57" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="F26" s="57" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="G26" s="57" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="H26" s="57" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="I26" s="57" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="J26" s="58" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4044,7 +4192,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="59" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C28" s="45"/>
       <c r="D28" s="45"/>
@@ -4060,7 +4208,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="59" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C29" s="60"/>
       <c r="D29" s="60"/>
@@ -4076,7 +4224,7 @@
         <v>4</v>
       </c>
       <c r="B30" s="59" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C30" s="45"/>
       <c r="D30" s="45"/>
@@ -4293,58 +4441,58 @@
     <row r="2" customFormat="false" ht="179.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="63"/>
       <c r="B2" s="64" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="C2" s="65" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D2" s="65" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="65" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="101.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="66"/>
       <c r="B3" s="66" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="C3" s="66" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="D3" s="67" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="E3" s="67" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="86.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="68"/>
       <c r="B4" s="68" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="C4" s="68" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D4" s="69" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E4" s="69" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="89.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="68"/>
       <c r="B5" s="68" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C5" s="69" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="D5" s="69" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="E5" s="68"/>
     </row>
@@ -4397,7 +4545,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="73" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="G1" s="74"/>
       <c r="H1" s="74"/>
@@ -4405,13 +4553,13 @@
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6"/>
       <c r="B2" s="10" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>9</v>
@@ -4423,16 +4571,16 @@
     <row r="3" customFormat="false" ht="201.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6"/>
       <c r="B3" s="10" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="F3" s="78"/>
       <c r="G3" s="77"/>
@@ -4441,13 +4589,13 @@
     <row r="4" customFormat="false" ht="76.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6"/>
       <c r="B4" s="10" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>9</v>
@@ -4459,13 +4607,13 @@
     <row r="5" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6"/>
       <c r="B5" s="10" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>9</v>
@@ -4477,16 +4625,16 @@
     <row r="6" s="2" customFormat="true" ht="73.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="7" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>20</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="F6" s="78"/>
       <c r="G6" s="77"/>
@@ -4497,16 +4645,16 @@
         <v>22</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="F7" s="76"/>
       <c r="G7" s="12"/>
@@ -4517,16 +4665,16 @@
         <v>27</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>29</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F8" s="76"/>
       <c r="G8" s="77"/>
@@ -4537,36 +4685,36 @@
         <v>27</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="F9" s="76"/>
       <c r="G9" s="77"/>
       <c r="H9" s="77"/>
     </row>
     <row r="10" s="2" customFormat="true" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="32" t="s">
+      <c r="A10" s="29" t="s">
         <v>33</v>
       </c>
       <c r="B10" s="79" t="s">
-        <v>138</v>
-      </c>
-      <c r="C10" s="33" t="s">
+        <v>146</v>
+      </c>
+      <c r="C10" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="33" t="s">
-        <v>131</v>
-      </c>
-      <c r="E10" s="33" t="s">
+      <c r="D10" s="30" t="s">
         <v>139</v>
+      </c>
+      <c r="E10" s="30" t="s">
+        <v>147</v>
       </c>
       <c r="F10" s="80"/>
       <c r="G10" s="77"/>
@@ -4577,16 +4725,16 @@
         <v>33</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="F11" s="81"/>
       <c r="G11" s="77"/>
@@ -4597,17 +4745,17 @@
         <v>33</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>40</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E12" s="15"/>
       <c r="F12" s="23" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="G12" s="77"/>
       <c r="H12" s="77"/>
@@ -4617,13 +4765,13 @@
         <v>33</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>44</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="E13" s="15"/>
       <c r="F13" s="23"/>
@@ -4631,128 +4779,144 @@
       <c r="H13" s="77"/>
     </row>
     <row r="14" customFormat="false" ht="211.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="83"/>
-      <c r="B14" s="84"/>
-      <c r="C14" s="84"/>
-      <c r="D14" s="84"/>
-      <c r="E14" s="84"/>
-      <c r="F14" s="28"/>
+      <c r="A14" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="35" t="s">
+        <v>155</v>
+      </c>
+      <c r="C14" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="35" t="s">
+        <v>156</v>
+      </c>
+      <c r="E14" s="35"/>
+      <c r="F14" s="36"/>
       <c r="G14" s="77"/>
       <c r="H14" s="77"/>
     </row>
     <row r="15" customFormat="false" ht="211.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="29"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="31"/>
+      <c r="A15" s="26"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="28"/>
       <c r="G15" s="77"/>
       <c r="H15" s="77"/>
     </row>
     <row r="16" customFormat="false" ht="159.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="C16" s="33" t="s">
+      <c r="A16" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" s="30" t="s">
+        <v>157</v>
+      </c>
+      <c r="C16" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="D16" s="33" t="s">
-        <v>148</v>
-      </c>
-      <c r="E16" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="F16" s="34"/>
+      <c r="D16" s="30" t="s">
+        <v>158</v>
+      </c>
+      <c r="E16" s="30" t="s">
+        <v>159</v>
+      </c>
+      <c r="F16" s="31"/>
       <c r="G16" s="82"/>
       <c r="H16" s="82"/>
     </row>
     <row r="17" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="35" t="s">
-        <v>46</v>
+      <c r="A17" s="32" t="s">
+        <v>48</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="C17" s="11" t="s">
         <v>24</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="F17" s="36"/>
+        <v>161</v>
+      </c>
+      <c r="F17" s="33"/>
     </row>
     <row r="18" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="C18" s="15" t="s">
         <v>40</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="E18" s="15"/>
       <c r="F18" s="23" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="C19" s="15" t="s">
         <v>44</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E19" s="15"/>
       <c r="F19" s="23"/>
     </row>
     <row r="20" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="83"/>
-      <c r="B20" s="84"/>
-      <c r="C20" s="84"/>
-      <c r="D20" s="84"/>
-      <c r="E20" s="84"/>
-      <c r="F20" s="28"/>
+      <c r="A20" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="35" t="s">
+        <v>167</v>
+      </c>
+      <c r="C20" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" s="35" t="s">
+        <v>168</v>
+      </c>
+      <c r="E20" s="35"/>
+      <c r="F20" s="36"/>
     </row>
     <row r="21" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="29"/>
-      <c r="B21" s="30"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="31"/>
+      <c r="A21" s="26"/>
+      <c r="B21" s="27"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="28"/>
     </row>
     <row r="22" customFormat="false" ht="150.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="32" t="s">
-        <v>57</v>
+      <c r="A22" s="29" t="s">
+        <v>61</v>
       </c>
       <c r="B22" s="79" t="s">
-        <v>157</v>
-      </c>
-      <c r="C22" s="33" t="s">
+        <v>169</v>
+      </c>
+      <c r="C22" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="D22" s="33" t="s">
-        <v>131</v>
-      </c>
-      <c r="E22" s="33" t="s">
-        <v>158</v>
+      <c r="D22" s="30" t="s">
+        <v>139</v>
+      </c>
+      <c r="E22" s="30" t="s">
+        <v>170</v>
       </c>
       <c r="F22" s="80"/>
       <c r="G22" s="77"/>
@@ -4760,154 +4924,162 @@
     </row>
     <row r="23" customFormat="false" ht="210.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="21" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="C23" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="F23" s="81"/>
       <c r="G23" s="77"/>
       <c r="H23" s="77"/>
     </row>
     <row r="24" customFormat="false" ht="177.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="85" t="s">
-        <v>57</v>
-      </c>
-      <c r="B24" s="86" t="s">
-        <v>161</v>
-      </c>
-      <c r="C24" s="86" t="s">
+      <c r="A24" s="83" t="s">
+        <v>61</v>
+      </c>
+      <c r="B24" s="84" t="s">
+        <v>173</v>
+      </c>
+      <c r="C24" s="84" t="s">
         <v>40</v>
       </c>
-      <c r="D24" s="86" t="s">
-        <v>162</v>
-      </c>
-      <c r="E24" s="86"/>
-      <c r="F24" s="87" t="s">
-        <v>163</v>
+      <c r="D24" s="84" t="s">
+        <v>174</v>
+      </c>
+      <c r="E24" s="84"/>
+      <c r="F24" s="36" t="s">
+        <v>175</v>
       </c>
       <c r="G24" s="77"/>
       <c r="H24" s="77"/>
     </row>
     <row r="25" customFormat="false" ht="202.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="83" t="s">
-        <v>57</v>
-      </c>
-      <c r="B25" s="84" t="s">
-        <v>164</v>
-      </c>
-      <c r="C25" s="84" t="s">
+      <c r="A25" s="85" t="s">
+        <v>61</v>
+      </c>
+      <c r="B25" s="86" t="s">
+        <v>176</v>
+      </c>
+      <c r="C25" s="86" t="s">
         <v>44</v>
       </c>
-      <c r="D25" s="84" t="s">
-        <v>165</v>
-      </c>
-      <c r="E25" s="84"/>
-      <c r="F25" s="28"/>
+      <c r="D25" s="86" t="s">
+        <v>177</v>
+      </c>
+      <c r="E25" s="86"/>
+      <c r="F25" s="87"/>
       <c r="G25" s="77"/>
       <c r="H25" s="77"/>
     </row>
     <row r="26" customFormat="false" ht="202.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="83"/>
-      <c r="B26" s="84"/>
-      <c r="C26" s="84"/>
-      <c r="D26" s="84"/>
-      <c r="E26" s="84"/>
-      <c r="F26" s="28"/>
+      <c r="A26" s="88" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" s="89" t="s">
+        <v>178</v>
+      </c>
+      <c r="C26" s="89" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" s="89" t="s">
+        <v>179</v>
+      </c>
+      <c r="E26" s="89"/>
+      <c r="F26" s="87"/>
       <c r="G26" s="77"/>
       <c r="H26" s="77"/>
     </row>
     <row r="27" customFormat="false" ht="202.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="29"/>
-      <c r="B27" s="30"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="31"/>
+      <c r="A27" s="26"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="28"/>
       <c r="G27" s="77"/>
       <c r="H27" s="77"/>
     </row>
     <row r="28" customFormat="false" ht="156.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="32" t="s">
-        <v>68</v>
-      </c>
-      <c r="B28" s="33" t="s">
-        <v>166</v>
-      </c>
-      <c r="C28" s="33" t="s">
+      <c r="A28" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="B28" s="30" t="s">
+        <v>180</v>
+      </c>
+      <c r="C28" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="D28" s="33" t="s">
-        <v>167</v>
-      </c>
-      <c r="E28" s="33" t="s">
-        <v>168</v>
-      </c>
-      <c r="F28" s="34"/>
+      <c r="D28" s="30" t="s">
+        <v>181</v>
+      </c>
+      <c r="E28" s="30" t="s">
+        <v>182</v>
+      </c>
+      <c r="F28" s="31"/>
       <c r="G28" s="77"/>
       <c r="H28" s="77"/>
     </row>
     <row r="29" customFormat="false" ht="248.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="35" t="s">
-        <v>68</v>
+      <c r="A29" s="32" t="s">
+        <v>74</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="C29" s="11" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="F29" s="36"/>
+        <v>184</v>
+      </c>
+      <c r="F29" s="33"/>
       <c r="G29" s="77"/>
       <c r="H29" s="77"/>
     </row>
     <row r="30" customFormat="false" ht="100.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="21" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="C30" s="15" t="s">
         <v>40</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="E30" s="15"/>
       <c r="F30" s="23" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="G30" s="77"/>
       <c r="H30" s="77"/>
     </row>
     <row r="31" customFormat="false" ht="108.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="21" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="C31" s="15" t="s">
         <v>44</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="E31" s="15"/>
       <c r="F31" s="23"/>
@@ -4915,22 +5087,30 @@
       <c r="H31" s="77"/>
     </row>
     <row r="32" customFormat="false" ht="108.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="83"/>
-      <c r="B32" s="84"/>
-      <c r="C32" s="84"/>
-      <c r="D32" s="84"/>
-      <c r="E32" s="84"/>
-      <c r="F32" s="28"/>
+      <c r="A32" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="B32" s="35" t="s">
+        <v>190</v>
+      </c>
+      <c r="C32" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="D32" s="35" t="s">
+        <v>191</v>
+      </c>
+      <c r="E32" s="35"/>
+      <c r="F32" s="36"/>
       <c r="G32" s="77"/>
       <c r="H32" s="77"/>
     </row>
     <row r="33" customFormat="false" ht="130.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="29"/>
-      <c r="B33" s="88"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="88"/>
-      <c r="E33" s="88"/>
-      <c r="F33" s="89"/>
+      <c r="A33" s="26"/>
+      <c r="B33" s="90"/>
+      <c r="C33" s="27"/>
+      <c r="D33" s="90"/>
+      <c r="E33" s="90"/>
+      <c r="F33" s="91"/>
       <c r="G33" s="77"/>
       <c r="H33" s="77"/>
     </row>
@@ -5032,51 +5212,51 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="11" style="3" width="10.16"/>
   </cols>
   <sheetData>
-    <row r="1" s="93" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="95" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="39" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="B1" s="40" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C1" s="40" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="D1" s="40" t="s">
-        <v>82</v>
-      </c>
-      <c r="E1" s="90" t="s">
-        <v>177</v>
-      </c>
-      <c r="F1" s="90" t="s">
+        <v>90</v>
+      </c>
+      <c r="E1" s="92" t="s">
+        <v>193</v>
+      </c>
+      <c r="F1" s="92" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="91" t="s">
+      <c r="G1" s="93" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="91" t="s">
-        <v>57</v>
-      </c>
-      <c r="I1" s="91" t="s">
-        <v>46</v>
-      </c>
-      <c r="J1" s="91" t="s">
-        <v>68</v>
-      </c>
-      <c r="K1" s="92"/>
+      <c r="H1" s="93" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="93" t="s">
+        <v>48</v>
+      </c>
+      <c r="J1" s="93" t="s">
+        <v>74</v>
+      </c>
+      <c r="K1" s="94"/>
       <c r="XFD1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="94" t="s">
-        <v>85</v>
-      </c>
-      <c r="B2" s="95" t="n">
+      <c r="A2" s="96" t="s">
+        <v>93</v>
+      </c>
+      <c r="B2" s="97" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="95" t="n">
+      <c r="C2" s="97" t="n">
         <v>2273097</v>
       </c>
-      <c r="D2" s="96" t="n">
+      <c r="D2" s="98" t="n">
         <v>2095051</v>
       </c>
       <c r="E2" s="45" t="n">
@@ -5100,16 +5280,16 @@
       <c r="L2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="94" t="s">
-        <v>178</v>
-      </c>
-      <c r="B3" s="95" t="n">
+      <c r="A3" s="96" t="s">
+        <v>194</v>
+      </c>
+      <c r="B3" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="95" t="n">
+      <c r="C3" s="97" t="n">
         <v>231073</v>
       </c>
-      <c r="D3" s="96" t="n">
+      <c r="D3" s="98" t="n">
         <v>172846</v>
       </c>
       <c r="E3" s="45" t="n">
@@ -5133,16 +5313,16 @@
       <c r="L3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="94" t="s">
-        <v>179</v>
-      </c>
-      <c r="B4" s="95" t="n">
+      <c r="A4" s="96" t="s">
+        <v>195</v>
+      </c>
+      <c r="B4" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="95" t="n">
+      <c r="C4" s="97" t="n">
         <v>128027</v>
       </c>
-      <c r="D4" s="96" t="n">
+      <c r="D4" s="98" t="n">
         <v>128014</v>
       </c>
       <c r="E4" s="45" t="n">
@@ -5166,16 +5346,16 @@
       <c r="L4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="94" t="s">
-        <v>180</v>
-      </c>
-      <c r="B5" s="95" t="n">
+      <c r="A5" s="96" t="s">
+        <v>196</v>
+      </c>
+      <c r="B5" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="95" t="n">
+      <c r="C5" s="97" t="n">
         <v>158930</v>
       </c>
-      <c r="D5" s="96" t="n">
+      <c r="D5" s="98" t="n">
         <v>90694</v>
       </c>
       <c r="E5" s="45" t="n">
@@ -5199,16 +5379,16 @@
       <c r="L5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="94" t="s">
-        <v>181</v>
-      </c>
-      <c r="B6" s="95" t="n">
+      <c r="A6" s="96" t="s">
+        <v>197</v>
+      </c>
+      <c r="B6" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="95" t="n">
+      <c r="C6" s="97" t="n">
         <v>10293</v>
       </c>
-      <c r="D6" s="96" t="n">
+      <c r="D6" s="98" t="n">
         <v>10286</v>
       </c>
       <c r="E6" s="45" t="n">
@@ -5232,16 +5412,16 @@
       <c r="L6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="94" t="s">
-        <v>182</v>
-      </c>
-      <c r="B7" s="95" t="n">
+      <c r="A7" s="96" t="s">
+        <v>198</v>
+      </c>
+      <c r="B7" s="97" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="95" t="n">
+      <c r="C7" s="97" t="n">
         <v>7938</v>
       </c>
-      <c r="D7" s="96" t="n">
+      <c r="D7" s="98" t="n">
         <v>5931</v>
       </c>
       <c r="E7" s="45" t="n">
@@ -5265,16 +5445,16 @@
       <c r="L7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="94" t="s">
-        <v>183</v>
-      </c>
-      <c r="B8" s="95" t="n">
+      <c r="A8" s="96" t="s">
+        <v>199</v>
+      </c>
+      <c r="B8" s="97" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="95" t="n">
+      <c r="C8" s="97" t="n">
         <v>5796</v>
       </c>
-      <c r="D8" s="96" t="n">
+      <c r="D8" s="98" t="n">
         <v>5385</v>
       </c>
       <c r="E8" s="45" t="n">
@@ -5298,16 +5478,16 @@
       <c r="L8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="94" t="s">
-        <v>184</v>
-      </c>
-      <c r="B9" s="95" t="n">
+      <c r="A9" s="96" t="s">
+        <v>200</v>
+      </c>
+      <c r="B9" s="97" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="95" t="n">
+      <c r="C9" s="97" t="n">
         <v>5499</v>
       </c>
-      <c r="D9" s="96" t="n">
+      <c r="D9" s="98" t="n">
         <v>5228</v>
       </c>
       <c r="E9" s="45" t="n">
@@ -5331,16 +5511,16 @@
       <c r="L9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="94" t="s">
-        <v>185</v>
-      </c>
-      <c r="B10" s="95" t="n">
+      <c r="A10" s="96" t="s">
+        <v>201</v>
+      </c>
+      <c r="B10" s="97" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="95" t="n">
+      <c r="C10" s="97" t="n">
         <v>5897</v>
       </c>
-      <c r="D10" s="96" t="n">
+      <c r="D10" s="98" t="n">
         <v>3219</v>
       </c>
       <c r="E10" s="45" t="n">
@@ -5364,16 +5544,16 @@
       <c r="L10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="94" t="s">
-        <v>89</v>
-      </c>
-      <c r="B11" s="95" t="n">
+      <c r="A11" s="96" t="s">
+        <v>97</v>
+      </c>
+      <c r="B11" s="97" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="95" t="n">
+      <c r="C11" s="97" t="n">
         <v>1966</v>
       </c>
-      <c r="D11" s="96" t="n">
+      <c r="D11" s="98" t="n">
         <v>1948</v>
       </c>
       <c r="E11" s="45" t="n">
@@ -5397,16 +5577,16 @@
       <c r="L11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="94" t="s">
-        <v>186</v>
-      </c>
-      <c r="B12" s="95" t="n">
+      <c r="A12" s="96" t="s">
+        <v>202</v>
+      </c>
+      <c r="B12" s="97" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="95" t="n">
+      <c r="C12" s="97" t="n">
         <v>1507</v>
       </c>
-      <c r="D12" s="96" t="n">
+      <c r="D12" s="98" t="n">
         <v>1470</v>
       </c>
       <c r="E12" s="45" t="n">
@@ -5430,16 +5610,16 @@
       <c r="L12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="94" t="s">
-        <v>187</v>
-      </c>
-      <c r="B13" s="95" t="n">
+      <c r="A13" s="96" t="s">
+        <v>203</v>
+      </c>
+      <c r="B13" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="95" t="n">
+      <c r="C13" s="97" t="n">
         <v>652</v>
       </c>
-      <c r="D13" s="96" t="n">
+      <c r="D13" s="98" t="n">
         <v>652</v>
       </c>
       <c r="E13" s="45" t="n">
@@ -5463,16 +5643,16 @@
       <c r="L13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="94" t="s">
-        <v>188</v>
-      </c>
-      <c r="B14" s="95" t="n">
+      <c r="A14" s="96" t="s">
+        <v>204</v>
+      </c>
+      <c r="B14" s="97" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="95" t="n">
+      <c r="C14" s="97" t="n">
         <v>36</v>
       </c>
-      <c r="D14" s="96" t="n">
+      <c r="D14" s="98" t="n">
         <v>36</v>
       </c>
       <c r="E14" s="45" t="n">
@@ -5496,16 +5676,16 @@
       <c r="L14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="94" t="s">
-        <v>189</v>
-      </c>
-      <c r="B15" s="95" t="n">
+      <c r="A15" s="96" t="s">
+        <v>205</v>
+      </c>
+      <c r="B15" s="97" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="95" t="n">
+      <c r="C15" s="97" t="n">
         <v>21</v>
       </c>
-      <c r="D15" s="96" t="n">
+      <c r="D15" s="98" t="n">
         <v>21</v>
       </c>
       <c r="E15" s="45" t="n">
@@ -5529,16 +5709,16 @@
       <c r="L15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="97" t="s">
-        <v>190</v>
-      </c>
-      <c r="B16" s="98" t="n">
+      <c r="A16" s="99" t="s">
+        <v>206</v>
+      </c>
+      <c r="B16" s="100" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="98" t="n">
+      <c r="C16" s="100" t="n">
         <v>11</v>
       </c>
-      <c r="D16" s="98" t="n">
+      <c r="D16" s="100" t="n">
         <v>11</v>
       </c>
       <c r="E16" s="52" t="n">
@@ -5607,8 +5787,8 @@
       <c r="L19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="92" t="s">
-        <v>100</v>
+      <c r="A20" s="94" t="s">
+        <v>108</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>79</v>
@@ -5699,11 +5879,11 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultColWidth="10.16796875" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="99" width="45.65"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="99" width="74.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="99" width="74.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="99" width="55.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="99" width="52.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="101" width="45.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="101" width="74.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="101" width="74.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="101" width="55.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="101" width="52.63"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5726,58 +5906,58 @@
     <row r="2" customFormat="false" ht="179.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="63"/>
       <c r="B2" s="64" t="s">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="C2" s="65" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D2" s="65" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="E2" s="65" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="131.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="64"/>
       <c r="B3" s="64" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="C3" s="64" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="D3" s="65" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="E3" s="65" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="141.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="64"/>
       <c r="B4" s="64" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D4" s="65" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="E4" s="65" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="176.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="64"/>
       <c r="B5" s="64" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="C5" s="65" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="D5" s="65" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="E5" s="64"/>
     </row>
@@ -5801,11 +5981,11 @@
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultColWidth="10.16796875" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="99" width="45.65"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="99" width="74.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="99" width="74.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="99" width="55.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="99" width="52.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="101" width="45.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="101" width="74.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="101" width="74.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="101" width="55.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="101" width="52.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="71.46"/>
   </cols>
   <sheetData>
@@ -5825,115 +6005,115 @@
       <c r="E1" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="100" t="s">
-        <v>198</v>
+      <c r="F1" s="102" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="179.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="63" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="B2" s="64" t="s">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="C2" s="65" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D2" s="65" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="E2" s="65" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="F2" s="16"/>
     </row>
     <row r="3" customFormat="false" ht="179.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="63" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="B3" s="64" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="C3" s="65" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="D3" s="65" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="E3" s="65" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="F3" s="16"/>
     </row>
     <row r="4" customFormat="false" ht="131.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="101" t="s">
-        <v>203</v>
-      </c>
-      <c r="B4" s="102" t="s">
-        <v>204</v>
-      </c>
-      <c r="C4" s="103" t="s">
-        <v>205</v>
-      </c>
-      <c r="D4" s="103" t="s">
-        <v>206</v>
-      </c>
-      <c r="E4" s="103"/>
-      <c r="F4" s="104"/>
+      <c r="A4" s="103" t="s">
+        <v>219</v>
+      </c>
+      <c r="B4" s="104" t="s">
+        <v>220</v>
+      </c>
+      <c r="C4" s="105" t="s">
+        <v>221</v>
+      </c>
+      <c r="D4" s="105" t="s">
+        <v>222</v>
+      </c>
+      <c r="E4" s="105"/>
+      <c r="F4" s="106"/>
     </row>
     <row r="5" customFormat="false" ht="131.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="105" t="s">
-        <v>207</v>
-      </c>
-      <c r="B5" s="106" t="s">
-        <v>208</v>
-      </c>
-      <c r="C5" s="107" t="s">
-        <v>209</v>
-      </c>
-      <c r="D5" s="107" t="s">
-        <v>206</v>
-      </c>
-      <c r="E5" s="107"/>
-      <c r="F5" s="108"/>
+      <c r="A5" s="107" t="s">
+        <v>223</v>
+      </c>
+      <c r="B5" s="108" t="s">
+        <v>224</v>
+      </c>
+      <c r="C5" s="109" t="s">
+        <v>225</v>
+      </c>
+      <c r="D5" s="109" t="s">
+        <v>222</v>
+      </c>
+      <c r="E5" s="109"/>
+      <c r="F5" s="110"/>
     </row>
     <row r="6" customFormat="false" ht="141.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="109" t="s">
-        <v>210</v>
-      </c>
-      <c r="B6" s="110" t="s">
-        <v>211</v>
-      </c>
-      <c r="C6" s="110" t="s">
-        <v>212</v>
-      </c>
-      <c r="D6" s="111" t="s">
-        <v>202</v>
-      </c>
-      <c r="E6" s="111" t="s">
-        <v>213</v>
-      </c>
-      <c r="F6" s="112"/>
+      <c r="A6" s="111" t="s">
+        <v>226</v>
+      </c>
+      <c r="B6" s="112" t="s">
+        <v>227</v>
+      </c>
+      <c r="C6" s="112" t="s">
+        <v>228</v>
+      </c>
+      <c r="D6" s="113" t="s">
+        <v>218</v>
+      </c>
+      <c r="E6" s="113" t="s">
+        <v>229</v>
+      </c>
+      <c r="F6" s="114"/>
     </row>
     <row r="7" customFormat="false" ht="176.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="113" t="s">
-        <v>210</v>
-      </c>
-      <c r="B7" s="114" t="s">
-        <v>214</v>
-      </c>
-      <c r="C7" s="115" t="s">
-        <v>205</v>
-      </c>
-      <c r="D7" s="115" t="s">
-        <v>215</v>
-      </c>
-      <c r="E7" s="114"/>
-      <c r="F7" s="116"/>
+      <c r="A7" s="115" t="s">
+        <v>226</v>
+      </c>
+      <c r="B7" s="116" t="s">
+        <v>230</v>
+      </c>
+      <c r="C7" s="117" t="s">
+        <v>221</v>
+      </c>
+      <c r="D7" s="117" t="s">
+        <v>231</v>
+      </c>
+      <c r="E7" s="116"/>
+      <c r="F7" s="118"/>
     </row>
     <row r="8" customFormat="false" ht="168.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="117" t="s">
-        <v>216</v>
+      <c r="A8" s="119" t="s">
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -5980,7 +6160,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="G1" s="77"/>
       <c r="H1" s="77"/>
@@ -5995,7 +6175,7 @@
         <v>7</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>9</v>
@@ -6010,13 +6190,13 @@
     <row r="3" customFormat="false" ht="74.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6"/>
       <c r="B3" s="7" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>9</v>
@@ -6031,16 +6211,16 @@
     <row r="4" customFormat="false" ht="173.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6"/>
       <c r="B4" s="7" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="F4" s="8"/>
       <c r="G4" s="77"/>
@@ -6052,13 +6232,13 @@
     <row r="5" customFormat="false" ht="85.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6"/>
       <c r="B5" s="7" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>9</v>
@@ -6073,16 +6253,16 @@
     <row r="6" s="2" customFormat="true" ht="75.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="7" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>20</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="77"/>
@@ -6096,16 +6276,16 @@
         <v>22</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>24</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="12"/>
@@ -6116,16 +6296,16 @@
         <v>27</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>29</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="77"/>
@@ -6139,16 +6319,16 @@
         <v>27</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>24</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="77"/>
@@ -6158,22 +6338,22 @@
       <c r="K9" s="77"/>
     </row>
     <row r="10" s="2" customFormat="true" ht="106.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="32" t="s">
+      <c r="A10" s="29" t="s">
         <v>33</v>
       </c>
       <c r="B10" s="79" t="s">
-        <v>233</v>
-      </c>
-      <c r="C10" s="33" t="s">
+        <v>249</v>
+      </c>
+      <c r="C10" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="33" t="s">
-        <v>227</v>
-      </c>
-      <c r="E10" s="33" t="s">
-        <v>234</v>
-      </c>
-      <c r="F10" s="118"/>
+      <c r="D10" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="E10" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="F10" s="120"/>
       <c r="G10" s="77"/>
       <c r="H10" s="77"/>
       <c r="I10" s="77"/>
@@ -6185,16 +6365,16 @@
         <v>33</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="F11" s="22"/>
       <c r="G11" s="77"/>
@@ -6208,17 +6388,17 @@
         <v>33</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>40</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="E12" s="15"/>
       <c r="F12" s="23" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="G12" s="77"/>
       <c r="H12" s="77"/>
@@ -6231,13 +6411,13 @@
         <v>33</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>44</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="E13" s="15"/>
       <c r="F13" s="23"/>
@@ -6248,12 +6428,20 @@
       <c r="K13" s="77"/>
     </row>
     <row r="14" customFormat="false" ht="130.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="83"/>
-      <c r="B14" s="84"/>
-      <c r="C14" s="84"/>
-      <c r="D14" s="84"/>
-      <c r="E14" s="84"/>
-      <c r="F14" s="28"/>
+      <c r="A14" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="35" t="s">
+        <v>258</v>
+      </c>
+      <c r="C14" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="35" t="s">
+        <v>259</v>
+      </c>
+      <c r="E14" s="35"/>
+      <c r="F14" s="36"/>
       <c r="G14" s="77"/>
       <c r="H14" s="77"/>
       <c r="I14" s="77"/>
@@ -6261,12 +6449,12 @@
       <c r="K14" s="77"/>
     </row>
     <row r="15" customFormat="false" ht="114.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="29"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="31"/>
+      <c r="A15" s="26"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="28"/>
       <c r="G15" s="77"/>
       <c r="H15" s="77"/>
       <c r="I15" s="77"/>
@@ -6274,22 +6462,22 @@
       <c r="K15" s="77"/>
     </row>
     <row r="16" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" s="33" t="s">
-        <v>242</v>
-      </c>
-      <c r="C16" s="33" t="s">
+      <c r="A16" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" s="30" t="s">
+        <v>260</v>
+      </c>
+      <c r="C16" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="D16" s="33" t="s">
-        <v>243</v>
-      </c>
-      <c r="E16" s="33" t="s">
-        <v>244</v>
-      </c>
-      <c r="F16" s="34"/>
+      <c r="D16" s="30" t="s">
+        <v>261</v>
+      </c>
+      <c r="E16" s="30" t="s">
+        <v>262</v>
+      </c>
+      <c r="F16" s="31"/>
       <c r="G16" s="77"/>
       <c r="H16" s="77"/>
       <c r="I16" s="77"/>
@@ -6298,19 +6486,19 @@
     </row>
     <row r="17" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="C17" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="F17" s="23"/>
       <c r="G17" s="77"/>
@@ -6320,21 +6508,21 @@
       <c r="K17" s="77"/>
     </row>
     <row r="18" customFormat="false" ht="184.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="85" t="s">
-        <v>46</v>
-      </c>
-      <c r="B18" s="119" t="s">
-        <v>247</v>
-      </c>
-      <c r="C18" s="86" t="s">
+      <c r="A18" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="C18" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="86" t="s">
-        <v>248</v>
-      </c>
-      <c r="E18" s="86"/>
-      <c r="F18" s="87" t="s">
-        <v>249</v>
+      <c r="D18" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="E18" s="15"/>
+      <c r="F18" s="23" t="s">
+        <v>267</v>
       </c>
       <c r="G18" s="77"/>
       <c r="H18" s="77"/>
@@ -6344,19 +6532,19 @@
     </row>
     <row r="19" customFormat="false" ht="207.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="83" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B19" s="84" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="C19" s="84" t="s">
         <v>44</v>
       </c>
       <c r="D19" s="84" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="E19" s="84"/>
-      <c r="F19" s="28"/>
+      <c r="F19" s="36"/>
       <c r="G19" s="77"/>
       <c r="H19" s="77"/>
       <c r="I19" s="77"/>
@@ -6364,12 +6552,20 @@
       <c r="K19" s="77"/>
     </row>
     <row r="20" customFormat="false" ht="207.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="83"/>
-      <c r="B20" s="84"/>
-      <c r="C20" s="84"/>
-      <c r="D20" s="84"/>
-      <c r="E20" s="84"/>
-      <c r="F20" s="28"/>
+      <c r="A20" s="88" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="89" t="s">
+        <v>270</v>
+      </c>
+      <c r="C20" s="89" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" s="89" t="s">
+        <v>271</v>
+      </c>
+      <c r="E20" s="89"/>
+      <c r="F20" s="87"/>
       <c r="G20" s="77"/>
       <c r="H20" s="77"/>
       <c r="I20" s="77"/>
@@ -6377,12 +6573,12 @@
       <c r="K20" s="77"/>
     </row>
     <row r="21" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="120"/>
-      <c r="B21" s="121"/>
-      <c r="C21" s="121"/>
-      <c r="D21" s="121"/>
-      <c r="E21" s="121"/>
-      <c r="F21" s="122"/>
+      <c r="A21" s="121"/>
+      <c r="B21" s="122"/>
+      <c r="C21" s="122"/>
+      <c r="D21" s="122"/>
+      <c r="E21" s="122"/>
+      <c r="F21" s="123"/>
       <c r="G21" s="77"/>
       <c r="H21" s="77"/>
       <c r="I21" s="77"/>
@@ -6390,22 +6586,22 @@
       <c r="K21" s="77"/>
     </row>
     <row r="22" customFormat="false" ht="172.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="32" t="s">
-        <v>57</v>
+      <c r="A22" s="29" t="s">
+        <v>61</v>
       </c>
       <c r="B22" s="79" t="s">
-        <v>252</v>
-      </c>
-      <c r="C22" s="33" t="s">
+        <v>272</v>
+      </c>
+      <c r="C22" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="D22" s="33" t="s">
-        <v>227</v>
-      </c>
-      <c r="E22" s="33" t="s">
-        <v>253</v>
-      </c>
-      <c r="F22" s="118"/>
+      <c r="D22" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="E22" s="30" t="s">
+        <v>273</v>
+      </c>
+      <c r="F22" s="120"/>
       <c r="G22" s="77"/>
       <c r="H22" s="77"/>
       <c r="I22" s="77"/>
@@ -6414,19 +6610,19 @@
     </row>
     <row r="23" customFormat="false" ht="256.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="21" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="C23" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="F23" s="22"/>
       <c r="G23" s="77"/>
@@ -6437,20 +6633,20 @@
     </row>
     <row r="24" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="21" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="C24" s="15" t="s">
         <v>40</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="E24" s="15"/>
       <c r="F24" s="23" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="G24" s="77"/>
       <c r="H24" s="77"/>
@@ -6460,16 +6656,16 @@
     </row>
     <row r="25" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="21" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="C25" s="15" t="s">
         <v>44</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="E25" s="15"/>
       <c r="F25" s="23"/>
@@ -6480,12 +6676,20 @@
       <c r="K25" s="77"/>
     </row>
     <row r="26" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="83"/>
-      <c r="B26" s="84"/>
-      <c r="C26" s="84"/>
-      <c r="D26" s="84"/>
-      <c r="E26" s="84"/>
-      <c r="F26" s="28"/>
+      <c r="A26" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" s="35" t="s">
+        <v>281</v>
+      </c>
+      <c r="C26" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" s="35" t="s">
+        <v>282</v>
+      </c>
+      <c r="E26" s="35"/>
+      <c r="F26" s="36"/>
       <c r="G26" s="77"/>
       <c r="H26" s="77"/>
       <c r="I26" s="77"/>
@@ -6493,12 +6697,12 @@
       <c r="K26" s="77"/>
     </row>
     <row r="27" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="29"/>
-      <c r="B27" s="30"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="31"/>
+      <c r="A27" s="26"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="28"/>
       <c r="G27" s="77"/>
       <c r="H27" s="77"/>
       <c r="I27" s="77"/>
@@ -6506,22 +6710,22 @@
       <c r="K27" s="77"/>
     </row>
     <row r="28" customFormat="false" ht="114.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="32" t="s">
-        <v>68</v>
-      </c>
-      <c r="B28" s="33" t="s">
-        <v>261</v>
-      </c>
-      <c r="C28" s="33" t="s">
+      <c r="A28" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="B28" s="30" t="s">
+        <v>283</v>
+      </c>
+      <c r="C28" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="D28" s="33" t="s">
-        <v>262</v>
-      </c>
-      <c r="E28" s="33" t="s">
-        <v>263</v>
-      </c>
-      <c r="F28" s="34"/>
+      <c r="D28" s="30" t="s">
+        <v>284</v>
+      </c>
+      <c r="E28" s="30" t="s">
+        <v>285</v>
+      </c>
+      <c r="F28" s="31"/>
       <c r="G28" s="77"/>
       <c r="H28" s="77"/>
       <c r="I28" s="77"/>
@@ -6530,19 +6734,19 @@
     </row>
     <row r="29" customFormat="false" ht="195.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="21" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="C29" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>263</v>
+        <v>285</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>265</v>
+        <v>287</v>
       </c>
       <c r="F29" s="23"/>
       <c r="G29" s="77"/>
@@ -6553,20 +6757,20 @@
     </row>
     <row r="30" customFormat="false" ht="199" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="21" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="C30" s="15" t="s">
         <v>40</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>267</v>
+        <v>289</v>
       </c>
       <c r="E30" s="15"/>
       <c r="F30" s="23" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="G30" s="77"/>
       <c r="H30" s="77"/>
@@ -6576,16 +6780,16 @@
     </row>
     <row r="31" customFormat="false" ht="153.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="21" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="C31" s="15" t="s">
         <v>44</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>270</v>
+        <v>292</v>
       </c>
       <c r="E31" s="15"/>
       <c r="F31" s="23"/>
@@ -6596,12 +6800,20 @@
       <c r="K31" s="77"/>
     </row>
     <row r="32" customFormat="false" ht="153.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="83"/>
-      <c r="B32" s="84"/>
-      <c r="C32" s="84"/>
-      <c r="D32" s="84"/>
-      <c r="E32" s="84"/>
-      <c r="F32" s="28"/>
+      <c r="A32" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="B32" s="35" t="s">
+        <v>293</v>
+      </c>
+      <c r="C32" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="D32" s="35" t="s">
+        <v>294</v>
+      </c>
+      <c r="E32" s="35"/>
+      <c r="F32" s="36"/>
       <c r="G32" s="77"/>
       <c r="H32" s="77"/>
       <c r="I32" s="77"/>
@@ -6609,12 +6821,12 @@
       <c r="K32" s="77"/>
     </row>
     <row r="33" customFormat="false" ht="149.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="29"/>
-      <c r="B33" s="123"/>
-      <c r="C33" s="123"/>
-      <c r="D33" s="123"/>
-      <c r="E33" s="123"/>
-      <c r="F33" s="124"/>
+      <c r="A33" s="26"/>
+      <c r="B33" s="124"/>
+      <c r="C33" s="124"/>
+      <c r="D33" s="124"/>
+      <c r="E33" s="124"/>
+      <c r="F33" s="125"/>
       <c r="G33" s="77"/>
       <c r="H33" s="77"/>
       <c r="I33" s="77"/>
@@ -6714,21 +6926,21 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="3" width="26.32"/>
   </cols>
   <sheetData>
-    <row r="1" s="125" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="126" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="39" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="B1" s="39" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C1" s="40" t="s">
-        <v>271</v>
+        <v>295</v>
       </c>
       <c r="D1" s="40" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="E1" s="40" t="s">
-        <v>272</v>
+        <v>296</v>
       </c>
       <c r="F1" s="40" t="s">
         <v>27</v>
@@ -6737,19 +6949,19 @@
         <v>33</v>
       </c>
       <c r="H1" s="40" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="I1" s="40" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J1" s="41" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="XFD1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="43" t="s">
-        <v>273</v>
+        <v>297</v>
       </c>
       <c r="B2" s="44" t="n">
         <v>0</v>
@@ -6781,7 +6993,7 @@
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="43" t="s">
-        <v>274</v>
+        <v>298</v>
       </c>
       <c r="B3" s="44" t="n">
         <v>1</v>
@@ -6813,7 +7025,7 @@
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="43" t="s">
-        <v>275</v>
+        <v>299</v>
       </c>
       <c r="B4" s="44" t="n">
         <v>2</v>
@@ -6845,7 +7057,7 @@
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="43" t="s">
-        <v>276</v>
+        <v>300</v>
       </c>
       <c r="B5" s="44" t="n">
         <v>3</v>
@@ -6877,7 +7089,7 @@
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="43" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="B6" s="44" t="n">
         <v>4</v>
@@ -6909,7 +7121,7 @@
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="43" t="s">
-        <v>277</v>
+        <v>301</v>
       </c>
       <c r="B7" s="44" t="n">
         <v>5</v>
@@ -6941,7 +7153,7 @@
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="43" t="s">
-        <v>278</v>
+        <v>302</v>
       </c>
       <c r="B8" s="44" t="n">
         <v>6</v>
@@ -6973,7 +7185,7 @@
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="43" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="B9" s="44" t="n">
         <v>7</v>
@@ -7005,7 +7217,7 @@
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="43" t="s">
-        <v>279</v>
+        <v>303</v>
       </c>
       <c r="B10" s="44" t="n">
         <v>8</v>
@@ -7037,7 +7249,7 @@
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="43" t="s">
-        <v>280</v>
+        <v>304</v>
       </c>
       <c r="B11" s="44" t="n">
         <v>9</v>
@@ -7069,7 +7281,7 @@
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="43" t="s">
-        <v>281</v>
+        <v>305</v>
       </c>
       <c r="B12" s="44" t="n">
         <v>10</v>
@@ -7101,7 +7313,7 @@
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="43" t="s">
-        <v>282</v>
+        <v>306</v>
       </c>
       <c r="B13" s="44" t="n">
         <v>11</v>
@@ -7133,7 +7345,7 @@
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="43" t="s">
-        <v>283</v>
+        <v>307</v>
       </c>
       <c r="B14" s="44" t="n">
         <v>12</v>
@@ -7164,8 +7376,8 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="126" t="s">
-        <v>190</v>
+      <c r="A15" s="127" t="s">
+        <v>206</v>
       </c>
       <c r="B15" s="51" t="n">
         <v>13</v>
@@ -7239,7 +7451,7 @@
     </row>
     <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="C19" s="3" t="n">
         <v>122</v>
